--- a/Didox_MXIK_va_Ombor_Qoldigi.xlsx
+++ b/Didox_MXIK_va_Ombor_Qoldigi.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MXIK Ombor Qoldiq Balansi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MXIK Nomuvofiqliklari" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MXIK Jamlangan Balans" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MXIK Ombor Qoldiq Balansi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MXIK Nomuvofiqliklari" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,12 @@
       <b val="1"/>
       <color rgb="00991B1B"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +77,18 @@
         <bgColor rgb="00991B1B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -99,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -114,6 +131,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,6 +524,5067 @@
   <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>MXIK Kodi (17 xonali)</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Tasnif Nomi</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Birlashgan Tovar Nomlari Soni</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Ushbu MXIK ostidagi Tovar Nomlari (Tafsilot)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Jami Kirim Miqdori</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Jami Kirim Summasi (UZS)</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Jami Chiqim Miqdori</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Jami Chiqim Summasi (UZS)</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Hozirgi Ombor Qoldig'i (Kirim - Chiqim)</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Qoldiq Summasi (UZS)</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Holati</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>06214001011000000</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Тиббий бандаж</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>119</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>• "(01910) Бандаж поддерживающий для руки, правый,  Размер 2": [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 2": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
+• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 3": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
+• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 4": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
+• (01901) Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3: [Kirim: 32 | Chiqim: 0 | Qoldiq: 32]
+• (01901-3 )Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01902 )Бандаж детский для попучной грыжи: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01902) Бандаж детский для попучной грыжи: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• (01903) Бандаж эластичный дородовой, Размер 2: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• (01903) Бандаж эластичный дородовой, Размер 3: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• (01903-2)Бандаж эластичный дородовой, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01903-3)Бандаж эластичный дородовой, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01904) Бандаж фиксирующий эластичный, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01904) Бандаж фиксирующий эластичный, Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01904) Бандаж фиксирующий эластичный, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01904) Бандаж фиксирующий эластичный, Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01904-2)Бандаж фиксирующий эластичный, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01904-3)Бандаж фиксирующий эластичный, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01904-4)Бандаж фиксирующий эластичный, Размер 4: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01910) Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• (01910) Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01910-л)Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01910-п)Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• (01926) Бандаж поддерживающий для руки (детский): [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
+• (01926)Бандаж поддерживающий для руки (детский): [Kirim: 0 | Chiqim: 29 | Qoldiq: -29]
+• (01927) Бандаж поддерживающий для руки. Размер 2: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• (01927) Бандаж поддерживающий для руки. Размер 3: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• (01927-2)Бандаж поддерживающий для руки. Размер 2: [Kirim: 0 | Chiqim: 34 | Qoldiq: -34]
+• (01927-3)Бандаж поддерживающий для руки. Размер 3: [Kirim: 0 | Chiqim: 35 | Qoldiq: -35]
+• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01929-2)Бандаж медицинский послеоперационный (поддерживающий), Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01929-3)Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• (01929-4)Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• (01929-5)Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01931) Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01931) Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
+• (01931) Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
+• (01931-1)Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01931-2)Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
+• (01931-3)Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]
+• (01933) Бандаж послеродовой, Размер 2: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01933) Бандаж послеродовой, Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01933) Бандаж послеродовой, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01933-2)Бандаж послеродовой, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01933-3)Бандаж послеродовой, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01936) Бандаж послеродовой, Размер 2: [Kirim: 7 | Chiqim: 0 | Qoldiq: 7]
+• (01936-2)Бандаж для паховой грыжи, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01954-1)Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01954-2)Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• (01954-3)Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01961-1)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• (01961-2)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• (01961-3)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01979) Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01979) Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01979-2)Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01979-2)Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01984) Бандаж послеоперационный на грудной клетку, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01984) Бандаж послеоперационный на грудной клетку, Размер 3: [Kirim: 5 | Chiqim: 2 | Qoldiq: 3]
+• (01984) Бандаж послеоперационный на грудной клетку, Размер 4: [Kirim: 5 | Chiqim: 3 | Qoldiq: 2]
+• Бандаж детский для попучной грыжи: [Kirim: 40 | Chiqim: 56 | Qoldiq: -16]
+• Бандаж для паховой грыжи, Размер 2: [Kirim: 10 | Chiqim: 11 | Qoldiq: -1]
+• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
+• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
+• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• Бандаж медицинский послеоперационный (поддерживающий), Размер 2: [Kirim: 20 | Chiqim: 10 | Qoldiq: 10]
+• Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 20 | Chiqim: 14 | Qoldiq: 6]
+• Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 20 | Chiqim: 19 | Qoldiq: 1]
+• Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 10 | Chiqim: 5 | Qoldiq: 5]
+• Бандаж медицинский послеоперационный (поддерживающий), Размер 6: [Kirim: 10 | Chiqim: 2 | Qoldiq: 8]
+• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• Бандаж поддерживающий для руки (детский: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Бандаж поддерживающий для руки (детский): [Kirim: 60 | Chiqim: 147 | Qoldiq: -87]
+• Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 10 | Chiqim: 53 | Qoldiq: -43]
+• Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 10 | Chiqim: 50 | Qoldiq: -40]
+• Бандаж поддерживающий для руки. Размер 1: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
+• Бандаж поддерживающий для руки. Размер 2: [Kirim: 100 | Chiqim: 143 | Qoldiq: -43]
+• Бандаж поддерживающий для руки. Размер 3: [Kirim: 100 | Chiqim: 137 | Qoldiq: -37]
+• Бандаж послеоперационный на грудной клетку, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• Бандаж послеоперационный на грудной клетку, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• Бандаж послеоперационный на грудной клетку, Размер 4: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Бандаж послеродовой, Размер 2: [Kirim: 20 | Chiqim: 34 | Qoldiq: -14]
+• Бандаж послеродовой, Размер 3: [Kirim: 20 | Chiqim: 49 | Qoldiq: -29]
+• Бандаж послеродовой, Размер 4: [Kirim: 20 | Chiqim: 30 | Qoldiq: -10]
+• Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3: [Kirim: 0 | Chiqim: 19 | Qoldiq: -19]
+• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
+• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом) Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• Бандаж фиксирующий эластичный, Размер 2: [Kirim: 30 | Chiqim: 26 | Qoldiq: 4]
+• Бандаж фиксирующий эластичный, Размер 3: [Kirim: 30 | Chiqim: 49 | Qoldiq: -19]
+• Бандаж фиксирующий эластичный, Размер 4: [Kirim: 30 | Chiqim: 45 | Qoldiq: -15]
+• Бандаж фиксирующий эластичный, Размер 5: [Kirim: 30 | Chiqim: 27 | Qoldiq: 3]
+• Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 10 | Chiqim: 25 | Qoldiq: -15]
+• Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 10 | Chiqim: 70 | Qoldiq: -60]
+• Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 10 | Chiqim: 72 | Qoldiq: -62]
+• Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
+• Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 10 | Chiqim: 21 | Qoldiq: -11]
+• Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 10 | Chiqim: 29 | Qoldiq: -19]
+• Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 0 | Chiqim: 37 | Qoldiq: -37]
+• Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 0 | Chiqim: 37 | Qoldiq: -37]
+• Бандаж эластичный дородовой, Размер: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Бандаж эластичный дородовой, Размер 2: [Kirim: 30 | Chiqim: 58 | Qoldiq: -28]
+• Бандаж эластичный дородовой, Размер 2Бандаж эластичный дородовой, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Бандаж эластичный дородовой, Размер 3: [Kirim: 30 | Chiqim: 58 | Qoldiq: -28]
+• Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• Тутор коленного сустава, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>112599000</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>1622</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>94350446.15000017</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>26531338.3600377</v>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>09018010033000000</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Ўзбекистон Республикаси Соғлиқни сақлаш вазирлигининг 06.29.2016 йилдаги  60-сонли буйруғи билан тасдиқланган рўйхатга киритилган, тиббий буюмлар</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>111</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 1": [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
+• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 2": [Kirim: 400 | Chiqim: 0 | Qoldiq: 400]
+• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 3": [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]
+• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 1": [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 2": [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 3": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01908) Трусы медицинские после обрезания для мальчиков, Размер 2: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
+• (01908) Трусы медицинские после обрезания для мальчиков, Размер 3: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• (01908-1)Трусы медицинские для мальчиков Размер 1: [Kirim: 0 | Chiqim: 16 | Qoldiq: -16]
+• (01908-2)Трусы медицинские для мальчиков Размер 2: [Kirim: 0 | Chiqim: 46 | Qoldiq: -46]
+• (01908-3)Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 32 | Qoldiq: -32]
+• (01909) Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• (01909)Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01912) Воротник ортопедический жесткий, Размер 1: [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
+• (01912) Воротник ортопедический жесткий, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01912) Воротник ортопедический жесткий, Размер 3: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
+• (01912) Воротник ортопедический жесткий, Размер 4: [Kirim: 4 | Chiqim: 0 | Qoldiq: 4]
+• (01912-2)Воротник ортопедический жесткий, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01912-4)Воротник ортопедический жесткий, Размер 4: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01914-2)Корректор осанки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
+• (01914-3)Корректор осанки, Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• (01914-4)Корректор осанки, Размер 4: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
+• (01918) Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• (01918) Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• (01918) Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01918-2)Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
+• (01918-3)Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
+• (01918-4)Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 0 | Chiqim: 14 | Qoldiq: -14]
+• (01919-1)Корректор осанки детский, с рёбрами жёсткости, Размер 1: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01919-2)Корректор осанки детский, с рёбрами жёсткости, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01919-3)Корректор осанки детский, с рёбрами жёсткости, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
+• (01921-1)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01921-2)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01921-3)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01924) Воротник ортопедический, надувной: [Kirim: 77 | Chiqim: 0 | Qoldiq: 77]
+• (01924)Воротник ортопедический,надувной: [Kirim: 0 | Chiqim: 24 | Qoldiq: -24]
+• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
+• (01930-1)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01930-2)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• (01930-3)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
+• (01947) Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• (01947)Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]
+• (01950) Корректор осанки (универсальный): [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01950)Корректор осанки (универсальный): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01953)Корректор осанки, детский. (универсальный): [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• Shprist 50ml: [Kirim: 840 | Chiqim: 110 | Qoldiq: 730]
+• Браслет Идентификационный Голубого Цвета: [Kirim: 500 | Chiqim: 8 | Qoldiq: 492]
+• Браслет Идентификационный Розового Цвета: [Kirim: 500 | Chiqim: 10 | Qoldiq: 490]
+• Воротник ортопедический жесткий, Размер 1: [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
+• Воротник ортопедический жесткий, Размер 2: [Kirim: 5 | Chiqim: 9 | Qoldiq: -4]
+• Воротник ортопедический жесткий, Размер 3: [Kirim: 4 | Chiqim: 8 | Qoldiq: -4]
+• Воротник ортопедический жесткий, Размер 4: [Kirim: 4 | Chiqim: 6 | Qoldiq: -2]
+• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 10 | Chiqim: 22 | Qoldiq: -12]
+• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 10 | Chiqim: 45 | Qoldiq: -35]
+• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 10 | Chiqim: 40 | Qoldiq: -30]
+• Воротник ортопедический мягкий, для детей (шина шанца), Размер 1: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• Воротник ортопедический мягкий, для детей (шина шанца), Размер 2: [Kirim: 0 | Chiqim: 9 | Qoldiq: -9]
+• Воротник ортопедический мягкий, для детей (шина шанца), Размер 3: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• Воротник ортопедический мягкий, для детей, Размер 1: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
+• Воротник ортопедический мягкий, для детей, Размер 2: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
+• Воротник ортопедический мягкий, для детей, Размер 3: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
+• Воротник ортопедический, надувной: [Kirim: 56 | Chiqim: 7 | Qoldiq: 49]
+• Воротник ортопедический,надувной: [Kirim: 0 | Chiqim: 84 | Qoldiq: -84]
+• Канюля Кислородная, Стерильный для Однократного Применения для Подростковый (Child): [Kirim: 600 | Chiqim: 383 | Qoldiq: 217]
+• Катетеры Кислородные, Стерильные для Однократного Применения для Взрослых (Adult): [Kirim: 400 | Chiqim: 1,060 | Qoldiq: -660]
+• Катетеры Кислородные, Стерильный для Однократного Применения для Взрослый (Adult): [Kirim: 700 | Chiqim: 0 | Qoldiq: 700]
+• Корректор осанки (универсальный): [Kirim: 20 | Chiqim: 12 | Qoldiq: 8]
+• Корректор осанки детский, с рёбрами жёсткости, Размер 1: [Kirim: 10 | Chiqim: 18 | Qoldiq: -8]
+• Корректор осанки детский, с рёбрами жёсткости, Размер 2: [Kirim: 20 | Chiqim: 38 | Qoldiq: -18]
+• Корректор осанки детский, с рёбрами жёсткости, Размер 3: [Kirim: 20 | Chiqim: 26 | Qoldiq: -6]
+• Корректор осанки, Размер 1: [Kirim: 40 | Chiqim: 10 | Qoldiq: 30]
+• Корректор осанки, Размер 2: [Kirim: 40 | Chiqim: 22 | Qoldiq: 18]
+• Корректор осанки, Размер 3: [Kirim: 40 | Chiqim: 22 | Qoldiq: 18]
+• Корректор осанки, Размер 4: [Kirim: 40 | Chiqim: 12 | Qoldiq: 28]
+• Корректор осанки, детский. (универсальный): [Kirim: 20 | Chiqim: 11 | Qoldiq: 9]
+• Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 20 | Chiqim: 37 | Qoldiq: -17]
+• Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 20 | Chiqim: 57 | Qoldiq: -37]
+• Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 20 | Chiqim: 32 | Qoldiq: -12]
+• Маска Кислородная, Стерильная для Однократного Применения для Взрослый: [Kirim: 200 | Chiqim: 47 | Qoldiq: 153]
+• Маска Кислородная, Стерильная для Однократного Применения для Детский: [Kirim: 200 | Chiqim: 49 | Qoldiq: 151]
+• Мочеприемник Прикроватный с Т-образным Сливным Клапаном, Стерильный для Однократного Применения Объемом 2 л: [Kirim: 500 | Chiqim: 320 | Qoldiq: 180]
+• Набор для ингалятора (Маска кислородная) Disposable Nebulizer для взрослых: [Kirim: 200 | Chiqim: 84 | Qoldiq: 116]
+• Набор для ингалятора (Маска кислородная) Disposable Nebulizer для детский: [Kirim: 200 | Chiqim: 200 | Qoldiq: 0]
+• Небулайзер Компрессорный NIMO модель HNK-NBL-S с Комплектующими: [Kirim: 48 | Chiqim: 14 | Qoldiq: 34]
+• Перчатки ARMOUR Хирургические, Латексные, Стерильный для Однократного Применения, Размер: 7,5: [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
+• Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5: [Kirim: 0 | Chiqim: 500 | Qoldiq: -500]
+• Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 54 | Qoldiq: -54]
+• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 10 | Chiqim: 12 | Qoldiq: -2]
+• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 10 | Chiqim: 27 | Qoldiq: -17]
+• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 10 | Chiqim: 23 | Qoldiq: -13]
+• Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 20 | Chiqim: 39 | Qoldiq: -19]
+• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 11 SURGEON: [Kirim: 250 | Chiqim: 340 | Qoldiq: -90]
+• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 15 SURGEON: [Kirim: 250 | Chiqim: 250 | Qoldiq: 0]
+• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 22 SURGEON: [Kirim: 500 | Chiqim: 580 | Qoldiq: -80]
+• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 23 SURGEON: [Kirim: 500 | Chiqim: 500 | Qoldiq: 0]
+• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 24 SURGEON: [Kirim: 250 | Chiqim: 250 | Qoldiq: 0]
+• Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 11  SURGEON: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
+• Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 22  SURGEON: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
+• Трусы медицинские для мальчиков Размер 1: [Kirim: 0 | Chiqim: 417 | Qoldiq: -417]
+• Трусы медицинские для мальчиков Размер 2: [Kirim: 0 | Chiqim: 924 | Qoldiq: -924]
+• Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 821 | Qoldiq: -821]
+• Трусы медицинские для мальчиков Размер 3Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• Трусы медицинские после обрезания для мальчиков, Размер 1: [Kirim: 400 | Chiqim: 5 | Qoldiq: 395]
+• Трусы медицинские после обрезания для мальчиков, Размер 2: [Kirim: 600 | Chiqim: 44 | Qoldiq: 556]
+• Трусы медицинские после обрезания для мальчиков, Размер 3: [Kirim: 400 | Chiqim: 9 | Qoldiq: 391]</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>12094</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>138336000</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>7858</v>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>111617589.0499999</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>4236</v>
+      </c>
+      <c r="K3" s="13" t="n">
+        <v>48453059.03753927</v>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>03923001007000000</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Пластмассадан тайёрланган идишлар, бутилкалар, флаконлар ва шунга ўхшаш идишлар</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>• .Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт.: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• Бутылка для детс.питание "MUMMY" обье 80 мл 1074-1 кор.-1шт: [Kirim: 240 | Chiqim: 2,017 | Qoldiq: -1,777]
+• Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128-  шт: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
+• Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128- шт: [Kirim: 0 | Chiqim: 435 | Qoldiq: -435]
+• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт: [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
+• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт.: [Kirim: 984 | Chiqim: 1,166 | Qoldiq: -182]
+• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1127-шт.: [Kirim: 480 | Chiqim: 518 | Qoldiq: -38]
+• Бутылка плас-вые с ручкой для кормление 240мл/ MUMMY 1079- шт: [Kirim: 528 | Chiqim: 452 | Qoldiq: 76]
+• Бутылочки для детс. питание "MUMMY"1074: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Бутылочки для детс. питание "MUMMY"1078: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Бутылочки для детс. питание "MUMMY"1079: [Kirim: 72 | Chiqim: 5 | Qoldiq: 67]
+• Бутылочки для детс. питание "MUMMY"1127: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Бутылочки для детс. питание "MUMMY"1128: [Kirim: 312 | Chiqim: 0 | Qoldiq: 312]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 1 шт: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 шт-: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074- шт: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт: [Kirim: 1,128 | Chiqim: 0 | Qoldiq: 1,128]
+• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт-: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Детская бутылка пластмассовый    (7.17.016) 330ml: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детская бутылка пластмассовый   (ALGO 7.17.013) 125ml: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
+• Детская бутылка пластмассовый  (7.17.017) 260 ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детская бутылка пластмассовый  (ALGO 7.17.012) 280 ml: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детская бутылка пластмассовый  (ALGO 8107) 280 ml: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
+• Детская бутылка пластмассовый  (ALGO 8228) 60 ml: [Kirim: 576 | Chiqim: 0 | Qoldiq: 576]
+• Детская бутылка пластмассовый  (RBT-706)  706ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детская бутылка пластмассовый (7,17,016) 330 ml: [Kirim: 0 | Chiqim: 126 | Qoldiq: -126]
+• Детская бутылка пластмассовый (7,17,017) 260 ml: [Kirim: 0 | Chiqim: 92 | Qoldiq: -92]
+• Детская бутылка пластмассовый (7.17.016) 330 ml: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детская бутылка пластмассовый (ALGO 8107) 280 ml: [Kirim: 0 | Chiqim: 508 | Qoldiq: -508]
+• Детская бутылка пластмассовый (ALGO 8228) 60 ml: [Kirim: 0 | Chiqim: 1,270 | Qoldiq: -1,270]
+• Детская бутылка пластмассовый (RBT-706) 706ml (7.17.027): [Kirim: 0 | Chiqim: 82 | Qoldiq: -82]
+• Детская бутылка пластмассовый 125ml Бренд: ALGO 8108 (7.17.013): [Kirim: 288 | Chiqim: 635 | Qoldiq: -347]
+• Детская бутылка пластмассовый Бренд: ALGO. Model: 8228 60ml (7.17.042): [Kirim: 1,152 | Chiqim: 0 | Qoldiq: 1,152]
+• Детские  бутылки  180 мл (DDE-1035): [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
+• Детские  бутылки  270 мл (DDE-1036): [Kirim: 210 | Chiqim: 0 | Qoldiq: 210]
+• Детские  бутылки (200): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские  бутылки (248): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детские  бутылки ONLY BABY NATURAL 125 мл (А-3): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детские  бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детские бутилки (248): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутилки (249): [Kirim: 288 | Chiqim: 54 | Qoldiq: 234]
+• Детские бутилки (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутилки (360): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки  (200): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки  (201): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки  (202): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки  (249): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки (200) 180ml: [Kirim: 0 | Chiqim: 136 | Qoldiq: -136]
+• Детские бутылки (201): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки (201) 240ml: [Kirim: 0 | Chiqim: 136 | Qoldiq: -136]
+• Детские бутылки (202): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Детские бутылки (202) 300ml: [Kirim: 0 | Chiqim: 72 | Qoldiq: -72]
+• Детские бутылки (248): [Kirim: 144 | Chiqim: 716 | Qoldiq: -572]
+• Детские бутылки (249): [Kirim: 432 | Chiqim: 954 | Qoldiq: -522]
+• Детские бутылки (358): [Kirim: 864 | Chiqim: 1,296 | Qoldiq: -432]
+• Детские бутылки (360): [Kirim: 1,584 | Chiqim: 1,946 | Qoldiq: -362]
+• Детские бутылки (A-2-T): [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детские бутылки (А-2 )  260 мл: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детские бутылки (А-2 ) 260 мл: [Kirim: 0 | Chiqim: 186 | Qoldiq: -186]
+• Детские бутылки (А-3-Т 125 мл): [Kirim: 192 | Chiqim: 186 | Qoldiq: 6]
+• Детские бутылки 180 мл (DDE-1035): [Kirim: 0 | Chiqim: 107 | Qoldiq: -107]
+• Детские бутылки 270 мл (DDE-1036): [Kirim: 0 | Chiqim: 24 | Qoldiq: -24]
+• Детские бутылки ONLY BABY NATURAL 125 мл (А-3): [Kirim: 0 | Chiqim: 41 | Qoldiq: -41]
+• Детские бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 0 | Chiqim: 26 | Qoldiq: -26]
+• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7,17,036: [Kirim: 0 | Chiqim: 1,015 | Qoldiq: -1,015]
+• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7.17.036: [Kirim: 1,056 | Chiqim: 0 | Qoldiq: 1,056]
+• Детские бутылки стеклянные из безцвет стекла 120ml (9131): [Kirim: 384 | Chiqim: 12 | Qoldiq: 372]
+• Детские бутылки стеклянные из безцвет стекла 120ml (9131) (7.17.032): [Kirim: 0 | Chiqim: 796 | Qoldiq: -796]
+• Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519) (7.17.021): [Kirim: 0 | Chiqim: 39 | Qoldiq: -39]
+• Детские бутылки стеклянные из безцвет стекла 240ml (9130): [Kirim: 384 | Chiqim: 12 | Qoldiq: 372]
+• Детские бутылки стеклянные из безцвет стекла 240ml (9130) (7.17.031): [Kirim: 0 | Chiqim: 555 | Qoldiq: -555]
+• Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374): [Kirim: 192 | Chiqim: 10 | Qoldiq: 182]
+• Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374) (7.17.023): [Kirim: 0 | Chiqim: 278 | Qoldiq: -278]
+• Детские бутылки стеклянные из безцвет стекла ALGO 120ml (7.17.043): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детские бутылки стеклянные из безцвет стекла ALGO 120ml (RBT-206) (7,17,043): [Kirim: 0 | Chiqim: 196 | Qoldiq: -196]
+• Детские бутьлки  (248): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутьлки  (249): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутьлки  (358: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутьлки  (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутьлки  (360 ): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Соска-Пустышки "PANDA" силиконовая 1122: [Kirim: 720 | Chiqim: 348 | Qoldiq: 372]</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>19266</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>217341945.0000003</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>16457</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>241963660.569998</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>2809</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>31688649.61616323</v>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>04016001083000000</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Резинали сўрғич</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>• Teddy Ниппел накладкаси + сўрғич: [Kirim: 630 | Chiqim: 225 | Qoldiq: 405]
+• Дет Соски (LOT-10): [Kirim: 320 | Chiqim: 650 | Qoldiq: -330]
+• Детcкие Соски (LOT-12): [Kirim: 340 | Chiqim: 340 | Qoldiq: 0]
+• Детские  соски (260): [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
+• Детские  соски (383): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские  соски (387): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские  соски для питания (285): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские  соски для питания (291): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские Cоски  (383): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские соски  для питания (285): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детские соски  для питания (291): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
+• Детские соски (038): [Kirim: 11,520 | Chiqim: 10,790 | Qoldiq: 730]
+• Детские соски (260): [Kirim: 1,008 | Chiqim: 1,056 | Qoldiq: -48]
+• Детские соски (383): [Kirim: 216 | Chiqim: 345 | Qoldiq: -129]
+• Детские соски (387): [Kirim: 576 | Chiqim: 680 | Qoldiq: -104]
+• Детские соски (LOT-10): [Kirim: 640 | Chiqim: 2 | Qoldiq: 638]
+• Детские соски для питания (285): [Kirim: 0 | Chiqim: 382 | Qoldiq: -382]
+• Детские соски для питания (291): [Kirim: 72 | Chiqim: 569 | Qoldiq: -497]
+• Соска для питание ниблер MUMMY 1129-1 шт: [Kirim: 288 | Chiqim: 5 | Qoldiq: 283]
+• Соска для питание ниблер MUMMY 1129-1 шт -: [Kirim: 360 | Chiqim: 751 | Qoldiq: -391]
+• Соска для питание ниблер MUMMY 1129-1 шт -2025: [Kirim: 108 | Chiqim: 0 | Qoldiq: 108]
+• Соска пустышка Panda c крышкой 106 шт: [Kirim: 2,220 | Chiqim: 3,864 | Qoldiq: -1,644]
+• Соска-Пустышки "PANDA"  силиконовая 1123: [Kirim: 7,200 | Chiqim: 0 | Qoldiq: 7,200]
+• Соска-Пустышки "PANDA" силиконовая 1122: [Kirim: 5,760 | Chiqim: 5,689 | Qoldiq: 71]
+• Соска-Пустышки "PANDA" силиконовая 1123: [Kirim: 0 | Chiqim: 7,669 | Qoldiq: -7,669]
+• Соски пустышки Mummy 1112: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Соски пустышки Mummy 1113: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Соски пустышки Mummy 1114: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Соски пустышки Mummy модель 1111 в одном комплекте 2 шт: [Kirim: 216 | Chiqim: 2 | Qoldiq: 214]
+• Соски пустышки Mummy модель 1112 в одном комплекте 2 шт: [Kirim: 72 | Chiqim: 2 | Qoldiq: 70]
+• Соски пустышки Mummy модель1113 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Соски пустышки Mummy модель1115 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Соски-Пустышки "PANDA" 100: [Kirim: 5,760 | Chiqim: 12 | Qoldiq: 5,748]
+• Соски-Пустышки "PANDA" 100 шт: [Kirim: 1,440 | Chiqim: 6,386 | Qoldiq: -4,946]</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>40738</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>100886785.7</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>39419</v>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>110605802.9999992</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1319</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>3266475.289368649</v>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>09021001001000000</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Ортопедик асбоблар (таёқчалар, бинтлар, камарлар) ёки синишларни даволаш учун (шу жумладан шиналар)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>• "(01959) Вальгусная шина большого пальца стопы (шарнирная), пара ": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• "(01960) Вальгусная шина большого пальца стопы (носочки), пара. Размер (S)": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01905) Вальгусная шина большого пальца стопы (ночная), пара: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
+• (01905)Вальгусная шина большого пальца стопы (ночная): [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• (01922) Тутор коленного сустава, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01922) Тутор коленного сустава, Размер 2: [Kirim: 24 | Chiqim: 0 | Qoldiq: 24]
+• (01922) Тутор коленного сустава, Размер 3: [Kirim: 15 | Chiqim: 0 | Qoldiq: 15]
+• (01922-2)Тутор коленного сустава, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01922-3)Тутор коленного сустава, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01922d) Тутор коленного сустава, детский универсальный: [Kirim: 7 | Chiqim: 0 | Qoldiq: 7]
+• (01923) Вальгусная шина большого пальца стопы (дневной), пара: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• (01960)Вальгусная шина большого пальцастопы (носочки), пара. Размер (S): [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
+• (01963) Шина для фиксации пальцев руки, Размер 1: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01963) Шина для фиксации пальцев руки, Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• (01963) Шина для фиксации пальцев руки, Размер 3: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• Вальгусная шина большого пальца стопы (дневной), пара: [Kirim: 20 | Chiqim: 50 | Qoldiq: -30]
+• Вальгусная шина большого пальца стопы (носочки), пара. Размер (S): [Kirim: 20 | Chiqim: 6 | Qoldiq: 14]
+• Вальгусная шина большого пальца стопы (ночная): [Kirim: 0 | Chiqim: 79 | Qoldiq: -79]
+• Вальгусная шина большого пальца стопы (ночная), пара: [Kirim: 20 | Chiqim: 2 | Qoldiq: 18]
+• Вальгусная шина большого пальца стопы (шарнирная), пара: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
+• Вальгусная шина большого пальцастопы (носочки), пара. Размер (S): [Kirim: 0 | Chiqim: 22 | Qoldiq: -22]
+• Вальгусная шина большого пальцастопы (шарнирная), пара: [Kirim: 0 | Chiqim: 34 | Qoldiq: -34]
+• Костыли Нержавейка №2 Китай: [Kirim: 190 | Chiqim: 190 | Qoldiq: 0]
+• Тутор коленного сустава, Размер 1: [Kirim: 5 | Chiqim: 6 | Qoldiq: -1]
+• Тутор коленного сустава, Размер 2: [Kirim: 6 | Chiqim: 23 | Qoldiq: -17]
+• Тутор коленного сустава, Размер 3: [Kirim: 6 | Chiqim: 16 | Qoldiq: -10]
+• Тутор коленного сустава, детский универсальный: [Kirim: 7 | Chiqim: 7 | Qoldiq: 0]
+• Шина для фиксации пальцев руки, Размер 1: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
+• Шина для фиксации пальцев руки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
+• Шина для фиксации пальцев руки, Размер 3: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>570</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>38694000</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>472</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>42580503.55</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>6652652.631578947</v>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>00000000000000000</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Tasnif kodi</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>• Amelya oq: [Kirim: 0 | Chiqim: 2,000 | Qoldiq: -2,000]
+• Ayollar gigiyenik prokladkasi: [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
+• Best soft 120-talik: [Kirim: 0 | Chiqim: 1,200 | Qoldiq: -1,200]
+• Best soft 15-talik: [Kirim: 0 | Chiqim: 4,320 | Qoldiq: -4,320]
+• Best soft 72-talik: [Kirim: 0 | Chiqim: 1,200 | Qoldiq: -1,200]
+• Diva mamasha: [Kirim: 0 | Chiqim: 1,500 | Qoldiq: -1,500]
+• Gigiyenik mahsulotlar: [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
+• Tayyor biologik oziq-ovqat qo'shimchalari: [Kirim: 0 | Chiqim: 5,310,003 | Qoldiq: -5,310,003]
+• kattalar-bolalar tagliklari, (gigeniya va xo’jalik mahsulotlari): [Kirim: 0 | Chiqim: 500,000,000 | Qoldiq: -500,000,000]
+• Аскорбинка Витаминка C: [Kirim: 0 | Chiqim: 6,150,000 | Qoldiq: -6,150,000]
+• Бумагу и изделия бумажные санитарно-гигиенического назначения: [Kirim: 0 | Chiqim: 36,000,000 | Qoldiq: -36,000,000]
+• Гигиена ёки душ воситалари: [Kirim: 0 | Chiqim: 5,000,000 | Qoldiq: -5,000,000]
+• Гигиеник воситалар: [Kirim: 8,950,800 | Chiqim: 0 | Qoldiq: 8,950,800]
+• Гигиеник воситаларлар: [Kirim: 16,250,800 | Chiqim: 0 | Qoldiq: 16,250,800]
+• Детские гигиенические товары (бутылки для детского питания, зубогрызки , соски в ассортименте): [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
+• Детские гигиенические товары в  ассортименте: [Kirim: 209,247,300 | Chiqim: 0 | Qoldiq: 209,247,300]
+• Детские гигиенические товары в ассортименте: [Kirim: 97,698,400 | Chiqim: 0 | Qoldiq: 97,698,400]
+• Детские товары в ассортименте: [Kirim: 0 | Chiqim: 600,000,000 | Qoldiq: -600,000,000]
+• Зубные щетки в ассортименте: [Kirim: 0 | Chiqim: 13,642,800 | Qoldiq: -13,642,800]
+• Масло оливковое очищенное: [Kirim: 0 | Chiqim: 3,469,200 | Qoldiq: -3,469,200]
+• Парфюмерно-косметическая продукция и влажные гигиенические салфетки в ассортименте: [Kirim: 0 | Chiqim: 83,382,000 | Qoldiq: -83,382,000]
+• Пахтали таёкчалар: [Kirim: 0 | Chiqim: 15,001,000 | Qoldiq: -15,001,000]
+• Пластмассадан  тайорланган  бутилкалар  флаконлар  ва шунга  ухшаш  идишлар: [Kirim: 4,759,300 | Chiqim: 0 | Qoldiq: 4,759,300]
+• Подгузники детские упакованные в пакеты из полимерной пленки: [Kirim: 0 | Chiqim: 200,000,000 | Qoldiq: -200,000,000]
+• Тиш пастаси: [Kirim: 5,362,300 | Chiqim: 0 | Qoldiq: 5,362,300]
+• Товары народного потребления: [Kirim: 0 | Chiqim: 35,002,200 | Qoldiq: -35,002,200]
+• дори дармон ва бад махсулотлари учун: [Kirim: 500,000,000 | Chiqim: 0 | Qoldiq: 500,000,000]
+• кир ювиш парашоги: [Kirim: 0 | Chiqim: 2,700,000 | Qoldiq: -2,700,000]
+• медицинские изделия: [Kirim: 0 | Chiqim: 132,889,248 | Qoldiq: -132,889,248]
+• тиббий буюмлар: [Kirim: 0 | Chiqim: 5,081,440 | Qoldiq: -5,081,440]</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>842268899.99</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1943638110.88</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>-1101369210.89</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>03306001001000000</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Тиш пастаси</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>• Зубная паста Лесной бальзам с органическими маслами, углём и кальцием, 75 МЛ: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
+• Зубная паста детская Ежик Сема  60мл: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• Зубная паста детская Ежик Сема  Крем брюле 60мл: [Kirim: 180 | Chiqim: 0 | Qoldiq: 180]
+• Зубная паста детская Ежик Сема 60мл: [Kirim: 0 | Chiqim: 101 | Qoldiq: -101]
+• Зубная паста детская Крокодильчик Свомпи  с мятой 60мл: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
+• Зубная паста детская Крокодильчик Свомпи с мятой 60мл: [Kirim: 0 | Chiqim: 139 | Qoldiq: -139]
+• Зубная паста профилактическая детская Фруктовая  75г: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
+• Зубная паста профилактическая детская Фруктовая 75г: [Kirim: 0 | Chiqim: 105 | Qoldiq: -105]
+• ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ Р2, 75 МЛ: [Kirim: 12 | Chiqim: 104 | Qoldiq: -92]
+• ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ ЧЗ, 75 МЛ: [Kirim: 36 | Chiqim: 5 | Qoldiq: 31]
+• ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ КОРЫ ДУБА И ПИХТЫ НА ОТВАРЕ ТРАВ, 75 МЛ: [Kirim: 96 | Chiqim: 6 | Qoldiq: 90]
+• ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ ПРОПОЛИСА И ЗВЕРОБОЯ НА ОТВАРЕ ТРАВ, 75 МЛ: [Kirim: 36 | Chiqim: 0 | Qoldiq: 36]
+• ЛЕСНОЙ БАЛЬЗАМ Профилактическая зубная паста "Лесной бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ: [Kirim: 36 | Chiqim: 0 | Qoldiq: 36]
+• Профилактическая зубная паста "Лесной Бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ: [Kirim: 12 | Chiqim: 28 | Qoldiq: -16]
+• Профилактическая зубная паста "Лесной Бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
+• Профилактическая зубная паста "Лесной бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ: [Kirim: 36 | Chiqim: 61 | Qoldiq: -25]
+• Профилактическая зубная паста "Лесной бальзам" с экстрактами коры дуба и пихты на отваре трав, 75 МЛ: [Kirim: 96 | Chiqim: 134 | Qoldiq: -38]
+• Профилактическая зубная паста "Лесной бальзам" с экстрактами прополиса и зверобоя на отваре трав, 75 МЛ: [Kirim: 48 | Chiqim: 19 | Qoldiq: 29]
+• Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 МЛ: [Kirim: 48 | Chiqim: 125 | Qoldiq: -77]
+• Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 мл: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
+• детская Ежик Сема с мятой  60мл: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
+• детская Ежик Сема с мятой 60мл: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>1322</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>8164047.879999999</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>842</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>8254017.82</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>480</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>2964253.390620272</v>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>09619002001000000</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Тагликлар</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>• SMART ADULT DIAPERS L: [Kirim: 1,200 | Chiqim: 1,200 | Qoldiq: 0]
+• SMART ADULT DIAPERS M: [Kirim: 600 | Chiqim: 540 | Qoldiq: 60]
+• SMART ADULT DIAPERS XL: [Kirim: 2,400 | Chiqim: 2,342 | Qoldiq: 58]
+• Подгузники для взрослых  Evony  Х-Large 30х4: [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
+• Подгузники для взрослых  Evony Large 30х4: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
+• Подгузники для взрослых  Evony М размер 30х4: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• Подгузники для взрослых Evony Large 30х4: [Kirim: 0 | Chiqim: 80 | Qoldiq: -80]
+• Подгузники для взрослых Evony М размер 30х4: [Kirim: 0 | Chiqim: 40 | Qoldiq: -40]
+• Подгузники для взрослых Evony Х-Large 30х4: [Kirim: 0 | Chiqim: 160 | Qoldiq: -160]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/12: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/38: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MAXI 4/16: [Kirim: 840 | Chiqim: 0 | Qoldiq: 840]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MIDI 3/18: [Kirim: 600 | Chiqim: 0 | Qoldiq: 600]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR 5/14: [Kirim: 840 | Chiqim: 596 | Qoldiq: 244]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/12: [Kirim: 0 | Chiqim: 203 | Qoldiq: -203]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/38: [Kirim: 0 | Chiqim: 27 | Qoldiq: -27]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MAXI 4/16: [Kirim: 0 | Chiqim: 621 | Qoldiq: -621]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MIDI 3/18: [Kirim: 0 | Chiqim: 452 | Qoldiq: -452]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MINI 2/20: [Kirim: 720 | Chiqim: 421 | Qoldiq: 299]
+• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium YENIDOG'AN 1/22: [Kirim: 1,745 | Chiqim: 972 | Qoldiq: 773]</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>9515</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>137804285.72</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>7654</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>136209821.5499999</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>26952577.58538307</v>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>03304999015000000</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Присыпка (в т.ч. детская)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>• Kodomo Детская присыпка (Extra Mild) 50гр: [Kirim: 576 | Chiqim: 489 | Qoldiq: 87]
+• Kodomo Детская присыпка (Extra Mild) English &amp; Arabic Label 180гр: [Kirim: 336 | Chiqim: 178 | Qoldiq: 158]
+• Kodomo Детская присыпка (Gentle Soft) 50гр: [Kirim: 576 | Chiqim: 624 | Qoldiq: -48]
+• Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр: [Kirim: 240 | Chiqim: 207 | Qoldiq: 33]
+• Kodomo Детская присыпка (Natural Soft Protection) 50гр: [Kirim: 576 | Chiqim: 620 | Qoldiq: -44]
+• Kodomo Детская присыпка (Natural Soft Protection)English &amp; Arabic Language 180гр: [Kirim: 288 | Chiqim: 207 | Qoldiq: 81]
+• Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 160гр: [Kirim: 240 | Chiqim: 174 | Qoldiq: 66]
+• Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр: [Kirim: 576 | Chiqim: 608 | Qoldiq: -32]
+• Teddy Болалар упаси (Лаванда) 50 гр: [Kirim: 432 | Chiqim: 367 | Qoldiq: 65]
+• Teddy Болалар упаси (Оддий) 50 гр: [Kirim: 432 | Chiqim: 219 | Qoldiq: 213]
+• Teddy Присыпка  простой  50 гр: [Kirim: 216 | Chiqim: 0 | Qoldiq: 216]
+• Детская присыпка  " Попкинсы"  120г: [Kirim: 320 | Chiqim: 0 | Qoldiq: 320]
+• Детская присыпка " Попкинсы" 120г: [Kirim: 0 | Chiqim: 120 | Qoldiq: -120]
+• Детская присыпка 80 г/Puder 80g: [Kirim: 24 | Chiqim: 10 | Qoldiq: 14]
+• Пересипка детский Baby "UPPY" 100 мл: [Kirim: 960 | Chiqim: 960 | Qoldiq: 0]
+• №1 Kodomo Детская присыпка (Gentle Soft) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• №1 Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр: [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
+• №1 Kodomo Детская присыпка (Natural Soft Protection) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• №1 Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>6704</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>61153395.69000001</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>4783</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>56578035.75999999</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>1921</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>17523220.93086068</v>
+      </c>
+      <c r="L10" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>04014001012000000</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Тишлар учун резина</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>• Грудная накладка  MUMMY - 1132 -шт: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Грудная накладка MUMMY - 1132 -шт: [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
+• Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION) (7.29.003): [Kirim: 0 | Chiqim: 225 | Qoldiq: -225]
+• Детский силиконовый прорезыватель для зубов RBT-401  (CORN EDITION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION): [Kirim: 0 | Chiqim: 256 | Qoldiq: -256]
+• Детский силиконовый прорезыватель для зубов RBT-402  (BANANA EDITION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION): [Kirim: 0 | Chiqim: 255 | Qoldiq: -255]
+• Зубагризки: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Зубагризки (FZ-188): [Kirim: 432 | Chiqim: 456 | Qoldiq: -24]
+• Зубагризки (FZ-189): [Kirim: 432 | Chiqim: 401 | Qoldiq: 31]
+• Зубогрызки из силикова Артикуль №3 MUMMY модел 1102-  шт: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
+• Зубогрызки из силикова Артикуль №3 MUMMY модел 1102- шт: [Kirim: 96 | Chiqim: 697 | Qoldiq: -601]
+• Зубогрызки из силикона Артикуль №1 MUMMY модель 1100-шт: [Kirim: 2,640 | Chiqim: 2,556 | Qoldiq: 84]
+• Зубогрызки из силикона Артикуль №2 MUMMY модел 1101- шт: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Зубогрызки из силикона Артикуль №2 MUMMY модел 1101-шт: [Kirim: 1,296 | Chiqim: 1,468 | Qoldiq: -172]
+• Соска-Пустышки "PANDA"  силиконовая 1123: [Kirim: 1,440 | Chiqim: 0 | Qoldiq: 1,440]
+• Соска-Пустышки "PANDA" силиконовая 1123: [Kirim: 0 | Chiqim: 336 | Qoldiq: -336]</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>8352</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>28759388.57</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>6670</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>32928392.3900001</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1682</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>5791821.309236111</v>
+      </c>
+      <c r="L11" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>06214001013000000</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Корсет маҳсулотлари</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>• (01944) Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01944) Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01944) Корсет эластичный для коррекции фигуры, Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• (01944-3)Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01944-4)Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
+• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 28 | Chiqim: 0 | Qoldiq: 28]
+• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 49 | Chiqim: 0 | Qoldiq: 49]
+• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 28 | Chiqim: 0 | Qoldiq: 28]
+• (01946-2)Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 0 | Chiqim: 9 | Qoldiq: -9]
+• (01946-3)Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
+• (01946-4)Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
+• Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 21 | Chiqim: 35 | Qoldiq: -14]
+• Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 21 | Chiqim: 43 | Qoldiq: -22]
+• Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 21 | Chiqim: 32 | Qoldiq: -11]
+• Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 10 | Chiqim: 8 | Qoldiq: 2]
+• Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 10 | Chiqim: 6 | Qoldiq: 4]
+• Корсет эластичный для коррекции фигуры, Размер 5: [Kirim: 10 | Chiqim: 9 | Qoldiq: 1]</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>228</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>14646000</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>12213482.32999999</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>3918447.368421053</v>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>03003001018000000</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Бошқа қадоқланмаган дори воситалари (фармацевтик субстанциялар)</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>• Achchiq bodom 100 ml: [Kirim: 200 | Chiqim: 200 | Qoldiq: 0]
+• G'oz moyi 100 ml: [Kirim: 100 | Chiqim: 387 | Qoldiq: -287]
+• Gʻoz 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• G’oz yogʻi 100ml: [Kirim: 200 | Chiqim: 10 | Qoldiq: 190]
+• Kanakunjut 100 ml: [Kirim: 200 | Chiqim: 500 | Qoldiq: -300]
+• Kanakunjut 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• Kanakunjut yogʻi 100ml: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
+• Qovoq danak moyi 100 ml: [Kirim: 100 | Chiqim: 113 | Qoldiq: -13]
+• Qovoq donagi moyi 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• Sedana 100 ml: [Kirim: 200 | Chiqim: 281 | Qoldiq: -81]
+• Sedana 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
+• Shaftoli danak moyi 100 ml: [Kirim: 500 | Chiqim: 500 | Qoldiq: 0]
+• Shirin bodom 100 ml: [Kirim: 200 | Chiqim: 181 | Qoldiq: 19]
+• Zaytun 100 ml: [Kirim: 500 | Chiqim: 1,380 | Qoldiq: -880]
+• Zaytun 100ml: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
+• Zaytun yogʻi 100ml: [Kirim: 600 | Chiqim: 20 | Qoldiq: 580]</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>16387919</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>3572</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>18383124.71000005</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>566933.4140540541</v>
+      </c>
+      <c r="L13" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>02106999028000000</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>• Achchiq bodom yog'i 100 ml: [Kirim: 100 | Chiqim: 100 | Qoldiq: 0]
+• Achchiq bodom yog'i 100ml: [Kirim: 200 | Chiqim: 54 | Qoldiq: 146]
+• G'oz yog'i 100 ml: [Kirim: 100 | Chiqim: 48 | Qoldiq: 52]
+• Kanakunjut yog'i 100 ml: [Kirim: 300 | Chiqim: 294 | Qoldiq: 6]
+• Kanakunjut yog'i 100ml: [Kirim: 100 | Chiqim: 100 | Qoldiq: 0]
+• Qora sedana yog'i 100 ml: [Kirim: 200 | Chiqim: 107 | Qoldiq: 93]
+• Sedana yog'i 100ml: [Kirim: 100 | Chiqim: 50 | Qoldiq: 50]
+• Shaftoli danagi yog'i 100 ml: [Kirim: 500 | Chiqim: 366 | Qoldiq: 134]
+• Shaftoli yog'i 100ml: [Kirim: 300 | Chiqim: 268 | Qoldiq: 32]
+• Shirin bodom yog'i 100ml: [Kirim: 200 | Chiqim: 92 | Qoldiq: 108]
+• Zaytun yog'i 100 ml: [Kirim: 1,200 | Chiqim: 1,185 | Qoldiq: 15]
+• Zaytun yog'i 100ml: [Kirim: 300 | Chiqim: 300 | Qoldiq: 0]
+• Пол Пола чай №15: [Kirim: 450 | Chiqim: 67 | Qoldiq: 383]
+• Расторопша чай №15: [Kirim: 450 | Chiqim: 247 | Qoldiq: 203]
+• Шиповник чай №15: [Kirim: 450 | Chiqim: 119 | Qoldiq: 331]</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>23142857.81</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>3397</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>20027321.29000001</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>1553</v>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>7260779.430086868</v>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>03401001001000000</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Атир совун</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>• БОРО ПЛЮС Антибактериальное Мыло 100гр в коробке №1(1х1): [Kirim: 288 | Chiqim: 62 | Qoldiq: 226]
+• И01-072-00 Мыло туалетное твердое " ABSOLUT FitoGuard" Белый чай и масло оливы, 90 гр.: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
+• И01-072-00 Мыло туалетное твердое "ABSOLUT 2в1" дикая орхидея, 90 гр.: [Kirim: 12 | Chiqim: 29 | Qoldiq: -17]
+• И01-072-00 Мыло туалетное твердое "ABSOLUT For men" Лемонграсс и мята, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
+• И01-072-00 Мыло туалетное твердое "ABSOLUT" FitoGuard облепиха, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS освежающее, 90 гр.: [Kirim: 18 | Chiqim: 19 | Qoldiq: -1]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS ультразащита, 90 гр.: [Kirim: 12 | Chiqim: 60 | Qoldiq: -48]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard алоэ, 90 гр.: [Kirim: 18 | Chiqim: 9 | Qoldiq: 9]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard ромашка, 90 гр.: [Kirim: 12 | Chiqim: 29 | Qoldiq: -17]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' календула, 90 гр.: [Kirim: 12 | Chiqim: 9 | Qoldiq: 3]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' череда, 90 гр.: [Kirim: 12 | Chiqim: 6 | Qoldiq: 6]
+• И01-072-00 Мыло туалетное твердое 'ABSOLUT' 2в1 нежное, 90 гр.: [Kirim: 24 | Chiqim: 2 | Qoldiq: 22]
+• И01-072-00 Мыло туалетное твердое ABSOLUT грейпфрут и бергамот, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
+• И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Главаптека' (дегтярное), 90 гр.: [Kirim: 440 | Chiqim: 299 | Qoldiq: 141]
+• И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Малышам', 90 гр.: [Kirim: 432 | Chiqim: 355 | Qoldiq: 77]</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1328</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>7707857.159999997</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>884</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>5451071.52</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>444</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>2577024.532409638</v>
+      </c>
+      <c r="L15" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>03005002002000000</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Эластик бинтлар</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>• Бинт эластичный медицинский GT 100мм х 2 метр: [Kirim: 120 | Chiqim: 145 | Qoldiq: -25]
+• Бинт эластичный медицинский GT 100мм х 3 метр: [Kirim: 200 | Chiqim: 186 | Qoldiq: 14]
+• Бинт эластичный медицинский GT 100мм х 4 метр: [Kirim: 60 | Chiqim: 60 | Qoldiq: 0]
+• Бинт эластичный медицинский GT 100мм х 5 метр: [Kirim: 186 | Chiqim: 221 | Qoldiq: -35]
+• Бинт эластичный медицинский GT 100мм х 6 метр: [Kirim: 90 | Chiqim: 105 | Qoldiq: -15]
+• Бинт эластичный медицинский GT 120мм х 2 метр: [Kirim: 120 | Chiqim: 83 | Qoldiq: 37]
+• Бинт эластичный медицинский GT 120мм х 3 метр: [Kirim: 110 | Chiqim: 123 | Qoldiq: -13]
+• Бинт эластичный медицинский GT 120мм х 4 метр: [Kirim: 90 | Chiqim: 73 | Qoldiq: 17]
+• Бинт эластичный медицинский GT 120мм х 5 метр: [Kirim: 90 | Chiqim: 101 | Qoldiq: -11]
+• Бинт эластичный медицинский GT 140мм х 2 метр: [Kirim: 225 | Chiqim: 90 | Qoldiq: 135]
+• Бинт эластичный медицинский GT 140мм х 3 метр: [Kirim: 120 | Chiqim: 24 | Qoldiq: 96]
+• Бинт эластичный медицинский GT 140мм х 4 метр: [Kirim: 100 | Chiqim: 11 | Qoldiq: 89]
+• Бинт эластичный медицинский GT 140мм х 5 метр: [Kirim: 54 | Chiqim: 14 | Qoldiq: 40]
+• Бинт эластичный медицинский GT 80мм х 2 метр: [Kirim: 90 | Chiqim: 71 | Qoldiq: 19]
+• Бинт эластичный медицинский GT 80мм х 3 метр: [Kirim: 135 | Chiqim: 87 | Qoldiq: 48]</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>21765800</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>1394</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>19309464.10000002</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>396</v>
+      </c>
+      <c r="K16" s="13" t="n">
+        <v>4815227.262569833</v>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>03926001020008003</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар CANPOL Babies Клипса-ушлагич сўрғич учун, 0 ой+</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001): [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• Соски из силикона (RBT-309): [Kirim: 336 | Chiqim: 10 | Qoldiq: 326]
+• Соски из силикона (RBT-309) (7.23.034): [Kirim: 0 | Chiqim: 220 | Qoldiq: -220]
+• Соски из силикона (RBT-310): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Соски из силикона (RBT-310) (7.23.035): [Kirim: 0 | Chiqim: 62 | Qoldiq: -62]
+• Соски из силикона MAGEMIOR: [Kirim: 340 | Chiqim: 161 | Qoldiq: 179]
+• Соски из силикона RABITO (RBT-101): [Kirim: 288 | Chiqim: 76 | Qoldiq: 212]
+• Соски из силикона RABITO (RBT-410): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
+• Соски из силикона RABITO (RBT-410) (7.35.001): [Kirim: 0 | Chiqim: 251 | Qoldiq: -251]
+• Соски из силикона Артикул: 7,23,003: [Kirim: 0 | Chiqim: 300 | Qoldiq: -300]
+• Соски из силикона Артикул: 7,23,042: [Kirim: 0 | Chiqim: 182 | Qoldiq: -182]
+• Соски из силикона Артикул: 7.23.003: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
+• Соски из силикона Артикул: 7.23.042: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Соски из силикона Модель:S-23-A. Артикул: 7.23.026 barcode 6928568951760 размер:S (0-6 месяц): [Kirim: 600 | Chiqim: 360 | Qoldiq: 240]</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>2872</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>19155016.68</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>1632</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>15894642.88999999</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>1240</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>8270271.825626741</v>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>03304011005000000</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Қўл учун крем</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК И НОГТЕЙ КОМПЛЕКСНЫЙ, 80 МЛ: [Kirim: 10 | Chiqim: 55 | Qoldiq: -45]
+• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК НОЧНОЙ ВОССТАНАВЛИВАЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 159 | Qoldiq: -149]
+• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК РЕГЕНЕРИРУЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 27 | Qoldiq: -17]
+• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК СМЯГЧАЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
+• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК УВЛАЖНЯЮЩИЙ, 80 МЛ: [Kirim: 20 | Chiqim: 51 | Qoldiq: -31]
+• Крем БАРХАТНЫЕ РУЧКИ защитный для рук, 80 МЛ: [Kirim: 80 | Chiqim: 37 | Qoldiq: 43]
+• Крем БАРХАТНЫЕ РУЧКИ комплексный для рук и ногтей, 80 МЛ: [Kirim: 60 | Chiqim: 11 | Qoldiq: 49]
+• Крем БАРХАТНЫЕ РУЧКИ ночной восстанавливающий для рук, 80 МЛ: [Kirim: 50 | Chiqim: 7 | Qoldiq: 43]
+• Крем БАРХАТНЫЕ РУЧКИ питательный для рук, 80 МЛ: [Kirim: 120 | Chiqim: 65 | Qoldiq: 55]
+• Крем БАРХАТНЫЕ РУЧКИ регенерирующий для рук, 80 МЛ: [Kirim: 70 | Chiqim: 0 | Qoldiq: 70]
+• Крем БАРХАТНЫЕ РУЧКИ смягчающий для рук, 80 МЛ: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
+• Крем БАРХАТНЫЕ РУЧКИ увлажняющий для рук, 80 МЛ: [Kirim: 80 | Chiqim: 23 | Qoldiq: 57]
+• Крем косметический Нежные ручки Козье молоко 125мл: [Kirim: 250 | Chiqim: 161 | Qoldiq: 89]
+• Крем косметический Нежные ручки Питательный 125мл: [Kirim: 250 | Chiqim: 170 | Qoldiq: 80]</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>7599327.12</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>776</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>6842857.200000002</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <v>324</v>
+      </c>
+      <c r="K18" s="13" t="n">
+        <v>2238347.2608</v>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>03401001002000000</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Суюқ совун</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>• ELFIN  JIDKOYE  MILO 300 GR  DOZ: [Kirim: 810 | Chiqim: 0 | Qoldiq: 810]
+• ELFIN  JIDKOYE  MILO 300 GR SOS: [Kirim: 954 | Chiqim: 0 | Qoldiq: 954]
+• ELFIN  JIDKOYE  MILO 500 GR SOS: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
+• ELFIN JIDKOYE MILO 300 GR DOZ: [Kirim: 0 | Chiqim: 2,354 | Qoldiq: -2,354]
+• ELFIN JIDKOYE MILO 300 GR SOS: [Kirim: 0 | Chiqim: 2,318 | Qoldiq: -2,318]
+• ELFIN JIDKOYE MILO 300 GR SOSELFIN JIDKOYE MILO 300 GR SOS: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
+• ELFIN JIDKOYE MILO 500 GR SOS: [Kirim: 0 | Chiqim: 298 | Qoldiq: -298]
+• Elfin  jitki Mila 300 gr soskalik: [Kirim: 360 | Chiqim: 0 | Qoldiq: 360]
+• Elfin jidki mila 300 dozorlik: [Kirim: 1,800 | Chiqim: 441 | Qoldiq: 1,359]
+• Elfin jidki mila 300 gr soskalik: [Kirim: 1,440 | Chiqim: 734 | Qoldiq: 706]
+• HAVEN JIDKOYE MILO  500 GR  kapalak: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Елфин житки мило 300гр SOS: [Kirim: 432 | Chiqim: 131 | Qoldiq: 301]
+• Елфин житки мило 300гр Дазатр: [Kirim: 498 | Chiqim: 308 | Qoldiq: 190]</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>6714</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>18558714.3</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>6588</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>20880178.37000005</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>348286.8635388739</v>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>04014001006000000</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Болалар соскаси бутилка учун</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>• Детские cоски для  бутылочек  (40332MIX): [Kirim: 1,296 | Chiqim: 0 | Qoldiq: 1,296]
+• Детские Соски для бутылочек (40332MIX): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
+• Детские соски для бутылок: [Kirim: 4,600 | Chiqim: 0 | Qoldiq: 4,600]
+• Детские соски для бутылочек: [Kirim: 5,000 | Chiqim: 8,194 | Qoldiq: -3,194]
+• Детские соски для бутылочек (40332): [Kirim: 864 | Chiqim: 2,274 | Qoldiq: -1,410]
+• Соска пустышка Panda c крышкой 106 шт: [Kirim: 1,440 | Chiqim: 0 | Qoldiq: 1,440]
+• Соски пустышки Mummy модель 1111 в одном комплекте 2 шт: [Kirim: 216 | Chiqim: 411 | Qoldiq: -195]
+• Соски пустышки Mummy модель 1112 в одном комплекте 2 шт: [Kirim: 288 | Chiqim: 404 | Qoldiq: -116]
+• Соски пустышки Mummy модель 1114 в одном комплекте 2 шт: [Kirim: 144 | Chiqim: 164 | Qoldiq: -20]
+• Соски пустышки Mummy модель1113 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 337 | Qoldiq: -193]
+• Соски пустышки Mummy модель1115 одном комплекте 2 штук: [Kirim: 216 | Chiqim: 342 | Qoldiq: -126]</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>14640</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>19504999.97</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>12126</v>
+      </c>
+      <c r="I20" s="13" t="n">
+        <v>25891785.63000003</v>
+      </c>
+      <c r="J20" s="14" t="n">
+        <v>2514</v>
+      </c>
+      <c r="K20" s="13" t="n">
+        <v>3349424.175176229</v>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>03924001010000000</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Уй-рўзғор ва маиший эҳтиёжлар учун пластмасса буюмлар (пластмассадан тайёрланган ошхона идиш-товоқлари, приборлар ва ошхона анжомларидан ташқари)</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>• Детские  бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детские бутылки   (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Детские бутылки (358): [Kirim: 0 | Chiqim: 138 | Qoldiq: -138]
+• Детские бутылки (360): [Kirim: 288 | Chiqim: 121 | Qoldiq: 167]
+• Пластмассовый цепочка держатель для  соски( RBT-305): [Kirim: 1,728 | Chiqim: 0 | Qoldiq: 1,728]
+• Пластмассовый цепочка держатель для соски (RBT-129) 7,30,011: [Kirim: 0 | Chiqim: 1,306 | Qoldiq: -1,306]
+• Пластмассовый цепочка держатель для соски (RBT-129) 7.30.011: [Kirim: 1,728 | Chiqim: 0 | Qoldiq: 1,728]
+• Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003: [Kirim: 0 | Chiqim: 329 | Qoldiq: -329]
+• Пластмассовый цепочка держатель для соски (RBT-130) 7.30.003: [Kirim: 1,152 | Chiqim: 0 | Qoldiq: 1,152]
+• Пластмассовый цепочка держатель для соски( RBT-305): [Kirim: 0 | Chiqim: 48 | Qoldiq: -48]
+• Пластмассовый цепочка держатель для соски( RBT-305) (7.30.002): [Kirim: 0 | Chiqim: 1,291 | Qoldiq: -1,291]</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>5328</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>32060828.56</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>3233</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <v>25938660.62000002</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>2095</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>12606500.71944444</v>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>10306002005000000</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Услуги по электронному документообороту.</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>• Услуги по организации юридически значимого документооборота между организациями (Didox) за август 2026г.: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за апрель 2026г.: [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за декабрь 2025г.: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за июль 2026г.: [Kirim: 171 | Chiqim: 0 | Qoldiq: 171]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за июнь 2026г.: [Kirim: 149 | Chiqim: 0 | Qoldiq: 149]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за май 2026г.: [Kirim: 148 | Chiqim: 0 | Qoldiq: 148]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за март 2026г.: [Kirim: 157 | Chiqim: 0 | Qoldiq: 157]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за ноябрь 2025г.: [Kirim: 42 | Chiqim: 0 | Qoldiq: 42]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за февраль 2026г.: [Kirim: 119 | Chiqim: 0 | Qoldiq: 119]
+• Услуги по организации юридически значимого документооборота между организациями (Didox) за январь 2026г.: [Kirim: 68 | Chiqim: 0 | Qoldiq: 68]</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1174</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>632000</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>1174</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>632000</v>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>03924001002000000</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Пластик ошхона идишлари, приборлар ва ошхона анжомлари</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>• Детская бутылка пластмассовый  (ALGO 7.17.018) 125ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детская бутылка пластмассовый  (RBT-705)  160ml: [Kirim: 347 | Chiqim: 0 | Qoldiq: 347]
+• Детская бутылка пластмассовый (ALGO 7,17,018) 125ml: [Kirim: 0 | Chiqim: 105 | Qoldiq: -105]
+• Детская бутылка пластмассовый (RBT-705) 160ml: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
+• Детская бутылка пластмассовый (RBT-705) 160ml (7.17.028): [Kirim: 0 | Chiqim: 242 | Qoldiq: -242]
+• Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621): [Kirim: 480 | Chiqim: 10 | Qoldiq: 470]
+• Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621) (7.17.035): [Kirim: 0 | Chiqim: 566 | Qoldiq: -566]
+• Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1019</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>16434080.56</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>939</v>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>20854553.61999999</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>1290212.40902846</v>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>03307001002000000</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Гигиеник салфеткалар (нам ва қурутувчи )</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>• Влажные салфетки (120 штук): [Kirim: 2,640 | Chiqim: 2,640 | Qoldiq: 0]
+• Влажные салфетки (15 штук): [Kirim: 6,480 | Chiqim: 5,256 | Qoldiq: 1,224]
+• Влажные салфетки (72 штук): [Kirim: 3,120 | Chiqim: 2,996 | Qoldiq: 124]
+• Влажные салфетки «Aqua Touch»: [Kirim: 12 | Chiqim: 2 | Qoldiq: 10]
+• Салфетка влажный   120 шт: [Kirim: 1,076 | Chiqim: 0 | Qoldiq: 1,076]
+• Салфетка влажный   72 шт: [Kirim: 1,104 | Chiqim: 0 | Qoldiq: 1,104]
+• Салфетка влажный 120 шт: [Kirim: 0 | Chiqim: 1,039 | Qoldiq: -1,039]
+• Салфетка влажный 72 шт: [Kirim: 0 | Chiqim: 1,104 | Qoldiq: -1,104]</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>14432</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>38049571.44</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>13037</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>44391696.68999996</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>1395</v>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>3677879.168431263</v>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>03304011006000000</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Бадан учун крем</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>• БОРО ПЛЮС БЕЗ ЗАПАХА Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
+• БОРО ПЛЮС Крем для ног интенсивного действия 50мл туба №1(1х1): [Kirim: 144 | Chiqim: 144 | Qoldiq: 0]
+• БОРО ПЛЮС РЕГУЛЯРНЫЙ Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
+• БОРО ПЛЮС ТРАВЯНОЙ Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
+• Крем детский  под подгузник" PAPPY PAMPER" 45мл: [Kirim: 150 | Chiqim: 0 | Qoldiq: 150]
+• Крем детский  под подгузник" PAPPY PAMPER" 80мл: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
+• Крем детский под подгузник" PAPPY PAMPER" 45мл: [Kirim: 0 | Chiqim: 62 | Qoldiq: -62]
+• Крем детский под подгузник" PAPPY PAMPER" 80мл: [Kirim: 0 | Chiqim: 111 | Qoldiq: -111]</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1984</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>17009462.64</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>1757</v>
+      </c>
+      <c r="I25" s="13" t="n">
+        <v>19559642.86</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>227</v>
+      </c>
+      <c r="K25" s="13" t="n">
+        <v>1946143.154879032</v>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>03305005001431004</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Шампунь (барча турлари) Антипедикулёзный Шампунь, картон қутида, ПЭТ бутилка 110 г.</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>• Шампунь "PEPILINO"  265мл  Бегемотик Гоша: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• Шампунь "PEPILINO"  265мл  Дельфинчик Вилли: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• Шампунь "PEPILINO"  265мл  Зайка степашка: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• Шампунь "PEPILINO"  265мл  Медвежонок Пух: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
+• Шампунь "PEPILINO" 265мл Бегемотик Гоша: [Kirim: 0 | Chiqim: 28 | Qoldiq: -28]
+• Шампунь "PEPILINO" 265мл Дельфинчик Вилли: [Kirim: 0 | Chiqim: 100 | Qoldiq: -100]
+• Шампунь "PEPILINO" 265мл Зайка степашка: [Kirim: 0 | Chiqim: 14 | Qoldiq: -14]
+• Шампунь "PEPILINO" 265мл Медвежонок Пух: [Kirim: 0 | Chiqim: 38 | Qoldiq: -38]</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1339285.7</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>1526785.71</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>133928.57</v>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>03304021006000000</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Масло косметическое</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>• Teddy Болалар ёғи (Алоэ) 100 мл: [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]
+• Teddy Болалар ёғи (Гипоаллерген) 100 мл: [Kirim: 72 | Chiqim: 68 | Qoldiq: 4]
+• Teddy Болалар ёғи (Лаванда) 100 мл: [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]
+• Teddy Болалар ёғи (Ромашка) 100 мл: [Kirim: 72 | Chiqim: 66 | Qoldiq: 6]
+• Детская масло SHOFF 100gr: [Kirim: 1,584 | Chiqim: 1,270 | Qoldiq: 314]
+• Детская масло SHOFF 50gr: [Kirim: 1,536 | Chiqim: 1,195 | Qoldiq: 341]
+• Косметические изделия в ассортименте: [Kirim: 0 | Chiqim: 7,673,540 | Qoldiq: -7,673,540]
+• Парфюмерно-косметические: [Kirim: 0 | Chiqim: 10,483,200 | Qoldiq: -10,483,200]</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>3408</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>24395574.86</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>18159483</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>25332589.18000002</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <v>-18156075</v>
+      </c>
+      <c r="K27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>07010001004000000</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Шиша (бутилка)</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Артикул:7.17.032: [Kirim: 480 | Chiqim: 0 | Qoldiq: 480]
+• Детские бутылки стеклянные 240 ml. Бренд: ALGO. Артикул:7.17.031: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Детские бутылки стеклянные 60 ml. Бренд: Rabito. Model:  Артикул:7.17.023: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детские бутылки стеклянные из безцвет стекла 150ml (7.17.043): [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Детские бутылки стеклянные из безцвет стекла 240ml (7.17.044): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детские бутылки стеклянные из безцвет стекла 240ml (RBT-207) (7,17,044): [Kirim: 0 | Chiqim: 169 | Qoldiq: -169]
+• №1 Детские бутылки стеклянные 240 ml. Бренд: Rabito. Артикул:7.17.035: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>21490337.15</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>4828571.439999999</v>
+      </c>
+      <c r="J28" s="14" t="n">
+        <v>1079</v>
+      </c>
+      <c r="K28" s="13" t="n">
+        <v>18580187.32760417</v>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>03926001020000000</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>• Держатель для сосок (JK BABY модел с колокльчика ): [Kirim: 120 | Chiqim: 504 | Qoldiq: -384]
+• Держатель для сосок (JM BABY простой): [Kirim: 384 | Chiqim: 0 | Qoldiq: 384]
+• Детские бутылки (А-2 ) 260 мл: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• Детские бутылки (А-3-Т 125 мл): [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
+• Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003: [Kirim: 0 | Chiqim: 132 | Qoldiq: -132]
+• Соски из силикона (RBT-310): [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
+• Соски из силикона (RBT-310) (7.23.035): [Kirim: 0 | Chiqim: 98 | Qoldiq: -98]</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>504</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>3240000</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>756</v>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>6613749.949999998</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>-252</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>09603002002000000</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Тиш чўткаси</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>• зубная щетка № 11B: [Kirim: 360 | Chiqim: 360 | Qoldiq: 0]
+• зубная щетка № 14А: [Kirim: 1,728 | Chiqim: 1,152 | Qoldiq: 576]
+• зубная щетка № 2F: [Kirim: 720 | Chiqim: 480 | Qoldiq: 240]
+• зубная щетка № 4F: [Kirim: 720 | Chiqim: 624 | Qoldiq: 96]
+• зубная щетка № 5Д: [Kirim: 576 | Chiqim: 576 | Qoldiq: 0]
+• зубная щетка № 8Д: [Kirim: 1,344 | Chiqim: 636 | Qoldiq: 708]</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>5448</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>12528214.27</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>3828</v>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>11546785.27000004</v>
+      </c>
+      <c r="J30" s="14" t="n">
+        <v>1620</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>3725350.058259912</v>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>03926999004000000</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Молокоотсос (ПВХ)</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>• Молокоотос Mummy модель 1134: [Kirim: 840 | Chiqim: 786 | Qoldiq: 54]
+• Молокоотсос  (А1357): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
+• Молокоотсос (A1357): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
+• Молокоотсос (А-240): [Kirim: 192 | Chiqim: 192 | Qoldiq: 0]
+• Молокоотсос (А1357): [Kirim: 432 | Chiqim: 720 | Qoldiq: -288]
+• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>2136</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>25432285.73</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I31" s="13" t="n">
+        <v>19609821.48999999</v>
+      </c>
+      <c r="J31" s="14" t="n">
+        <v>438</v>
+      </c>
+      <c r="K31" s="13" t="n">
+        <v>5215047.35474719</v>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>06602001001000001</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Ҳассалар, ўриндиқ ҳассалар ва бошқа шунга ўхшаш буюмлар хасса</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>• Хасса (трость) 4х опорная №1 Серия - 1, Срок годности 01/2030: [Kirim: 50 | Chiqim: 50 | Qoldiq: 0]
+• Хасса (трость) деревянная №1 Серия - 1, Срок годности 01/2030: [Kirim: 162 | Chiqim: 162 | Qoldiq: 0]
+• Хасса (трость) подлокотная №1 Серия - 1, Срок годности 01/2030: [Kirim: 90 | Chiqim: 90 | Qoldiq: 0]
+• Хасса (трость) регулируемая №1  Серия - 1, Срок годности 01/2030: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
+• Хасса (трость) регулируемая №1 Цвет Серый Китай: [Kirim: 175 | Chiqim: 204 | Qoldiq: -29]
+• Хасса (трость) регулируемая №1 Цвет Черный Китай: [Kirim: 155 | Chiqim: 131 | Qoldiq: 24]</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>642</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>24056000</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>637</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>29271000</v>
+      </c>
+      <c r="J32" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" s="13" t="n">
+        <v>187352.0249221183</v>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>09619001002000000</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Аёллар учун санитария тампонлари</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>• deasy: [Kirim: 4,000 | Chiqim: 1,396 | Qoldiq: 2,604]
+• mira: [Kirim: 4,000 | Chiqim: 1,700 | Qoldiq: 2,300]
+• Женские прокладки (онажон): [Kirim: 15,000 | Chiqim: 13,380 | Qoldiq: 1,620]
+• Женские прокладки (роза): [Kirim: 7,500 | Chiqim: 8,540 | Qoldiq: -1,040]
+• Тампоны женские гиг. «LINDA» картонный упаковка №10: [Kirim: 4,500 | Chiqim: 3,320 | Qoldiq: 1,180]</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>51525000</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>28336</v>
+      </c>
+      <c r="I33" s="13" t="n">
+        <v>40508928.26000006</v>
+      </c>
+      <c r="J33" s="14" t="n">
+        <v>6664</v>
+      </c>
+      <c r="K33" s="13" t="n">
+        <v>9810360</v>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>09619001001000000</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Аёллар учун санитария ёстиқчалари (шу жумладан эркаклар учун)</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>• Вкладыши для груди RABITO (Артикул 7.31.005): [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
+• Гигиенические женские прокладки LIBRESSE Maxi Night wing sw 6x20pcs: [Kirim: 4 | Chiqim: 4 | Qoldiq: 0]
+• Гигиенические прокладки "Amelie": [Kirim: 2,000 | Chiqim: 0 | Qoldiq: 2,000]
+• Гигиенические прокладки "Дива": [Kirim: 1,500 | Chiqim: 0 | Qoldiq: 1,500]
+• Женские гигиенические прокладки дива мама: [Kirim: 4,500 | Chiqim: 3,486 | Qoldiq: 1,014]</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>8244</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>47020571.44</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>3490</v>
+      </c>
+      <c r="I34" s="13" t="n">
+        <v>31253571.29000003</v>
+      </c>
+      <c r="J34" s="14" t="n">
+        <v>4754</v>
+      </c>
+      <c r="K34" s="13" t="n">
+        <v>27114968.05261523</v>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>04014001003000000</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Презервативлар</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>• Презервативы из натурального латекса торговой марки "Lovit" (ANATOMIC): [Kirim: 1,184 | Chiqim: 0 | Qoldiq: 1,184]
+• Презервативы из натурального латекса торговой марки "Lovit" (Classic): [Kirim: 1,000 | Chiqim: 401 | Qoldiq: 599]
+• Презервативы из натурального латекса торговой марки "Lovit" (DOTTED): [Kirim: 1,000 | Chiqim: 679 | Qoldiq: 321]
+• Презервативы из натурального латекса торговой марки "Lovit" (RIBBED): [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
+• Презервативы из натурального латекса торговой марки "Lovit" (ULTRA THIN): [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>5184</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>9534857.129999999</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I35" s="13" t="n">
+        <v>3434598.25</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>4104</v>
+      </c>
+      <c r="K35" s="13" t="n">
+        <v>7548428.561249999</v>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180009</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Classic Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (апельсин): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
+• Аскорбинка 3,0 №10 (классик): [Kirim: 1,300 | Chiqim: 380 | Qoldiq: 920]
+• Аскорбинка 3,0 №10 (малина): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
+• Аскорбинка 3,0 №10 (смородина): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
+• Аскорбинка 3,0 №10 (яблоко): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>460</v>
+      </c>
+      <c r="I36" s="13" t="n">
+        <v>626785.7799999999</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>840</v>
+      </c>
+      <c r="K36" s="13" t="n">
+        <v>924000</v>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>02712001002000000</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Косметика вазелини</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>• Вазелин косметический 100гр: [Kirim: 3,600 | Chiqim: 6,426 | Qoldiq: -2,826]
+• Вазелин косметический 100гр в баночках: [Kirim: 2,880 | Chiqim: 6 | Qoldiq: 2,874]
+• Вазелин косметический 20гр: [Kirim: 2,000 | Chiqim: 3,000 | Qoldiq: -1,000]
+• Вазелин косметический 20гр в тубах: [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
+• Вазелин косметический 40гр: [Kirim: 1,000 | Chiqim: 689 | Qoldiq: 311]</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>10480</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>37833928.57</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>10121</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>44842410.70000003</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>359</v>
+      </c>
+      <c r="K37" s="13" t="n">
+        <v>1296028.659983779</v>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>04014001005000000</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Резинадан бурун тозалагич</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>• Аспиратор (носочиска) MUMMY 1130-1 шт: [Kirim: 1,020 | Chiqim: 9 | Qoldiq: 1,011]
+• Аспиратор (носочиска) MUMMY 1130-1 шт -: [Kirim: 300 | Chiqim: 1,247 | Qoldiq: -947]
+• Аспиратор (носочиска) MUMMY 1130-1 шт -2025: [Kirim: 120 | Chiqim: 2 | Qoldiq: 118]
+• Аспиратор (носочиска) MUMMY 1133 шт: [Kirim: 120 | Chiqim: 2,359 | Qoldiq: -2,239]
+• Носочистка  "MUMMY" модель 1133: [Kirim: 2,160 | Chiqim: 0 | Qoldiq: 2,160]</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>21428571.45</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>3617</v>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>29355357.24999998</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="K38" s="13" t="n">
+        <v>593317.9729435483</v>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>03307001038000000</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Ванна қабул қилиш учун восита</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>• Teddy Болалар упаси (Лаванда) 50 гр: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
+• Teddy Чўмилиш тузи (Лаванда) 500 гр: [Kirim: 32 | Chiqim: 15 | Qoldiq: 17]
+• Teddy Чўмилиш тузи (Ромашка) 500 гр: [Kirim: 32 | Chiqim: 21 | Qoldiq: 11]
+• Teddy Чўмилиш тузи (Хвоя) 500 гр: [Kirim: 32 | Chiqim: 15 | Qoldiq: 17]
+• Teddy Чўмилиш тузи (Череда) 500 гр: [Kirim: 32 | Chiqim: 18 | Qoldiq: 14]</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>793600</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>550714.28</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="K39" s="13" t="n">
+        <v>291400</v>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>06214001014000000</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Тиббий эластик тасма</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>• (01942-2)Пояс медицинский эластичный, согревающий, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• (01942-3)Пояс медицинский эластичный, согревающий, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Пояс медицинский эластичный, согревающий, Размер 2: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]
+• Пояс медицинский эластичный, согревающий, Размер 3: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]
+• Пояс медицинский эластичный, согревающий, Размер 4: [Kirim: 20 | Chiqim: 12 | Qoldiq: 8]</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>1552500.050000001</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K40" s="13" t="n">
+        <v>594000</v>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>03004900002002000</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>D-Пантенол, гидролизат, магния хлорид, ниацинамид, пиридоксин, рибофлавин, сульфат цинка, хлорид марганца - A11A</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>• Жидкий пластырь 100 мл С экстрактом подорожника в коробочке: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• Жидкий пластырь 50мл в коробочке: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
+• Пантенол взрослый 130мл в коробочке: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
+• Пантенол детский 130мл в коробочке: [Kirim: 24 | Chiqim: 0 | Qoldiq: 24]</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>9360000.010000002</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="14" t="n">
+        <v>264</v>
+      </c>
+      <c r="K41" s="13" t="n">
+        <v>9360000.010000002</v>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>07020999004000000</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Болалар шишали бутилка</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>• Детские бутылки стеклянные (В1376): [Kirim: 144 | Chiqim: 144 | Qoldiq: 0]
+• Детские бутылки стеклянные (В1377): [Kirim: 96 | Chiqim: 94 | Qoldiq: 2]
+• Детские бутылки стеклянные (В1377)): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
+• Детские бутылки стеклянные (В1378): [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>312</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>5297142.859999999</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>312</v>
+      </c>
+      <c r="I42" s="13" t="n">
+        <v>6428571.450000001</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>03304999024000000</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Маникюр ва педикюр учун косметика маҳсулотлари</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>• Маникюрный  набор (С-11): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Маникюрный набор  (FZ-47): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
+• Маникюрный набор (FZ-47): [Kirim: 0 | Chiqim: 53 | Qoldiq: -53]
+• Маникюрный набор (С-11): [Kirim: 0 | Chiqim: 115 | Qoldiq: -115]</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>2455714.28</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>3450000.020000001</v>
+      </c>
+      <c r="J43" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>04014001004000000</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Резинали кўкрак помпаси</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>• Грудная накладка  MUMMY - 1132 -шт: [Kirim: 624 | Chiqim: 0 | Qoldiq: 624]
+• Грудная накладка  MUMMY - 1132 -шт  04.2025: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Грудная накладка MUMMY - 1132: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
+• Грудная накладка MUMMY - 1132 -шт: [Kirim: 0 | Chiqim: 1,065 | Qoldiq: -1,065]</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>912</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>3257142.830000001</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>1065</v>
+      </c>
+      <c r="I44" s="13" t="n">
+        <v>4834821.41</v>
+      </c>
+      <c r="J44" s="15" t="n">
+        <v>-153</v>
+      </c>
+      <c r="K44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>05601001002000000</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Пахтали таёқча</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>• ПТ MG Cotton п.п. квадрат 100д: [Kirim: 1,875 | Chiqim: 1,545 | Qoldiq: 330]
+• ПТ MG Cotton п.п. квадрат 200д: [Kirim: 1,154 | Chiqim: 763 | Qoldiq: 391]
+• №1 Ватные палочки для ушей (ухочистка) BRICK 55: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>3069</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>14379464.29</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>2308</v>
+      </c>
+      <c r="I45" s="13" t="n">
+        <v>11636428.72999998</v>
+      </c>
+      <c r="J45" s="14" t="n">
+        <v>761</v>
+      </c>
+      <c r="K45" s="13" t="n">
+        <v>3565582.380153144</v>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>03305005001000000</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Шампунь (барча турлари)</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>• Шампунь "Антипедикулезный"110мл (комплект): [Kirim: 150 | Chiqim: 120 | Qoldiq: 30]
+• Шампунь "Антипедикулезный"130мл комплект: [Kirim: 150 | Chiqim: 94 | Qoldiq: 56]
+• Шампунь "Антипедикулезный"60мл (комплект): [Kirim: 300 | Chiqim: 179 | Qoldiq: 121]</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>393</v>
+      </c>
+      <c r="I46" s="13" t="n">
+        <v>2579553.519999999</v>
+      </c>
+      <c r="J46" s="14" t="n">
+        <v>207</v>
+      </c>
+      <c r="K46" s="13" t="n">
+        <v>1164375</v>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>10701001001000000</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Bino va inshootlar ijaraga berish xizmati</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>• Ijara to'lovi DEKABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]
+• Ijara to'lovi NOYABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]
+• Ijara to'lovi OKTABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>1071428.58</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="13" t="n">
+        <v>1071428.58</v>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>03005001002001001</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 1м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>• Марля медицинская отбеленная в кусках, 1 м: [Kirim: 500 | Chiqim: 10 | Qoldiq: 490]
+• Марля медицинская отбеленная в кусках, 1 м х 84 см: [Kirim: 0 | Chiqim: 450 | Qoldiq: -450]
+• Марля медицинская отбеленная в кусках, 2 м: [Kirim: 0 | Chiqim: 50 | Qoldiq: -50]</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>510</v>
+      </c>
+      <c r="I48" s="13" t="n">
+        <v>1095535.74</v>
+      </c>
+      <c r="J48" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180016</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза малина таъми билан</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №5 (апельсин): [Kirim: 0 | Chiqim: 400 | Qoldiq: -400]
+• Аскорбинка 3,0 №5 (малина): [Kirim: 1,600 | Chiqim: 1,000 | Qoldiq: 600]
+• Аскорбинка 3,0 №5 (яблоко): [Kirim: 0 | Chiqim: 400 | Qoldiq: -400]</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>960000</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I49" s="13" t="n">
+        <v>1046428.59</v>
+      </c>
+      <c r="J49" s="15" t="n">
+        <v>-200</v>
+      </c>
+      <c r="K49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>08414002002000000</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Ҳаво ёки вакуум насослари, компрессорлар, қурилиш соҳасида ишлатилмайдиган</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>• Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803: [Kirim: 240 | Chiqim: 304 | Qoldiq: -64]
+• №1 Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803: [Kirim: 800 | Chiqim: 0 | Qoldiq: 800]</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>94800000</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>304</v>
+      </c>
+      <c r="I50" s="13" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="J50" s="14" t="n">
+        <v>736</v>
+      </c>
+      <c r="K50" s="13" t="n">
+        <v>67089230.76923077</v>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>03926999438000000</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Бурун бўшлиғини ювиш учун мослама</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>• Аспиратор (носочиска) MUMMY1133: [Kirim: 180 | Chiqim: 0 | Qoldiq: 180]
+• Носочистка HELLO: [Kirim: 192 | Chiqim: 23 | Qoldiq: 169]</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I51" s="13" t="n">
+        <v>821428.5800000001</v>
+      </c>
+      <c r="J51" s="14" t="n">
+        <v>349</v>
+      </c>
+      <c r="K51" s="13" t="n">
+        <v>5066129.032258064</v>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>07013004008000000</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Шиша бутилкача</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>• Детские бутылки Стеклянные (В1377): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
+• Детские бутылки Стеклянные (В1378): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>336</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>6274285.72</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>336</v>
+      </c>
+      <c r="K52" s="13" t="n">
+        <v>6274285.72</v>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>03926001155000000</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Спринцовка (ПВХ)</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
+• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001): [Kirim: 0 | Chiqim: 222 | Qoldiq: -222]</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>9521781.43</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>222</v>
+      </c>
+      <c r="I53" s="13" t="n">
+        <v>11892857.18</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="K53" s="13" t="n">
+        <v>714133.6072499999</v>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>08414002001000000</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Ҳаво ёки вакуум насослари, компрессорлар (барча турлари)</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>• Молокоотсос вакуумный электический  (RH-803): [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
+• Молокоотсос вакуумный электический (RH-803): [Kirim: 0 | Chiqim: 200 | Qoldiq: -200]</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>25714285.71</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I54" s="13" t="n">
+        <v>29464285.72</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>03304011011004003</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Юз ва танани юмшатувчи, 75 мл</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>• Крем увлажняющий для лица и тела "Нежный",: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
+• Крем увлажняющий для лица и тела "Нежный", 75 ml: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>392857.14</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" s="13" t="n">
+        <v>463571.43</v>
+      </c>
+      <c r="J55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>03304011011000000</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>• Крем детский 50мл: [Kirim: 4,000 | Chiqim: 2,510 | Qoldiq: 1,490]</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>4107142.86</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>2510</v>
+      </c>
+      <c r="I56" s="13" t="n">
+        <v>3361607.11</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>1490</v>
+      </c>
+      <c r="K56" s="13" t="n">
+        <v>1529910.71535</v>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>04803001001000000</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Қоғоз салфетка</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>• полотенца рулонные: [Kirim: 8,400 | Chiqim: 7,236 | Qoldiq: 1,164]</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>8400</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>7236</v>
+      </c>
+      <c r="I57" s="13" t="n">
+        <v>41981250.05999999</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>1164</v>
+      </c>
+      <c r="K57" s="13" t="n">
+        <v>5196428.571428572</v>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180012</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (апельсин): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>360</v>
+      </c>
+      <c r="I58" s="13" t="n">
+        <v>510714.33</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>940</v>
+      </c>
+      <c r="K58" s="13" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180001</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (яблоко): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>360</v>
+      </c>
+      <c r="I59" s="13" t="n">
+        <v>510714.33</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>940</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180005</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (смородина): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>360</v>
+      </c>
+      <c r="I60" s="13" t="n">
+        <v>510714.33</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>940</v>
+      </c>
+      <c r="K60" s="13" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180014</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (малина): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>360</v>
+      </c>
+      <c r="I61" s="13" t="n">
+        <v>510714.33</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>940</v>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>1034000</v>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180003</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза олма таъми билан</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №5 (яблоко): [Kirim: 1,600 | Chiqim: 800 | Qoldiq: 800]</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>960000</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="I62" s="13" t="n">
+        <v>463392.8699999999</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>480000</v>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180011</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза апельсин таъми билан</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №5 (апельсин): [Kirim: 1,600 | Chiqim: 800 | Qoldiq: 800]</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>960000</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>800</v>
+      </c>
+      <c r="I63" s="13" t="n">
+        <v>463392.8699999999</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>480000</v>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180007</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза Қорағат таъми билан</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №5 (смородина): [Kirim: 1,000 | Chiqim: 400 | Qoldiq: 600]</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>600000</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="I64" s="13" t="n">
+        <v>232142.8699999999</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>360000</v>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>04015001004000000</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Жаррохлик қўлқопи</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>• Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5: [Kirim: 4,000 | Chiqim: 3,450 | Qoldiq: 550]</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>3450</v>
+      </c>
+      <c r="I65" s="13" t="n">
+        <v>7700892.890000002</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>550</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>1031250</v>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>01806001007000000</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>Шоколадли тўпламлар</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>• Chokovita N°60: [Kirim: 1,300 | Chiqim: 776 | Qoldiq: 524]</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>48450000</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>776</v>
+      </c>
+      <c r="I66" s="13" t="n">
+        <v>34642857.18999999</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>524</v>
+      </c>
+      <c r="K66" s="13" t="n">
+        <v>19529076.92307692</v>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>02106999028180023</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>Биологически активные добавки к пище NARPAY VITA ZONE Vanilla Таблетки аскорбиновой кислоты с глюкозой</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>• Аскорбинка 3,0 №10 (ваниль): [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>550000</v>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>03005001002001002</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 2 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>• Марля медицинская отбеленная в кусках, 2 м: [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="K68" s="13" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>03005001002001003</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 3 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>• Марля медицинская отбеленная в кусках, 3 м: [Kirim: 400 | Chiqim: 0 | Qoldiq: 400]</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>02106999028199012</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NUROMON MED Мойчечак гуллари кукунда</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>• Ромашка чай №15: [Kirim: 450 | Chiqim: 269 | Qoldiq: 181]</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>883930.5</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>269</v>
+      </c>
+      <c r="I70" s="13" t="n">
+        <v>960714.3300000002</v>
+      </c>
+      <c r="J70" s="14" t="n">
+        <v>181</v>
+      </c>
+      <c r="K70" s="13" t="n">
+        <v>355536.49</v>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>04016001027000000</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Металл қўллаб-қувватлаш оёқ учун резина қистирма</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>• Наконечник 19мм №1 Китай: [Kirim: 400 | Chiqim: 290 | Qoldiq: 110]</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>1428580</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>290</v>
+      </c>
+      <c r="I71" s="13" t="n">
+        <v>1346428.56</v>
+      </c>
+      <c r="J71" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="K71" s="13" t="n">
+        <v>392859.5</v>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>03306001003000000</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Тиш ипи</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>• Зубная нить (616): [Kirim: 108 | Chiqim: 0 | Qoldiq: 108]</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>1253571.43</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="K72" s="13" t="n">
+        <v>1253571.43</v>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>03005001002001004</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 5 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>• Марля медицинская отбеленная в кусках, 5 м: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K73" s="13" t="n">
+        <v>850000</v>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>02007002003000000</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Мармелад</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>• Vita Buum life: [Kirim: 720 | Chiqim: 638 | Qoldiq: 82]</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>28944000</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>638</v>
+      </c>
+      <c r="I74" s="13" t="n">
+        <v>28482142.90999999</v>
+      </c>
+      <c r="J74" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="K74" s="13" t="n">
+        <v>3296400</v>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>01509001001000000</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Зайтун мойи (тозаланган ёки тозаланмаган)</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>• Масло оливковое очищенное EXTRA VIRGIN OLIVE OIL 12x250ML TM Marioliva: [Kirim: 240 | Chiqim: 197 | Qoldiq: 43]</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>6215357.140000001</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>197</v>
+      </c>
+      <c r="I75" s="13" t="n">
+        <v>7387500</v>
+      </c>
+      <c r="J75" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="K75" s="13" t="n">
+        <v>1113584.820916667</v>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>03402004012000000</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Юза-фаол органик моддалар (совундан ташқари), бошқалар</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>• "Nihol" 250 гр.: [Kirim: 50 | Chiqim: 23 | Qoldiq: 27]</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G76" s="13" t="n">
+        <v>2410714.29</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I76" s="13" t="n">
+        <v>1396428.63</v>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="K76" s="13" t="n">
+        <v>1301785.7166</v>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>08213001002000000</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Қайчи (барча турдаги ва фойдаланиш мақсадлари учун)</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>• Маникюрний набор BABY CARE KIT: [Kirim: 144 | Chiqim: 120 | Qoldiq: 24]</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>2468571.42</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="I77" s="13" t="n">
+        <v>2464285.73</v>
+      </c>
+      <c r="J77" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K77" s="13" t="n">
+        <v>411428.5699999999</v>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>03401001005009001</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>Болалар совуни Bubchen мойчечак билан, 125 гр.</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>• Детское мыло,125 г: [Kirim: 24 | Chiqim: 12 | Qoldiq: 12]</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="G78" s="13" t="n">
+        <v>621428.5699999999</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I78" s="13" t="n">
+        <v>367500</v>
+      </c>
+      <c r="J78" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K78" s="13" t="n">
+        <v>310714.285</v>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>03005001003000000</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>Бинт</t>
+        </is>
+      </c>
+      <c r="D79" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>• Бинт тканный нестерильный GT 7m x 14cm: [Kirim: 2,700 | Chiqim: 2,692 | Qoldiq: 8]</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>6277500</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>2692</v>
+      </c>
+      <c r="I79" s="13" t="n">
+        <v>7210714.259999998</v>
+      </c>
+      <c r="J79" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K79" s="13" t="n">
+        <v>18600</v>
+      </c>
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>03304011011004016</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN майин парвариш 0+, таглик остидан, 150 мл</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>• Крем для младенцев,150 мл: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G80" s="13" t="n">
+        <v>1267857.14</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I80" s="13" t="n">
+        <v>964553.58</v>
+      </c>
+      <c r="J80" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" s="13" t="n">
+        <v>443749.999</v>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>03304011014002001</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун молочко  Bubchen болалар учун каритэ ва кунгабоқар ёғи билан, ПЭТ флакон 200 мл.</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>• Молочко,200 мл: [Kirim: 16 | Chiqim: 11 | Qoldiq: 5]</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>814285.71</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I81" s="13" t="n">
+        <v>660982.1499999999</v>
+      </c>
+      <c r="J81" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="13" t="n">
+        <v>254464.284375</v>
+      </c>
+      <c r="L81" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>03401002001004009</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Юз ювиш учун геллар BÜBCHEN чўмилиш учун, 200 мл</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>• Средство для купания младенцев,200 мл: [Kirim: 8 | Chiqim: 4 | Qoldiq: 4]</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>392857.14</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I82" s="13" t="n">
+        <v>231785.72</v>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" s="13" t="n">
+        <v>196428.57</v>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>03305005002018007</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Болалар шампуни BUBCHEN таъсирчан тери учун, ПЭТ бутилка 200 мл.</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>• Детский шампунь, 200 мл: [Kirim: 16 | Chiqim: 12 | Qoldiq: 4]</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I83" s="13" t="n">
+        <v>695357.16</v>
+      </c>
+      <c r="J83" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="13" t="n">
+        <v>196428.5725</v>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>03401002001004004</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Юз ювиш учун геллар BÜBCHEN 400 мл</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>• Гель для купания, 400 мл: [Kirim: 8 | Chiqim: 4 | Qoldiq: 4]</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" s="13" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I84" s="13" t="n">
+        <v>459642.86</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" s="13" t="n">
+        <v>392857.145</v>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>03306001002000000</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Ополаскиватель для рта</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>• ЛЕСНОЙ БАЛЬЗАМ ОПОЛАСКИВАТЕЛЬ ДЛЯ ДЕСЕН КОРА ДУБА ПИХТА ОТВАРЕ ТРАВ, 400 мл: [Kirim: 2 | Chiqim: 0 | Qoldiq: 2]</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>53928.57</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="13" t="n">
+        <v>53928.57</v>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>03304011011004005</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Косметик, 75мл</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>• Детский косметический крем,75 мл: [Kirim: 12 | Chiqim: 11 | Qoldiq: 1]</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>546428.5699999999</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I86" s="13" t="n">
+        <v>591250</v>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" s="13" t="n">
+        <v>45535.71416666666</v>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>09605002003000000</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Саёҳат тўпламлари (шахсий гигиена, кийим ёки пойабзал учун)</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>• №1 Гигиенический набор для малышей RBT-409: [Kirim: 176 | Chiqim: 176 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>2452107.43</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>176</v>
+      </c>
+      <c r="I87" s="13" t="n">
+        <v>3614285.72</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>03305005002000000</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Болалар шампуни</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>• Шампунь и средство для купания младенцев, 400 мл/ Bad &amp; Shampoo, 400ml: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I88" s="13" t="n">
+        <v>919285.72</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>03304001003000000</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>Бадан учун балзам</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>• Солнцезащитный крем для лица младенцев и детей с чувствительной кожей ФЗ 50+ 50 мл/Sensitive Gesich: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>571428.5699999999</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I89" s="13" t="n">
+        <v>668571.4399999999</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>03305005002018008</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Болалар шампуни BUBCHEN майин парвариш, ПЭТ бутилка 400 мл.</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>• Детский шампунь, 400 мл: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>657142.86</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I90" s="13" t="n">
+        <v>769285.72</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>03304011011004006</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Чақалоқлар учун мой, 200мл</t>
+        </is>
+      </c>
+      <c r="D91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>• Масло для младенцев, 200 мл: [Kirim: 16 | Chiqim: 16 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>857142.86</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I91" s="13" t="n">
+        <v>1011428.56</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>04015001002000000</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Тиббиёт қўлқоплари</t>
+        </is>
+      </c>
+      <c r="D92" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>• Перчатки Медицинские, Нитриловые Чёрного Цвета, Нестерильные для Однократного Применения LDH Glove, Размер:L: [Kirim: 2,000 | Chiqim: 2,000 | Qoldiq: 0]</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>625000</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I92" s="13" t="n">
+        <v>714285.7200000002</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>0 (Tugagan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>04421001010000000</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Тиш кавлагич</t>
+        </is>
+      </c>
+      <c r="D93" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>• Зубная нить (616): [Kirim: 60 | Chiqim: 137 | Qoldiq: -77]</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>696428.5699999999</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="I93" s="13" t="n">
+        <v>1957142.87</v>
+      </c>
+      <c r="J93" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="K93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>⚠️ MINUS (Xavfli!)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
@@ -4980,7 +10082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Didox_MXIK_va_Ombor_Qoldigi.xlsx
+++ b/Didox_MXIK_va_Ombor_Qoldigi.xlsx
@@ -521,5053 +521,4714 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="65" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MXIK Kodi (17 xonali)</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>Tasnif Nomi</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
-        <is>
-          <t>Birlashgan Tovar Nomlari Soni</t>
-        </is>
-      </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>Ushbu MXIK ostidagi Tovar Nomlari (Tafsilot)</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>Jami Kirim Miqdori</t>
-        </is>
-      </c>
-      <c r="G1" s="9" t="inlineStr">
-        <is>
-          <t>Jami Kirim Summasi (UZS)</t>
-        </is>
-      </c>
-      <c r="H1" s="9" t="inlineStr">
-        <is>
-          <t>Jami Chiqim Miqdori</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>Jami Chiqim Summasi (UZS)</t>
-        </is>
-      </c>
-      <c r="J1" s="9" t="inlineStr">
-        <is>
-          <t>Hozirgi Ombor Qoldig'i (Kirim - Chiqim)</t>
-        </is>
-      </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tasnif Nomi (Mahsulot guruhi)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Jamlangan Tovar Xillari Soni</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Barcha Tovar Nomlari Ro'yxati</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>O'lchov Birligi</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Kirim Miqdori (Jami)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Kirim Summasi (UZS)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Chiqim Miqdori (Jami)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Chiqim Summasi (UZS)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Hisobdagi Qoldiq (Kirim - Chiqim)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Qoldiq Summasi (UZS)</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Holati</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>06214001011000000</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Тиббий бандаж</t>
         </is>
       </c>
-      <c r="D2" s="11" t="n">
+      <c r="D2" t="n">
         <v>119</v>
       </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>• "(01910) Бандаж поддерживающий для руки, правый,  Размер 2": [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 2": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
-• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 3": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
-• "(01984) Бандаж послеоперационный на грудной клетку,  Размер 4": [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
-• (01901) Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3: [Kirim: 32 | Chiqim: 0 | Qoldiq: 32]
-• (01901-3 )Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01902 )Бандаж детский для попучной грыжи: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01902) Бандаж детский для попучной грыжи: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• (01903) Бандаж эластичный дородовой, Размер 2: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• (01903) Бандаж эластичный дородовой, Размер 3: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• (01903-2)Бандаж эластичный дородовой, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01903-3)Бандаж эластичный дородовой, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01904) Бандаж фиксирующий эластичный, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01904) Бандаж фиксирующий эластичный, Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01904) Бандаж фиксирующий эластичный, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01904) Бандаж фиксирующий эластичный, Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01904-2)Бандаж фиксирующий эластичный, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01904-3)Бандаж фиксирующий эластичный, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01904-4)Бандаж фиксирующий эластичный, Размер 4: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01910) Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• (01910) Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01910-л)Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01910-п)Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• (01926) Бандаж поддерживающий для руки (детский): [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
-• (01926)Бандаж поддерживающий для руки (детский): [Kirim: 0 | Chiqim: 29 | Qoldiq: -29]
-• (01927) Бандаж поддерживающий для руки. Размер 2: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• (01927) Бандаж поддерживающий для руки. Размер 3: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• (01927-2)Бандаж поддерживающий для руки. Размер 2: [Kirim: 0 | Chiqim: 34 | Qoldiq: -34]
-• (01927-3)Бандаж поддерживающий для руки. Размер 3: [Kirim: 0 | Chiqim: 35 | Qoldiq: -35]
-• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01929-2)Бандаж медицинский послеоперационный (поддерживающий), Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01929-3)Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• (01929-4)Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• (01929-5)Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01931) Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01931) Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
-• (01931) Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
-• (01931-1)Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01931-2)Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
-• (01931-3)Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]
-• (01933) Бандаж послеродовой, Размер 2: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01933) Бандаж послеродовой, Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01933) Бандаж послеродовой, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01933-2)Бандаж послеродовой, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01933-3)Бандаж послеродовой, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01936) Бандаж послеродовой, Размер 2: [Kirim: 7 | Chiqim: 0 | Qoldiq: 7]
-• (01936-2)Бандаж для паховой грыжи, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01954-1)Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01954-2)Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• (01954-3)Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01961-1)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• (01961-2)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• (01961-3)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01979) Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01979) Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01979-2)Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01979-2)Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01984) Бандаж послеоперационный на грудной клетку, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01984) Бандаж послеоперационный на грудной клетку, Размер 3: [Kirim: 5 | Chiqim: 2 | Qoldiq: 3]
-• (01984) Бандаж послеоперационный на грудной клетку, Размер 4: [Kirim: 5 | Chiqim: 3 | Qoldiq: 2]
-• Бандаж детский для попучной грыжи: [Kirim: 40 | Chiqim: 56 | Qoldiq: -16]
-• Бандаж для паховой грыжи, Размер 2: [Kirim: 10 | Chiqim: 11 | Qoldiq: -1]
-• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
-• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
-• Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• Бандаж медицинский послеоперационный (поддерживающий), Размер 2: [Kirim: 20 | Chiqim: 10 | Qoldiq: 10]
-• Бандаж медицинский послеоперационный (поддерживающий), Размер 3: [Kirim: 20 | Chiqim: 14 | Qoldiq: 6]
-• Бандаж медицинский послеоперационный (поддерживающий), Размер 4: [Kirim: 20 | Chiqim: 19 | Qoldiq: 1]
-• Бандаж медицинский послеоперационный (поддерживающий), Размер 5: [Kirim: 10 | Chiqim: 5 | Qoldiq: 5]
-• Бандаж медицинский послеоперационный (поддерживающий), Размер 6: [Kirim: 10 | Chiqim: 2 | Qoldiq: 8]
-• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• Бандаж поддерживающий для руки (детский: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Бандаж поддерживающий для руки (детский): [Kirim: 60 | Chiqim: 147 | Qoldiq: -87]
-• Бандаж поддерживающий для руки, левый, Размер 2: [Kirim: 10 | Chiqim: 53 | Qoldiq: -43]
-• Бандаж поддерживающий для руки, правый, Размер 2: [Kirim: 10 | Chiqim: 50 | Qoldiq: -40]
-• Бандаж поддерживающий для руки. Размер 1: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
-• Бандаж поддерживающий для руки. Размер 2: [Kirim: 100 | Chiqim: 143 | Qoldiq: -43]
-• Бандаж поддерживающий для руки. Размер 3: [Kirim: 100 | Chiqim: 137 | Qoldiq: -37]
-• Бандаж послеоперационный на грудной клетку, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• Бандаж послеоперационный на грудной клетку, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• Бандаж послеоперационный на грудной клетку, Размер 4: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Бандаж послеродовой, Размер 2: [Kirim: 20 | Chiqim: 34 | Qoldiq: -14]
-• Бандаж послеродовой, Размер 3: [Kirim: 20 | Chiqim: 49 | Qoldiq: -29]
-• Бандаж послеродовой, Размер 4: [Kirim: 20 | Chiqim: 30 | Qoldiq: -10]
-• Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3: [Kirim: 0 | Chiqim: 19 | Qoldiq: -19]
-• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
-• Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом) Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• Бандаж фиксирующий эластичный, Размер 2: [Kirim: 30 | Chiqim: 26 | Qoldiq: 4]
-• Бандаж фиксирующий эластичный, Размер 3: [Kirim: 30 | Chiqim: 49 | Qoldiq: -19]
-• Бандаж фиксирующий эластичный, Размер 4: [Kirim: 30 | Chiqim: 45 | Qoldiq: -15]
-• Бандаж фиксирующий эластичный, Размер 5: [Kirim: 30 | Chiqim: 27 | Qoldiq: 3]
-• Бандаж эластичный дородовой (летний), Размер 1: [Kirim: 10 | Chiqim: 25 | Qoldiq: -15]
-• Бандаж эластичный дородовой (летний), Размер 2: [Kirim: 10 | Chiqim: 70 | Qoldiq: -60]
-• Бандаж эластичный дородовой (летний), Размер 3: [Kirim: 10 | Chiqim: 72 | Qoldiq: -62]
-• Бандаж эластичный дородовой (с жёсткими вставками), Размер 1: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
-• Бандаж эластичный дородовой (с жёсткими вставками), Размер 2: [Kirim: 10 | Chiqim: 21 | Qoldiq: -11]
-• Бандаж эластичный дородовой (с жёсткими вставками), Размер 3: [Kirim: 10 | Chiqim: 29 | Qoldiq: -19]
-• Бандаж эластичный дородовой на лямках, Размер 2: [Kirim: 0 | Chiqim: 37 | Qoldiq: -37]
-• Бандаж эластичный дородовой на лямках, Размер 3: [Kirim: 0 | Chiqim: 37 | Qoldiq: -37]
-• Бандаж эластичный дородовой, Размер: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Бандаж эластичный дородовой, Размер 2: [Kirim: 30 | Chiqim: 58 | Qoldiq: -28]
-• Бандаж эластичный дородовой, Размер 2Бандаж эластичный дородовой, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Бандаж эластичный дородовой, Размер 3: [Kirim: 30 | Chiqim: 58 | Qoldiq: -28]
-• Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• Тутор коленного сустава, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>"(01910) Бандаж поддерживающий для руки, правый,  Размер 2" | "(01984) Бандаж послеоперационный на грудной клетку,  Размер 2" | "(01984) Бандаж послеоперационный на грудной клетку,  Размер 3" | "(01984) Бандаж послеоперационный на грудной клетку,  Размер 4" | (01901) Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3 | (01901-3 )Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3 | (01902 )Бандаж детский для попучной грыжи | (01902) Бандаж детский для попучной грыжи | (01903) Бандаж эластичный дородовой, Размер 2 | (01903) Бандаж эластичный дородовой, Размер 3 | (01903-2)Бандаж эластичный дородовой, Размер 2 | (01903-3)Бандаж эластичный дородовой, Размер 3 | (01904) Бандаж фиксирующий эластичный, Размер 2 | (01904) Бандаж фиксирующий эластичный, Размер 3 | (01904) Бандаж фиксирующий эластичный, Размер 4 | (01904) Бандаж фиксирующий эластичный, Размер 5 | (01904-2)Бандаж фиксирующий эластичный, Размер 2 | (01904-3)Бандаж фиксирующий эластичный, Размер 3 | (01904-4)Бандаж фиксирующий эластичный, Размер 4 | (01910) Бандаж поддерживающий для руки, левый, Размер 2 | (01910) Бандаж поддерживающий для руки, правый, Размер 2 | (01910-л)Бандаж поддерживающий для руки, левый, Размер 2 | (01910-п)Бандаж поддерживающий для руки, правый, Размер 2 | (01926) Бандаж поддерживающий для руки (детский) | (01926)Бандаж поддерживающий для руки (детский) | (01927) Бандаж поддерживающий для руки. Размер 2 | (01927) Бандаж поддерживающий для руки. Размер 3 | (01927-2)Бандаж поддерживающий для руки. Размер 2 | (01927-3)Бандаж поддерживающий для руки. Размер 3 | (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 3 | (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 4 | (01929) Бандаж медицинский послеоперационный (поддерживающий), Размер 5 | (01929-2)Бандаж медицинский послеоперационный (поддерживающий), Размер 2 | (01929-3)Бандаж медицинский послеоперационный (поддерживающий), Размер 3 | (01929-4)Бандаж медицинский послеоперационный (поддерживающий), Размер 4 | (01929-5)Бандаж медицинский послеоперационный (поддерживающий), Размер 5 | (01931) Бандаж эластичный дородовой (летний), Размер 1 | (01931) Бандаж эластичный дородовой (летний), Размер 2 | (01931) Бандаж эластичный дородовой (летний), Размер 3 | (01931-1)Бандаж эластичный дородовой (летний), Размер 1 | (01931-2)Бандаж эластичный дородовой (летний), Размер 2 | (01931-3)Бандаж эластичный дородовой (летний), Размер 3 | (01933) Бандаж послеродовой, Размер 2 | (01933) Бандаж послеродовой, Размер 3 | (01933) Бандаж послеродовой, Размер 4 | (01933-2)Бандаж послеродовой, Размер 2 | (01933-3)Бандаж послеродовой, Размер 3 | (01936) Бандаж послеродовой, Размер 2 | (01936-2)Бандаж для паховой грыжи, Размер 2 | (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 1 | (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 2 | (01954) Бандаж эластичный дородовой (с жёсткими вставками), Размер 3 | (01954-1)Бандаж эластичный дородовой (с жёсткими вставками), Размер 1 | (01954-2)Бандаж эластичный дородовой (с жёсткими вставками), Размер 2 | (01954-3)Бандаж эластичный дородовой (с жёсткими вставками), Размер 3 | (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1 | (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2 | (01961) Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3 | (01961-1)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1 | (01961-2)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2 | (01961-3)Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3 | (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2 | (01969) Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3 | (01979) Бандаж эластичный дородовой на лямках, Размер 2 | (01979) Бандаж эластичный дородовой на лямках, Размер 3 | (01979-2)Бандаж эластичный дородовой на лямках, Размер 2 | (01979-2)Бандаж эластичный дородовой на лямках, Размер 3 | (01984) Бандаж послеоперационный на грудной клетку, Размер 2 | (01984) Бандаж послеоперационный на грудной клетку, Размер 3 | (01984) Бандаж послеоперационный на грудной клетку, Размер 4 | Бандаж детский для попучной грыжи | Бандаж для паховой грыжи, Размер 2 | Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 1 | Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 2 | Бандаж медицинский послеоперацион-ный для фиксации грудной клетки, Размер 3 | Бандаж медицинский послеоперационный (поддерживающий), Размер 2 | Бандаж медицинский послеоперационный (поддерживающий), Размер 3 | Бандаж медицинский послеоперационный (поддерживающий), Размер 4 | Бандаж медицинский послеоперационный (поддерживающий), Размер 5 | Бандаж медицинский послеоперационный (поддерживающий), Размер 6 | Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 1 | Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 2 | Бандаж медицинский послеоперационный для фиксации грудной клетки, Размер 3 | Бандаж поддерживающий для руки (детский | Бандаж поддерживающий для руки (детский) | Бандаж поддерживающий для руки, левый, Размер 2 | Бандаж поддерживающий для руки, правый, Размер 2 | Бандаж поддерживающий для руки. Размер 1 | Бандаж поддерживающий для руки. Размер 2 | Бандаж поддерживающий для руки. Размер 3 | Бандаж послеоперационный на грудной клетку, Размер 2 | Бандаж послеоперационный на грудной клетку, Размер 3 | Бандаж послеоперационный на грудной клетку, Размер 4 | Бандаж послеродовой, Размер 2 | Бандаж послеродовой, Размер 3 | Бандаж послеродовой, Размер 4 | Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 2 | Бандаж фиксирующий на плечевой сустав (повязка дезо), Размер 3 | Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом Размер 3 | Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом)  Размер 3 | Бандаж фиксирующий на тазобедренный сустав "Шина фрейка" (с дополнительным чехлом) Размер 3 | Бандаж фиксирующий эластичный, Размер 2 | Бандаж фиксирующий эластичный, Размер 3 | Бандаж фиксирующий эластичный, Размер 4 | Бандаж фиксирующий эластичный, Размер 5 | Бандаж эластичный дородовой (летний), Размер 1 | Бандаж эластичный дородовой (летний), Размер 2 | Бандаж эластичный дородовой (летний), Размер 3 | Бандаж эластичный дородовой (с жёсткими вставками), Размер 1 | Бандаж эластичный дородовой (с жёсткими вставками), Размер 2 | Бандаж эластичный дородовой (с жёсткими вставками), Размер 3 | Бандаж эластичный дородовой на лямках, Размер 2 | Бандаж эластичный дородовой на лямках, Размер 3 | Бандаж эластичный дородовой, Размер | Бандаж эластичный дородовой, Размер 2 | Бандаж эластичный дородовой, Размер 2Бандаж эластичный дородовой, Размер 2 | Бандаж эластичный дородовой, Размер 3 | Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный | Тутор коленного сустава, Размер 2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>2122</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="H2" t="n">
         <v>112599000</v>
       </c>
-      <c r="H2" s="12" t="n">
-        <v>1622</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>94350446.15000017</v>
-      </c>
-      <c r="J2" s="14" t="n">
+      <c r="I2" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J2" t="n">
+        <v>94280981.87000017</v>
+      </c>
+      <c r="K2" t="n">
+        <v>502</v>
+      </c>
+      <c r="L2" t="n">
+        <v>26637463.71347785</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>09018010033000000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ўзбекистон Республикаси Соғлиқни сақлаш вазирлигининг 06.29.2016 йилдаги  60-сонли буйруғи билан тасдиқланган рўйхатга киритилган, тиббий буюмлар</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>111</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>"(01908) Трусы медицинские после обрезания для мальчиков,  Размер 1" | "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 2" | "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 3" | "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 1" | "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 2" | "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 3" | (01908) Трусы медицинские после обрезания для мальчиков, Размер 2 | (01908) Трусы медицинские после обрезания для мальчиков, Размер 3 | (01908-1)Трусы медицинские для мальчиков Размер 1 | (01908-2)Трусы медицинские для мальчиков Размер 2 | (01908-3)Трусы медицинские для мальчиков Размер 3 | (01909) Повязка медицинская из неопрена для фиксации лучезапястного сустав | (01909)Повязка медицинская из неопрена для фиксации лучезапястного сустав | (01912) Воротник ортопедический жесткий, Размер 1 | (01912) Воротник ортопедический жесткий, Размер 2 | (01912) Воротник ортопедический жесткий, Размер 3 | (01912) Воротник ортопедический жесткий, Размер 4 | (01912-2)Воротник ортопедический жесткий, Размер 2 | (01912-4)Воротник ортопедический жесткий, Размер 4 | (01914-2)Корректор осанки, Размер 2 | (01914-3)Корректор осанки, Размер 3 | (01914-4)Корректор осанки, Размер 4 | (01918) Корректор осанки, с рёбрами жёсткости, Размер 2 | (01918) Корректор осанки, с рёбрами жёсткости, Размер 3 | (01918) Корректор осанки, с рёбрами жёсткости, Размер 4 | (01918-2)Корректор осанки, с рёбрами жёсткости, Размер 2 | (01918-3)Корректор осанки, с рёбрами жёсткости, Размер 3 | (01918-4)Корректор осанки, с рёбрами жёсткости, Размер 4 | (01919-1)Корректор осанки детский, с рёбрами жёсткости, Размер 1 | (01919-2)Корректор осанки детский, с рёбрами жёсткости, Размер 2 | (01919-3)Корректор осанки детский, с рёбрами жёсткости, Размер 3 | (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1 | (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2 | (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3 | (01921-1)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1 | (01921-2)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2 | (01921-3)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3 | (01924) Воротник ортопедический, надувной | (01924)Воротник ортопедический,надувной | (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1 | (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2 | (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3 | (01930-1)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1 | (01930-2)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2 | (01930-3)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3 | (01947) Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный | (01947)Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный | (01950) Корректор осанки (универсальный) | (01950)Корректор осанки (универсальный) | (01953)Корректор осанки, детский. (универсальный) | Shprist 50ml | Браслет Идентификационный Голубого Цвета | Браслет Идентификационный Розового Цвета | Воротник ортопедический жесткий, Размер 1 | Воротник ортопедический жесткий, Размер 2 | Воротник ортопедический жесткий, Размер 3 | Воротник ортопедический жесткий, Размер 4 | Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1 | Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2 | Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3 | Воротник ортопедический мягкий, для детей (шина шанца), Размер 1 | Воротник ортопедический мягкий, для детей (шина шанца), Размер 2 | Воротник ортопедический мягкий, для детей (шина шанца), Размер 3 | Воротник ортопедический мягкий, для детей, Размер 1 | Воротник ортопедический мягкий, для детей, Размер 2 | Воротник ортопедический мягкий, для детей, Размер 3 | Воротник ортопедический, надувной | Воротник ортопедический,надувной | Канюля Кислородная, Стерильный для Однократного Применения для Подростковый (Child) | Катетеры Кислородные, Стерильные для Однократного Применения для Взрослых (Adult) | Катетеры Кислородные, Стерильный для Однократного Применения для Взрослый (Adult) | Корректор осанки (универсальный) | Корректор осанки детский, с рёбрами жёсткости, Размер 1 | Корректор осанки детский, с рёбрами жёсткости, Размер 2 | Корректор осанки детский, с рёбрами жёсткости, Размер 3 | Корректор осанки, Размер 1 | Корректор осанки, Размер 2 | Корректор осанки, Размер 3 | Корректор осанки, Размер 4 | Корректор осанки, детский. (универсальный) | Корректор осанки, с рёбрами жёсткости, Размер 2 | Корректор осанки, с рёбрами жёсткости, Размер 3 | Корректор осанки, с рёбрами жёсткости, Размер 4 | Маска Кислородная, Стерильная для Однократного Применения для Взрослый | Маска Кислородная, Стерильная для Однократного Применения для Детский | Мочеприемник Прикроватный с Т-образным Сливным Клапаном, Стерильный для Однократного Применения Объемом 2 л | Набор для ингалятора (Маска кислородная) Disposable Nebulizer для взрослых | Набор для ингалятора (Маска кислородная) Disposable Nebulizer для детский | Небулайзер Компрессорный NIMO модель HNK-NBL-S с Комплектующими | Перчатки ARMOUR Хирургические, Латексные, Стерильный для Однократного Применения, Размер: 7,5 | Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5 | Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный | Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный | Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1 | Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2 | Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3 | Повязка медицинская из неопрена для фиксации лучезапястного сустав | Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 11 SURGEON | Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 15 SURGEON | Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 22 SURGEON | Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 23 SURGEON | Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 24 SURGEON | Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 11  SURGEON | Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 22  SURGEON | Трусы медицинские для мальчиков Размер 1 | Трусы медицинские для мальчиков Размер 2 | Трусы медицинские для мальчиков Размер 3 | Трусы медицинские для мальчиков Размер 3Трусы медицинские для мальчиков Размер 3 | Трусы медицинские после обрезания для мальчиков, Размер 1 | Трусы медицинские после обрезания для мальчиков, Размер 2 | Трусы медицинские после обрезания для мальчиков, Размер 3</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12094</v>
+      </c>
+      <c r="H3" t="n">
+        <v>138336000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7856</v>
+      </c>
+      <c r="J3" t="n">
+        <v>111445089.0499999</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4238</v>
+      </c>
+      <c r="L3" t="n">
+        <v>48475935.83595171</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>03923001007000000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Пластмассадан тайёрланган идишлар, бутилкалар, флаконлар ва шунга ўхшаш идишлар</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>.Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт. | Бутылка для детс.питание "MUMMY" обье 80 мл 1074-1 кор.-1шт | Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128-  шт | Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128- шт | Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт | Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт. | Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1127-шт. | Бутылка плас-вые с ручкой для кормление 240мл/ MUMMY 1079- шт | Бутылочки для детс. питание "MUMMY"1074 | Бутылочки для детс. питание "MUMMY"1078 | Бутылочки для детс. питание "MUMMY"1079 | Бутылочки для детс. питание "MUMMY"1127 | Бутылочки для детс. питание "MUMMY"1128 | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 1 шт | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 шт- | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074- шт | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт | Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт- | Детская бутылка пластмассовый    (7.17.016) 330ml | Детская бутылка пластмассовый   (ALGO 7.17.013) 125ml | Детская бутылка пластмассовый  (7.17.017) 260 ml | Детская бутылка пластмассовый  (ALGO 7.17.012) 280 ml | Детская бутылка пластмассовый  (ALGO 8107) 280 ml | Детская бутылка пластмассовый  (ALGO 8228) 60 ml | Детская бутылка пластмассовый  (RBT-706)  706ml | Детская бутылка пластмассовый (7,17,016) 330 ml | Детская бутылка пластмассовый (7,17,017) 260 ml | Детская бутылка пластмассовый (7.17.016) 330 ml | Детская бутылка пластмассовый (ALGO 8107) 280 ml | Детская бутылка пластмассовый (ALGO 8228) 60 ml | Детская бутылка пластмассовый (RBT-706) 706ml (7.17.027) | Детская бутылка пластмассовый 125ml Бренд: ALGO 8108 (7.17.013) | Детская бутылка пластмассовый Бренд: ALGO. Model: 8228 60ml (7.17.042) | Детские  бутылки  180 мл (DDE-1035) | Детские  бутылки  270 мл (DDE-1036) | Детские  бутылки (200) | Детские  бутылки (248) | Детские  бутылки ONLY BABY NATURAL 125 мл (А-3) | Детские  бутылки ONLY BABY NATURAL 260 мл (А-2) | Детские бутилки (248) | Детские бутилки (249) | Детские бутилки (358) | Детские бутилки (360) | Детские бутылки  (200) | Детские бутылки  (201) | Детские бутылки  (202) | Детские бутылки  (249) | Детские бутылки (200) 180ml | Детские бутылки (201) | Детские бутылки (201) 240ml | Детские бутылки (202) | Детские бутылки (202) 300ml | Детские бутылки (248) | Детские бутылки (249) | Детские бутылки (358) | Детские бутылки (360) | Детские бутылки (A-2-T) | Детские бутылки (А-2 )  260 мл | Детские бутылки (А-2 ) 260 мл | Детские бутылки (А-3-Т 125 мл) | Детские бутылки 180 мл (DDE-1035) | Детские бутылки 270 мл (DDE-1036) | Детские бутылки ONLY BABY NATURAL 125 мл (А-3) | Детские бутылки ONLY BABY NATURAL 260 мл (А-2) | Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7,17,036 | Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7.17.036 | Детские бутылки стеклянные из безцвет стекла 120ml (9131) | Детские бутылки стеклянные из безцвет стекла 120ml (9131) (7.17.032) | Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519) | Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519) (7.17.021) | Детские бутылки стеклянные из безцвет стекла 240ml (9130) | Детские бутылки стеклянные из безцвет стекла 240ml (9130) (7.17.031) | Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374) | Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374) (7.17.023) | Детские бутылки стеклянные из безцвет стекла ALGO 120ml (7.17.043) | Детские бутылки стеклянные из безцвет стекла ALGO 120ml (RBT-206) (7,17,043) | Детские бутьлки  (248) | Детские бутьлки  (249) | Детские бутьлки  (358 | Детские бутьлки  (358) | Детские бутьлки  (360 ) | Соска-Пустышки "PANDA" силиконовая 1122</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>19266</v>
+      </c>
+      <c r="H4" t="n">
+        <v>217341945.0000003</v>
+      </c>
+      <c r="I4" t="n">
+        <v>16457</v>
+      </c>
+      <c r="J4" t="n">
+        <v>241963660.569998</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2809</v>
+      </c>
+      <c r="L4" t="n">
+        <v>31688649.61616323</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>04016001083000000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Резинали сўрғич</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Teddy Ниппел накладкаси + сўрғич | Дет Соски (LOT-10) | Детcкие Соски (LOT-12) | Детские  соски (260) | Детские  соски (383) | Детские  соски (387) | Детские  соски для питания (285) | Детские  соски для питания (291) | Детские Cоски  (383) | Детские соски  для питания (285) | Детские соски  для питания (291) | Детские соски (038) | Детские соски (260) | Детские соски (383) | Детские соски (387) | Детские соски (LOT-10) | Детские соски для питания (285) | Детские соски для питания (291) | Соска для питание ниблер MUMMY 1129-1 шт | Соска для питание ниблер MUMMY 1129-1 шт - | Соска для питание ниблер MUMMY 1129-1 шт -2025 | Соска пустышка Panda c крышкой 106 шт | Соска-Пустышки "PANDA"  силиконовая 1123 | Соска-Пустышки "PANDA" силиконовая 1122 | Соска-Пустышки "PANDA" силиконовая 1123 | Соски пустышки Mummy 1112 | Соски пустышки Mummy 1113 | Соски пустышки Mummy 1114 | Соски пустышки Mummy модель 1111 в одном комплекте 2 шт | Соски пустышки Mummy модель 1112 в одном комплекте 2 шт | Соски пустышки Mummy модель1113 одном комплекте 2 штук | Соски пустышки Mummy модель1115 одном комплекте 2 штук | Соски-Пустышки "PANDA" 100 | Соски-Пустышки "PANDA" 100 шт</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>40738</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100886785.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>39363</v>
+      </c>
+      <c r="J5" t="n">
+        <v>110516517.2899992</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3405158.091646621</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>09021001001000000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ортопедик асбоблар (таёқчалар, бинтлар, камарлар) ёки синишларни даволаш учун (шу жумладан шиналар)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>"(01959) Вальгусная шина большого пальца стопы (шарнирная), пара " | "(01960) Вальгусная шина большого пальца стопы (носочки), пара. Размер (S)" | (01905) Вальгусная шина большого пальца стопы (ночная), пара | (01905)Вальгусная шина большого пальца стопы (ночная) | (01922) Тутор коленного сустава, Размер 1 | (01922) Тутор коленного сустава, Размер 2 | (01922) Тутор коленного сустава, Размер 3 | (01922-2)Тутор коленного сустава, Размер 2 | (01922-3)Тутор коленного сустава, Размер 3 | (01922d) Тутор коленного сустава, детский универсальный | (01923) Вальгусная шина большого пальца стопы (дневной), пара | (01960)Вальгусная шина большого пальцастопы (носочки), пара. Размер (S) | (01963) Шина для фиксации пальцев руки, Размер 1 | (01963) Шина для фиксации пальцев руки, Размер 2 | (01963) Шина для фиксации пальцев руки, Размер 3 | Вальгусная шина большого пальца стопы (дневной), пара | Вальгусная шина большого пальца стопы (носочки), пара. Размер (S) | Вальгусная шина большого пальца стопы (ночная) | Вальгусная шина большого пальца стопы (ночная), пара | Вальгусная шина большого пальца стопы (шарнирная), пара | Вальгусная шина большого пальцастопы (носочки), пара. Размер (S) | Вальгусная шина большого пальцастопы (шарнирная), пара | Костыли Нержавейка №2 Китай | Тутор коленного сустава, Размер 1 | Тутор коленного сустава, Размер 2 | Тутор коленного сустава, Размер 3 | Тутор коленного сустава, детский универсальный | Шина для фиксации пальцев руки, Размер 1 | Шина для фиксации пальцев руки, Размер 2 | Шина для фиксации пальцев руки, Размер 3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>570</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38694000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>472</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42580503.55</v>
+      </c>
+      <c r="K6" t="n">
+        <v>98</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6652652.631578947</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>03306001001000000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Тиш пастаси</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Зубная паста Лесной бальзам с органическими маслами, углём и кальцием, 75 МЛ | Зубная паста детская Ежик Сема  60мл | Зубная паста детская Ежик Сема  Крем брюле 60мл | Зубная паста детская Ежик Сема 60мл | Зубная паста детская Крокодильчик Свомпи  с мятой 60мл | Зубная паста детская Крокодильчик Свомпи с мятой 60мл | Зубная паста профилактическая детская Фруктовая  75г | Зубная паста профилактическая детская Фруктовая 75г | ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ Р2, 75 МЛ | ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ ЧЗ, 75 МЛ | ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ КОРЫ ДУБА И ПИХТЫ НА ОТВАРЕ ТРАВ, 75 МЛ | ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ ПРОПОЛИСА И ЗВЕРОБОЯ НА ОТВАРЕ ТРАВ, 75 МЛ | ЛЕСНОЙ БАЛЬЗАМ Профилактическая зубная паста "Лесной бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной Бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной Бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной бальзам" с экстрактами коры дуба и пихты на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной бальзам" с экстрактами прополиса и зверобоя на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 МЛ | Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 мл | детская Ежик Сема с мятой  60мл | детская Ежик Сема с мятой 60мл</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1322</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8164047.879999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>839</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8235535.680000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>483</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2982779.974311649</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>09619002001000000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Тагликлар</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SMART ADULT DIAPERS L | SMART ADULT DIAPERS M | SMART ADULT DIAPERS XL | Подгузники для взрослых  Evony  Х-Large 30х4 | Подгузники для взрослых  Evony Large 30х4 | Подгузники для взрослых  Evony М размер 30х4 | Подгузники для взрослых Evony Large 30х4 | Подгузники для взрослых Evony М размер 30х4 | Подгузники для взрослых Evony Х-Large 30х4 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/12 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/38 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MAXI 4/16 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MIDI 3/18 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR 5/14 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/12 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/38 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MAXI 4/16 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MIDI 3/18 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MINI 2/20 | УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium YENIDOG'AN 1/22</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9515</v>
+      </c>
+      <c r="H8" t="n">
+        <v>137804285.72</v>
+      </c>
+      <c r="I8" t="n">
+        <v>7654</v>
+      </c>
+      <c r="J8" t="n">
+        <v>136209821.5499999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1861</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26952577.58538307</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>03304999015000000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Присыпка (в т.ч. детская)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kodomo Детская присыпка (Extra Mild) 50гр | Kodomo Детская присыпка (Extra Mild) English &amp; Arabic Label 180гр | Kodomo Детская присыпка (Gentle Soft) 50гр | Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр | Kodomo Детская присыпка (Natural Soft Protection) 50гр | Kodomo Детская присыпка (Natural Soft Protection)English &amp; Arabic Language 180гр | Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 160гр | Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр | Teddy Болалар упаси (Лаванда) 50 гр | Teddy Болалар упаси (Оддий) 50 гр | Teddy Присыпка  простой  50 гр | Детская присыпка  " Попкинсы"  120г | Детская присыпка " Попкинсы" 120г | Детская присыпка 80 г/Puder 80g | Пересипка детский Baby "UPPY" 100 мл | №1 Kodomo Детская присыпка (Gentle Soft) 50гр | №1 Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр | №1 Kodomo Детская присыпка (Natural Soft Protection) 50гр | №1 Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6704</v>
+      </c>
+      <c r="H9" t="n">
+        <v>61153395.69000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4783</v>
+      </c>
+      <c r="J9" t="n">
+        <v>56578035.75999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1921</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17523220.93086068</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>04014001012000000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Тишлар учун резина</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Грудная накладка  MUMMY - 1132 -шт | Грудная накладка MUMMY - 1132 -шт | Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION) | Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION) (7.29.003) | Детский силиконовый прорезыватель для зубов RBT-401  (CORN EDITION) | Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION) | Детский силиконовый прорезыватель для зубов RBT-402  (BANANA EDITION) | Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION) | Зубагризки | Зубагризки (FZ-188) | Зубагризки (FZ-189) | Зубогрызки из силикова Артикуль №3 MUMMY модел 1102-  шт | Зубогрызки из силикова Артикуль №3 MUMMY модел 1102- шт | Зубогрызки из силикона Артикуль №1 MUMMY модель 1100-шт | Зубогрызки из силикона Артикуль №2 MUMMY модел 1101- шт | Зубогрызки из силикона Артикуль №2 MUMMY модел 1101-шт | Соска-Пустышки "PANDA"  силиконовая 1123 | Соска-Пустышки "PANDA" силиконовая 1123</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>8352</v>
+      </c>
+      <c r="H10" t="n">
+        <v>28759388.57</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6670</v>
+      </c>
+      <c r="J10" t="n">
+        <v>32928392.3900001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1682</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5791821.309236111</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06214001013000000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Корсет маҳсулотлари</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(01944) Корсет эластичный для коррекции фигуры, Размер 3 | (01944) Корсет эластичный для коррекции фигуры, Размер 4 | (01944) Корсет эластичный для коррекции фигуры, Размер 5 | (01944-3)Корсет эластичный для коррекции фигуры, Размер 3 | (01944-4)Корсет эластичный для коррекции фигуры, Размер 4 | (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 2 | (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 3 | (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 4 | (01946-2)Корсет поясничный ортопедический, с жёстками вставками, Размер 2 | (01946-3)Корсет поясничный ортопедический, с жёстками вставками, Размер 3 | (01946-4)Корсет поясничный ортопедический, с жёстками вставками, Размер 4 | Корсет поясничный ортопедический, с жёстками вставками, Размер 2 | Корсет поясничный ортопедический, с жёстками вставками, Размер 3 | Корсет поясничный ортопедический, с жёстками вставками, Размер 4 | Корсет эластичный для коррекции фигуры, Размер 3 | Корсет эластичный для коррекции фигуры, Размер 4 | Корсет эластичный для коррекции фигуры, Размер 5</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>228</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14646000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>167</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12213482.32999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>61</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3918447.368421053</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>03003001018000000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Бошқа қадоқланмаган дори воситалари (фармацевтик субстанциялар)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Achchiq bodom 100 ml | G'oz moyi 100 ml | Gʻoz 100ml | G’oz yogʻi 100ml | Kanakunjut 100 ml | Kanakunjut 100ml | Kanakunjut yogʻi 100ml | Qovoq danak moyi 100 ml | Qovoq donagi moyi 100ml | Sedana 100 ml | Sedana 100ml | Shaftoli danak moyi 100 ml | Shirin bodom 100 ml | Zaytun 100 ml | Zaytun 100ml | Zaytun yogʻi 100ml</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3700</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16387919</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3572</v>
+      </c>
+      <c r="J12" t="n">
+        <v>18383124.71000005</v>
+      </c>
+      <c r="K12" t="n">
+        <v>128</v>
+      </c>
+      <c r="L12" t="n">
+        <v>566933.4140540541</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>02106999028000000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Achchiq bodom yog'i 100 ml | Achchiq bodom yog'i 100ml | G'oz yog'i 100 ml | Kanakunjut yog'i 100 ml | Kanakunjut yog'i 100ml | Qora sedana yog'i 100 ml | Sedana yog'i 100ml | Shaftoli danagi yog'i 100 ml | Shaftoli yog'i 100ml | Shirin bodom yog'i 100ml | Zaytun yog'i 100 ml | Zaytun yog'i 100ml | Пол Пола чай №15 | Расторопша чай №15 | Шиповник чай №15</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>4950</v>
+      </c>
+      <c r="H13" t="n">
+        <v>23142857.81</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3387</v>
+      </c>
+      <c r="J13" t="n">
+        <v>19965714.15000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1563</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7307532.678187878</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>03005002002000000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Эластик бинтлар</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Бинт эластичный медицинский GT 100мм х 2 метр | Бинт эластичный медицинский GT 100мм х 3 метр | Бинт эластичный медицинский GT 100мм х 4 метр | Бинт эластичный медицинский GT 100мм х 5 метр | Бинт эластичный медицинский GT 100мм х 6 метр | Бинт эластичный медицинский GT 120мм х 2 метр | Бинт эластичный медицинский GT 120мм х 3 метр | Бинт эластичный медицинский GT 120мм х 4 метр | Бинт эластичный медицинский GT 120мм х 5 метр | Бинт эластичный медицинский GT 140мм х 2 метр | Бинт эластичный медицинский GT 140мм х 3 метр | Бинт эластичный медицинский GT 140мм х 4 метр | Бинт эластичный медицинский GT 140мм х 5 метр | Бинт эластичный медицинский GT 80мм х 2 метр | Бинт эластичный медицинский GT 80мм х 3 метр</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1790</v>
+      </c>
+      <c r="H14" t="n">
+        <v>21765800</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1394</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19309464.10000002</v>
+      </c>
+      <c r="K14" t="n">
+        <v>396</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4815227.262569833</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>03401001001000000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Атир совун</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>БОРО ПЛЮС Антибактериальное Мыло 100гр в коробке №1(1х1) | И01-072-00 Мыло туалетное твердое " ABSOLUT FitoGuard" Белый чай и масло оливы, 90 гр. | И01-072-00 Мыло туалетное твердое "ABSOLUT 2в1" дикая орхидея, 90 гр. | И01-072-00 Мыло туалетное твердое "ABSOLUT For men" Лемонграсс и мята, 90 гр. | И01-072-00 Мыло туалетное твердое "ABSOLUT" FitoGuard облепиха, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS освежающее, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS ультразащита, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard алоэ, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard ромашка, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' календула, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' череда, 90 гр. | И01-072-00 Мыло туалетное твердое 'ABSOLUT' 2в1 нежное, 90 гр. | И01-072-00 Мыло туалетное твердое ABSOLUT грейпфрут и бергамот, 90 гр. | И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Главаптека' (дегтярное), 90 гр. | И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Малышам', 90 гр.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1328</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7707857.159999997</v>
+      </c>
+      <c r="I15" t="n">
+        <v>884</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5451071.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>444</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2577024.532409638</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>03926001020008003</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар CANPOL Babies Клипса-ушлагич сўрғич учун, 0 ой+</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001) | Соски из силикона (RBT-309) | Соски из силикона (RBT-309) (7.23.034) | Соски из силикона (RBT-310) | Соски из силикона (RBT-310) (7.23.035) | Соски из силикона MAGEMIOR | Соски из силикона RABITO (RBT-101) | Соски из силикона RABITO (RBT-410) | Соски из силикона RABITO (RBT-410) (7.35.001) | Соски из силикона Артикул: 7,23,003 | Соски из силикона Артикул: 7,23,042 | Соски из силикона Артикул: 7.23.003 | Соски из силикона Артикул: 7.23.042 | Соски из силикона Модель:S-23-A. Артикул: 7.23.026 barcode 6928568951760 размер:S (0-6 месяц)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2872</v>
+      </c>
+      <c r="H16" t="n">
+        <v>19155016.68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1632</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15894642.88999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8270271.825626741</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03304011005000000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Қўл учун крем</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК И НОГТЕЙ КОМПЛЕКСНЫЙ, 80 МЛ | БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК НОЧНОЙ ВОССТАНАВЛИВАЮЩИЙ Р2, 80 МЛ | БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК РЕГЕНЕРИРУЮЩИЙ Р2, 80 МЛ | БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК СМЯГЧАЮЩИЙ Р2, 80 МЛ | БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК УВЛАЖНЯЮЩИЙ, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ защитный для рук, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ комплексный для рук и ногтей, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ ночной восстанавливающий для рук, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ питательный для рук, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ регенерирующий для рук, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ смягчающий для рук, 80 МЛ | Крем БАРХАТНЫЕ РУЧКИ увлажняющий для рук, 80 МЛ | Крем косметический Нежные ручки Козье молоко 125мл | Крем косметический Нежные ручки Питательный 125мл</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7599327.12</v>
+      </c>
+      <c r="I17" t="n">
+        <v>776</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6842857.200000002</v>
+      </c>
+      <c r="K17" t="n">
+        <v>324</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2238347.2608</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03401001002000000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Суюқ совун</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ELFIN  JIDKOYE  MILO 300 GR  DOZ | ELFIN  JIDKOYE  MILO 300 GR SOS | ELFIN  JIDKOYE  MILO 500 GR SOS | ELFIN JIDKOYE MILO 300 GR DOZ | ELFIN JIDKOYE MILO 300 GR SOS | ELFIN JIDKOYE MILO 300 GR SOSELFIN JIDKOYE MILO 300 GR SOS | ELFIN JIDKOYE MILO 500 GR SOS | Elfin  jitki Mila 300 gr soskalik | Elfin jidki mila 300 dozorlik | Elfin jidki mila 300 gr soskalik | HAVEN JIDKOYE MILO  500 GR  kapalak | Елфин житки мило 300гр SOS | Елфин житки мило 300гр Дазатр</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6714</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18558714.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6588</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20880178.37000005</v>
+      </c>
+      <c r="K18" t="n">
+        <v>126</v>
+      </c>
+      <c r="L18" t="n">
+        <v>348286.8635388739</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>04014001006000000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Болалар соскаси бутилка учун</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Детские cоски для  бутылочек  (40332MIX) | Детские Соски для бутылочек (40332MIX) | Детские соски для бутылок | Детские соски для бутылочек | Детские соски для бутылочек (40332) | Соска пустышка Panda c крышкой 106 шт | Соски пустышки Mummy модель 1111 в одном комплекте 2 шт | Соски пустышки Mummy модель 1112 в одном комплекте 2 шт | Соски пустышки Mummy модель 1114 в одном комплекте 2 шт | Соски пустышки Mummy модель1113 одном комплекте 2 штук | Соски пустышки Mummy модель1115 одном комплекте 2 штук</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>14640</v>
+      </c>
+      <c r="H19" t="n">
+        <v>19504999.97</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12106</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25876607.06000003</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2534</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3376070.349998633</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>03924001010000000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Уй-рўзғор ва маиший эҳтиёжлар учун пластмасса буюмлар (пластмассадан тайёрланган ошхона идиш-товоқлари, приборлар ва ошхона анжомларидан ташқари)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Детские  бутылки ONLY BABY NATURAL 260 мл (А-2) | Детские бутылки   (358) | Детские бутылки (358) | Детские бутылки (360) | Пластмассовый цепочка держатель для  соски( RBT-305) | Пластмассовый цепочка держатель для соски (RBT-129) 7,30,011 | Пластмассовый цепочка держатель для соски (RBT-129) 7.30.011 | Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003 | Пластмассовый цепочка держатель для соски (RBT-130) 7.30.003 | Пластмассовый цепочка держатель для соски( RBT-305) | Пластмассовый цепочка держатель для соски( RBT-305) (7.30.002)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>5328</v>
+      </c>
+      <c r="H20" t="n">
+        <v>32060828.56</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3233</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25938660.62000002</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2095</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12606500.71944444</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10306002005000000</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Услуги по электронному документообороту.</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Услуги по организации юридически значимого документооборота между организациями (Didox) за август 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за апрель 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за декабрь 2025г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за июль 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за июнь 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за май 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за март 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за ноябрь 2025г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за февраль 2026г. | Услуги по организации юридически значимого документооборота между организациями (Didox) за январь 2026г.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1174</v>
+      </c>
+      <c r="H21" t="n">
+        <v>632000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1174</v>
+      </c>
+      <c r="L21" t="n">
+        <v>632000</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>03924001002000000</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Пластик ошхона идишлари, приборлар ва ошхона анжомлари</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Детская бутылка пластмассовый  (ALGO 7.17.018) 125ml | Детская бутылка пластмассовый  (RBT-705)  160ml | Детская бутылка пластмассовый (ALGO 7,17,018) 125ml | Детская бутылка пластмассовый (RBT-705) 160ml | Детская бутылка пластмассовый (RBT-705) 160ml (7.17.028) | Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621) | Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621) (7.17.035) | Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION) | Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1019</v>
+      </c>
+      <c r="H22" t="n">
+        <v>16434080.56</v>
+      </c>
+      <c r="I22" t="n">
+        <v>939</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20854553.61999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>80</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1290212.40902846</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>03307001002000000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Гигиеник салфеткалар (нам ва қурутувчи )</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Влажные салфетки (120 штук) | Влажные салфетки (15 штук) | Влажные салфетки (72 штук) | Влажные салфетки «Aqua Touch» | Салфетка влажный   120 шт | Салфетка влажный   72 шт | Салфетка влажный 120 шт | Салфетка влажный 72 шт</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>13472</v>
+      </c>
+      <c r="H23" t="n">
+        <v>34149571.44</v>
+      </c>
+      <c r="I23" t="n">
+        <v>12989</v>
+      </c>
+      <c r="J23" t="n">
+        <v>44113125.25999996</v>
+      </c>
+      <c r="K23" t="n">
+        <v>483</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1224335.139958432</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>03304011006000000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Бадан учун крем</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>БОРО ПЛЮС БЕЗ ЗАПАХА Крем 25мл туба №1(1х1) | БОРО ПЛЮС Крем для ног интенсивного действия 50мл туба №1(1х1) | БОРО ПЛЮС РЕГУЛЯРНЫЙ Крем 25мл туба №1(1х1) | БОРО ПЛЮС ТРАВЯНОЙ Крем 25мл туба №1(1х1) | Крем детский  под подгузник" PAPPY PAMPER" 45мл | Крем детский  под подгузник" PAPPY PAMPER" 80мл | Крем детский под подгузник" PAPPY PAMPER" 45мл | Крем детский под подгузник" PAPPY PAMPER" 80мл</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1984</v>
+      </c>
+      <c r="H24" t="n">
+        <v>17009462.64</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1747</v>
+      </c>
+      <c r="J24" t="n">
+        <v>19518571.43</v>
+      </c>
+      <c r="K24" t="n">
+        <v>237</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2031876.333508065</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03305005001431004</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Шампунь (барча турлари) Антипедикулёзный Шампунь, картон қутида, ПЭТ бутилка 110 г.</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Шампунь "PEPILINO"  265мл  Бегемотик Гоша | Шампунь "PEPILINO"  265мл  Дельфинчик Вилли | Шампунь "PEPILINO"  265мл  Зайка степашка | Шампунь "PEPILINO"  265мл  Медвежонок Пух | Шампунь "PEPILINO" 265мл Бегемотик Гоша | Шампунь "PEPILINO" 265мл Дельфинчик Вилли | Шампунь "PEPILINO" 265мл Зайка степашка | Шампунь "PEPILINO" 265мл Медвежонок Пух</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1339285.7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>180</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1526785.71</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20</v>
+      </c>
+      <c r="L25" t="n">
+        <v>133928.57</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>07010001004000000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Шиша (бутилка)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Детские бутылки стеклянные 120 ml. Бренд: ALGO. Артикул:7.17.032 | Детские бутылки стеклянные 240 ml. Бренд: ALGO. Артикул:7.17.031 | Детские бутылки стеклянные 60 ml. Бренд: Rabito. Model:  Артикул:7.17.023 | Детские бутылки стеклянные из безцвет стекла 150ml (7.17.043) | Детские бутылки стеклянные из безцвет стекла 240ml (7.17.044) | Детские бутылки стеклянные из безцвет стекла 240ml (RBT-207) (7,17,044) | №1 Детские бутылки стеклянные 240 ml. Бренд: Rabito. Артикул:7.17.035</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1248</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21490337.15</v>
+      </c>
+      <c r="I26" t="n">
+        <v>169</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4828571.439999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1079</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18580187.32760417</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03926001020000000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Держатель для сосок (JK BABY модел с колокльчика ) | Держатель для сосок (JM BABY простой) | Детские бутылки (А-2 ) 260 мл | Детские бутылки (А-3-Т 125 мл) | Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003 | Соски из силикона (RBT-310) | Соски из силикона (RBT-310) (7.23.035)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>504</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3240000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>756</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6613749.949999998</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-252</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1620000</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>09603002002000000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Тиш чўткаси</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>зубная щетка № 11B | зубная щетка № 14А | зубная щетка № 2F | зубная щетка № 4F | зубная щетка № 5Д | зубная щетка № 8Д</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>5448</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12528214.27</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3828</v>
+      </c>
+      <c r="J28" t="n">
+        <v>11546785.27000004</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1620</v>
+      </c>
+      <c r="L28" t="n">
+        <v>3725350.058259912</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>03304021006000000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Косметика мойи</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Teddy Болалар ёғи (Алоэ) 100 мл | Teddy Болалар ёғи (Гипоаллерген) 100 мл | Teddy Болалар ёғи (Лаванда) 100 мл | Teddy Болалар ёғи (Ромашка) 100 мл | Детская масло SHOFF 100gr | Детская масло SHOFF 50gr</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>3408</v>
+      </c>
+      <c r="H29" t="n">
+        <v>24395574.86</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2743</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25332589.18000002</v>
+      </c>
+      <c r="K29" t="n">
+        <v>665</v>
+      </c>
+      <c r="L29" t="n">
+        <v>4760286.761120892</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>03926999004000000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Молокоотсос (ПВХ)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Молокоотос Mummy модель 1134 | Молокоотсос  (А1357) | Молокоотсос (A1357) | Молокоотсос (А-240) | Молокоотсос (А1357) | Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>2136</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25432285.73</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1696</v>
+      </c>
+      <c r="J30" t="n">
+        <v>19600000.05999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>440</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5238860.35636704</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06602001001000001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ҳассалар, ўриндиқ ҳассалар ва бошқа шунга ўхшаш буюмлар хасса</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Хасса (трость) 4х опорная №1 Серия - 1, Срок годности 01/2030 | Хасса (трость) деревянная №1 Серия - 1, Срок годности 01/2030 | Хасса (трость) подлокотная №1 Серия - 1, Срок годности 01/2030 | Хасса (трость) регулируемая №1  Серия - 1, Срок годности 01/2030 | Хасса (трость) регулируемая №1 Цвет Серый Китай | Хасса (трость) регулируемая №1 Цвет Черный Китай</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>642</v>
+      </c>
+      <c r="H31" t="n">
+        <v>24056000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>637</v>
+      </c>
+      <c r="J31" t="n">
+        <v>29271000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>187352.0249221183</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09619001002000000</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Аёллар учун санитария тампонлари</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>deasy | mira | Женские прокладки (онажон) | Женские прокладки (роза) | Тампоны женские гиг. «LINDA» картонный упаковка №10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>51525000</v>
+      </c>
+      <c r="I32" t="n">
+        <v>28296</v>
+      </c>
+      <c r="J32" t="n">
+        <v>40373213.97000006</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6704</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9869245.714285715</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>02712001002000000</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Вазелин косметический</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Вазелин косметический 100гр | Вазелин косметический 100гр в баночках | Вазелин косметический 20гр | Вазелин косметический 20гр в тубах | Вазелин косметический 40гр</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>17200</v>
+      </c>
+      <c r="H33" t="n">
+        <v>52057142.84999999</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10121</v>
+      </c>
+      <c r="J33" t="n">
+        <v>44842410.70000003</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7079</v>
+      </c>
+      <c r="L33" t="n">
+        <v>21425146.17646221</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>09619001001000000</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Аёллар учун санитария ёстиқчалари (шу жумладан эркаклар учун)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Вкладыши для груди RABITO (Артикул 7.31.005) | Гигиенические женские прокладки LIBRESSE Maxi Night wing sw 6x20pcs | Гигиенические прокладки "Amelie" | Гигиенические прокладки "Дива" | Женские гигиенические прокладки дива мама</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>8244</v>
+      </c>
+      <c r="H34" t="n">
+        <v>47020571.44</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3490</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31253571.29000003</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4754</v>
+      </c>
+      <c r="L34" t="n">
+        <v>27114968.05261523</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>04014001003000000</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Презервативлар</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Презервативы из натурального латекса торговой марки "Lovit" (ANATOMIC) | Презервативы из натурального латекса торговой марки "Lovit" (Classic) | Презервативы из натурального латекса торговой марки "Lovit" (DOTTED) | Презервативы из натурального латекса торговой марки "Lovit" (RIBBED) | Презервативы из натурального латекса торговой марки "Lovit" (ULTRA THIN)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>5184</v>
+      </c>
+      <c r="H35" t="n">
+        <v>9534857.129999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3434598.25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4104</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7548428.561249999</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>04014001005000000</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Резинадан бурун тозалагич</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Аспиратор (носочиска) MUMMY 1130-1 шт | Аспиратор (носочиска) MUMMY 1130-1 шт - | Аспиратор (носочиска) MUMMY 1130-1 шт -2025 | Аспиратор (носочиска) MUMMY 1133 шт | Носочистка  "MUMMY" модель 1133</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>3720</v>
+      </c>
+      <c r="H36" t="n">
+        <v>21428571.45</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3607</v>
+      </c>
+      <c r="J36" t="n">
+        <v>29257142.95999998</v>
+      </c>
+      <c r="K36" t="n">
+        <v>113</v>
+      </c>
+      <c r="L36" t="n">
+        <v>650921.6596370967</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>02106999028180009</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Classic Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (апельсин) | Аскорбинка 3,0 №10 (классик) | Аскорбинка 3,0 №10 (малина) | Аскорбинка 3,0 №10 (смородина) | Аскорбинка 3,0 №10 (яблоко)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="I37" t="n">
+        <v>440</v>
+      </c>
+      <c r="J37" t="n">
+        <v>603571.49</v>
+      </c>
+      <c r="K37" t="n">
+        <v>860</v>
+      </c>
+      <c r="L37" t="n">
+        <v>946000</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>03307001038000000</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ванна қабул қилиш учун восита</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Teddy Болалар упаси (Лаванда) 50 гр | Teddy Чўмилиш тузи (Лаванда) 500 гр | Teddy Чўмилиш тузи (Ромашка) 500 гр | Teddy Чўмилиш тузи (Хвоя) 500 гр | Teddy Чўмилиш тузи (Череда) 500 гр</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>128</v>
+      </c>
+      <c r="H38" t="n">
+        <v>793600</v>
+      </c>
+      <c r="I38" t="n">
+        <v>81</v>
+      </c>
+      <c r="J38" t="n">
+        <v>550714.28</v>
+      </c>
+      <c r="K38" t="n">
+        <v>47</v>
+      </c>
+      <c r="L38" t="n">
+        <v>291400</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>06214001014000000</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Тиббий эластик тасма</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(01942-2)Пояс медицинский эластичный, согревающий, Размер 2 | (01942-3)Пояс медицинский эластичный, согревающий, Размер 3 | Пояс медицинский эластичный, согревающий, Размер 2 | Пояс медицинский эластичный, согревающий, Размер 3 | Пояс медицинский эластичный, согревающий, Размер 4</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>60</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>42</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1552500.050000001</v>
+      </c>
+      <c r="K39" t="n">
+        <v>18</v>
+      </c>
+      <c r="L39" t="n">
+        <v>594000</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>04014001004000000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Резинали кўкрак помпаси</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Грудная накладка  MUMMY - 1132 -шт | Грудная накладка  MUMMY - 1132 -шт  04.2025 | Грудная накладка MUMMY - 1132 | Грудная накладка MUMMY - 1132 -шт</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>912</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3257142.830000001</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1065</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4834821.41</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-153</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-546428.566875</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>07020999004000000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Болалар шишали бутилка</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Детские бутылки стеклянные (В1376) | Детские бутылки стеклянные (В1377) | Детские бутылки стеклянные (В1377)) | Детские бутылки стеклянные (В1378)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>312</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5297142.859999999</v>
+      </c>
+      <c r="I41" t="n">
+        <v>312</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6428571.450000001</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>03004900002002000</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D-Пантенол, гидролизат, магния хлорид, ниацинамид, пиридоксин, рибофлавин, сульфат цинка, хлорид марганца - A11A</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Жидкий пластырь 100 мл С экстрактом подорожника в коробочке | Жидкий пластырь 50мл в коробочке | Пантенол взрослый 130мл в коробочке | Пантенол детский 130мл в коробочке</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>264</v>
+      </c>
+      <c r="H42" t="n">
+        <v>9360000.010000002</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>264</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9360000.010000002</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>03304999024000000</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Маникюр ва педикюр учун косметика маҳсулотлари</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Маникюрный  набор (С-11) | Маникюрный набор  (FZ-47) | Маникюрный набор (FZ-47) | Маникюрный набор (С-11)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>144</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2455714.28</v>
+      </c>
+      <c r="I43" t="n">
+        <v>168</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3450000.020000001</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-409285.7133333334</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>05601001002000000</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Пахтали таёқча</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ПТ MG Cotton п.п. квадрат 100д | ПТ MG Cotton п.п. квадрат 200д | №1 Ватные палочки для ушей (ухочистка) BRICK 55</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>3069</v>
+      </c>
+      <c r="H44" t="n">
+        <v>14379464.29</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2298</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11594464.43999998</v>
+      </c>
+      <c r="K44" t="n">
+        <v>771</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3612436.287908113</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>02106999028180016</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза малина таъми билан</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №5 (апельсин) | Аскорбинка 3,0 №5 (малина) | Аскорбинка 3,0 №5 (яблоко)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H45" t="n">
+        <v>960000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1046428.59</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-200</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>03305005001000000</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Шампунь (барча турлари)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Шампунь "Антипедикулезный"110мл (комплект) | Шампунь "Антипедикулезный"130мл комплект | Шампунь "Антипедикулезный"60мл (комплект)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>600</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>393</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2579553.519999999</v>
+      </c>
+      <c r="K46" t="n">
+        <v>207</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1164375</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>03005001002001001</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 1м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Марля медицинская отбеленная в кусках, 1 м | Марля медицинская отбеленная в кусках, 1 м х 84 см | Марля медицинская отбеленная в кусках, 2 м</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
         <v>500</v>
       </c>
-      <c r="K2" s="13" t="n">
-        <v>26531338.3600377</v>
-      </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="H47" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>510</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1095535.74</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10701001001000000</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bino va inshootlar ijaraga berish xizmati</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ijara to'lovi DEKABR  oyi 2025 yil | Ijara to'lovi NOYABR  oyi 2025 yil | Ijara to'lovi OKTABR  oyi 2025 yil</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1071428.58</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1071428.58</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>Omborda bor</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="n">
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>08414002002000000</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ҳаво ёки вакуум насослари, компрессорлар, қурилиш соҳасида ишлатилмайдиган</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>09018010033000000</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Ўзбекистон Республикаси Соғлиқни сақлаш вазирлигининг 06.29.2016 йилдаги  60-сонли буйруғи билан тасдиқланган рўйхатга киритилган, тиббий буюмлар</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 1": [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
-• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 2": [Kirim: 400 | Chiqim: 0 | Qoldiq: 400]
-• "(01908) Трусы медицинские после обрезания для мальчиков,  Размер 3": [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]
-• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 1": [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 2": [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• "(01919) Корректор осанки детский,  с рёбрами жёсткости, Размер 3": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01908) Трусы медицинские после обрезания для мальчиков, Размер 2: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
-• (01908) Трусы медицинские после обрезания для мальчиков, Размер 3: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• (01908-1)Трусы медицинские для мальчиков Размер 1: [Kirim: 0 | Chiqim: 16 | Qoldiq: -16]
-• (01908-2)Трусы медицинские для мальчиков Размер 2: [Kirim: 0 | Chiqim: 46 | Qoldiq: -46]
-• (01908-3)Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 32 | Qoldiq: -32]
-• (01909) Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• (01909)Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01912) Воротник ортопедический жесткий, Размер 1: [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
-• (01912) Воротник ортопедический жесткий, Размер 2: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01912) Воротник ортопедический жесткий, Размер 3: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
-• (01912) Воротник ортопедический жесткий, Размер 4: [Kirim: 4 | Chiqim: 0 | Qoldiq: 4]
-• (01912-2)Воротник ортопедический жесткий, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01912-4)Воротник ортопедический жесткий, Размер 4: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01914-2)Корректор осанки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
-• (01914-3)Корректор осанки, Размер 3: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• (01914-4)Корректор осанки, Размер 4: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
-• (01918) Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• (01918) Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• (01918) Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01918-2)Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
-• (01918-3)Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
-• (01918-4)Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 0 | Chiqim: 14 | Qoldiq: -14]
-• (01919-1)Корректор осанки детский, с рёбрами жёсткости, Размер 1: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01919-2)Корректор осанки детский, с рёбрами жёсткости, Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01919-3)Корректор осанки детский, с рёбрами жёсткости, Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01921) Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 30 | Chiqim: 0 | Qoldiq: 30]
-• (01921-1)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01921-2)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01921-3)Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01924) Воротник ортопедический, надувной: [Kirim: 77 | Chiqim: 0 | Qoldiq: 77]
-• (01924)Воротник ортопедический,надувной: [Kirim: 0 | Chiqim: 24 | Qoldiq: -24]
-• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01930) Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 50 | Chiqim: 0 | Qoldiq: 50]
-• (01930-1)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01930-2)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• (01930-3)Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
-• (01947) Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• (01947)Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]
-• (01950) Корректор осанки (универсальный): [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01950)Корректор осанки (универсальный): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01953)Корректор осанки, детский. (универсальный): [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• Shprist 50ml: [Kirim: 840 | Chiqim: 110 | Qoldiq: 730]
-• Браслет Идентификационный Голубого Цвета: [Kirim: 500 | Chiqim: 8 | Qoldiq: 492]
-• Браслет Идентификационный Розового Цвета: [Kirim: 500 | Chiqim: 10 | Qoldiq: 490]
-• Воротник ортопедический жесткий, Размер 1: [Kirim: 5 | Chiqim: 0 | Qoldiq: 5]
-• Воротник ортопедический жесткий, Размер 2: [Kirim: 5 | Chiqim: 9 | Qoldiq: -4]
-• Воротник ортопедический жесткий, Размер 3: [Kirim: 4 | Chiqim: 8 | Qoldiq: -4]
-• Воротник ортопедический жесткий, Размер 4: [Kirim: 4 | Chiqim: 6 | Qoldiq: -2]
-• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 1: [Kirim: 10 | Chiqim: 22 | Qoldiq: -12]
-• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 2: [Kirim: 10 | Chiqim: 45 | Qoldiq: -35]
-• Воротник ортопедический мягкий для взрослых (шина шанца), Размер 3: [Kirim: 10 | Chiqim: 40 | Qoldiq: -30]
-• Воротник ортопедический мягкий, для детей (шина шанца), Размер 1: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• Воротник ортопедический мягкий, для детей (шина шанца), Размер 2: [Kirim: 0 | Chiqim: 9 | Qoldiq: -9]
-• Воротник ортопедический мягкий, для детей (шина шанца), Размер 3: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• Воротник ортопедический мягкий, для детей, Размер 1: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
-• Воротник ортопедический мягкий, для детей, Размер 2: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
-• Воротник ортопедический мягкий, для детей, Размер 3: [Kirim: 16 | Chiqim: 0 | Qoldiq: 16]
-• Воротник ортопедический, надувной: [Kirim: 56 | Chiqim: 7 | Qoldiq: 49]
-• Воротник ортопедический,надувной: [Kirim: 0 | Chiqim: 84 | Qoldiq: -84]
-• Канюля Кислородная, Стерильный для Однократного Применения для Подростковый (Child): [Kirim: 600 | Chiqim: 383 | Qoldiq: 217]
-• Катетеры Кислородные, Стерильные для Однократного Применения для Взрослых (Adult): [Kirim: 400 | Chiqim: 1,060 | Qoldiq: -660]
-• Катетеры Кислородные, Стерильный для Однократного Применения для Взрослый (Adult): [Kirim: 700 | Chiqim: 0 | Qoldiq: 700]
-• Корректор осанки (универсальный): [Kirim: 20 | Chiqim: 12 | Qoldiq: 8]
-• Корректор осанки детский, с рёбрами жёсткости, Размер 1: [Kirim: 10 | Chiqim: 18 | Qoldiq: -8]
-• Корректор осанки детский, с рёбрами жёсткости, Размер 2: [Kirim: 20 | Chiqim: 38 | Qoldiq: -18]
-• Корректор осанки детский, с рёбрами жёсткости, Размер 3: [Kirim: 20 | Chiqim: 26 | Qoldiq: -6]
-• Корректор осанки, Размер 1: [Kirim: 40 | Chiqim: 10 | Qoldiq: 30]
-• Корректор осанки, Размер 2: [Kirim: 40 | Chiqim: 22 | Qoldiq: 18]
-• Корректор осанки, Размер 3: [Kirim: 40 | Chiqim: 22 | Qoldiq: 18]
-• Корректор осанки, Размер 4: [Kirim: 40 | Chiqim: 12 | Qoldiq: 28]
-• Корректор осанки, детский. (универсальный): [Kirim: 20 | Chiqim: 11 | Qoldiq: 9]
-• Корректор осанки, с рёбрами жёсткости, Размер 2: [Kirim: 20 | Chiqim: 37 | Qoldiq: -17]
-• Корректор осанки, с рёбрами жёсткости, Размер 3: [Kirim: 20 | Chiqim: 57 | Qoldiq: -37]
-• Корректор осанки, с рёбрами жёсткости, Размер 4: [Kirim: 20 | Chiqim: 32 | Qoldiq: -12]
-• Маска Кислородная, Стерильная для Однократного Применения для Взрослый: [Kirim: 200 | Chiqim: 47 | Qoldiq: 153]
-• Маска Кислородная, Стерильная для Однократного Применения для Детский: [Kirim: 200 | Chiqim: 49 | Qoldiq: 151]
-• Мочеприемник Прикроватный с Т-образным Сливным Клапаном, Стерильный для Однократного Применения Объемом 2 л: [Kirim: 500 | Chiqim: 320 | Qoldiq: 180]
-• Набор для ингалятора (Маска кислородная) Disposable Nebulizer для взрослых: [Kirim: 200 | Chiqim: 84 | Qoldiq: 116]
-• Набор для ингалятора (Маска кислородная) Disposable Nebulizer для детский: [Kirim: 200 | Chiqim: 200 | Qoldiq: 0]
-• Небулайзер Компрессорный NIMO модель HNK-NBL-S с Комплектующими: [Kirim: 48 | Chiqim: 14 | Qoldiq: 34]
-• Перчатки ARMOUR Хирургические, Латексные, Стерильный для Однократного Применения, Размер: 7,5: [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
-• Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5: [Kirim: 0 | Chiqim: 500 | Qoldiq: -500]
-• Повязка медицинская из неопрена для фиксации коленного сустава  (регулируемый) Универсальный: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• Повязка медицинская из неопрена для фиксации коленного сустава (регулируемый) Универсальный: [Kirim: 0 | Chiqim: 54 | Qoldiq: -54]
-• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 1: [Kirim: 10 | Chiqim: 12 | Qoldiq: -2]
-• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 2: [Kirim: 10 | Chiqim: 27 | Qoldiq: -17]
-• Повязка медицинская из неопрена для фиксации коленного сустава (шарнирная), Размер 3: [Kirim: 10 | Chiqim: 23 | Qoldiq: -13]
-• Повязка медицинская из неопрена для фиксации лучезапястного сустав: [Kirim: 20 | Chiqim: 39 | Qoldiq: -19]
-• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 11 SURGEON: [Kirim: 250 | Chiqim: 340 | Qoldiq: -90]
-• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 15 SURGEON: [Kirim: 250 | Chiqim: 250 | Qoldiq: 0]
-• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 22 SURGEON: [Kirim: 500 | Chiqim: 580 | Qoldiq: -80]
-• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 23 SURGEON: [Kirim: 500 | Chiqim: 500 | Qoldiq: 0]
-• Скальпель Хирургическая, Стерильная для Одноразового Использования из Нержавеющий стали, Размер: 24 SURGEON: [Kirim: 250 | Chiqim: 250 | Qoldiq: 0]
-• Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 11  SURGEON: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
-• Скальпель Хирургическая, Стерильный для Одноразового Использования из Нержавеющий стали, Размер: 22  SURGEON: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
-• Трусы медицинские для мальчиков Размер 1: [Kirim: 0 | Chiqim: 417 | Qoldiq: -417]
-• Трусы медицинские для мальчиков Размер 2: [Kirim: 0 | Chiqim: 924 | Qoldiq: -924]
-• Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 821 | Qoldiq: -821]
-• Трусы медицинские для мальчиков Размер 3Трусы медицинские для мальчиков Размер 3: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• Трусы медицинские после обрезания для мальчиков, Размер 1: [Kirim: 400 | Chiqim: 5 | Qoldiq: 395]
-• Трусы медицинские после обрезания для мальчиков, Размер 2: [Kirim: 600 | Chiqim: 44 | Qoldiq: 556]
-• Трусы медицинские после обрезания для мальчиков, Размер 3: [Kirim: 400 | Chiqim: 9 | Qoldiq: 391]</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n">
-        <v>12094</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>138336000</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>7858</v>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>111617589.0499999</v>
-      </c>
-      <c r="J3" s="14" t="n">
-        <v>4236</v>
-      </c>
-      <c r="K3" s="13" t="n">
-        <v>48453059.03753927</v>
-      </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803 | №1 Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1040</v>
+      </c>
+      <c r="H49" t="n">
+        <v>94800000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>304</v>
+      </c>
+      <c r="J49" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="K49" t="n">
+        <v>736</v>
+      </c>
+      <c r="L49" t="n">
+        <v>67089230.76923077</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>Omborda bor</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>03923001007000000</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Пластмассадан тайёрланган идишлар, бутилкалар, флаконлар ва шунга ўхшаш идишлар</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="n">
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>03926999438000000</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Бурун бўшлиғини ювиш учун мослама</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Аспиратор (носочиска) MUMMY1133 | Носочистка HELLO</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>372</v>
+      </c>
+      <c r="H50" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>23</v>
+      </c>
+      <c r="J50" t="n">
+        <v>821428.5800000001</v>
+      </c>
+      <c r="K50" t="n">
+        <v>349</v>
+      </c>
+      <c r="L50" t="n">
+        <v>5066129.032258064</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>07013004008000000</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Шиша бутилкача</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Детские бутылки Стеклянные (В1377) | Детские бутылки Стеклянные (В1378)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>336</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6274285.72</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>336</v>
+      </c>
+      <c r="L51" t="n">
+        <v>6274285.72</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>03926001155000000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Спринцовка (ПВХ)</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 | Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>240</v>
+      </c>
+      <c r="H52" t="n">
+        <v>9521781.43</v>
+      </c>
+      <c r="I52" t="n">
+        <v>222</v>
+      </c>
+      <c r="J52" t="n">
+        <v>11892857.18</v>
+      </c>
+      <c r="K52" t="n">
+        <v>18</v>
+      </c>
+      <c r="L52" t="n">
+        <v>714133.6072499999</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>08414002001000000</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ҳаво ёки вакуум насослари, компрессорлар (барча турлари)</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Молокоотсос вакуумный электический  (RH-803) | Молокоотсос вакуумный электический (RH-803)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>200</v>
+      </c>
+      <c r="H53" t="n">
+        <v>25714285.71</v>
+      </c>
+      <c r="I53" t="n">
+        <v>200</v>
+      </c>
+      <c r="J53" t="n">
+        <v>29464285.72</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>03304011011004003</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Юз ва танани юмшатувчи, 75 мл</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Крем увлажняющий для лица и тела "Нежный", | Крем увлажняющий для лица и тела "Нежный", 75 ml</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>392857.14</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>463571.43</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04803001001000000</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Қоғоз салфетка</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>полотенца рулонные</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>8400</v>
+      </c>
+      <c r="H55" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J55" t="n">
+        <v>41772321.48999999</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5357142.857142857</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>03304011011000000</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Крем детский 50мл</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4107142.86</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2490</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3334821.4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1510</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1550446.42965</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>04015001004000000</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Жаррохлик қўлқопи</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3450</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7700892.890000002</v>
+      </c>
+      <c r="K57" t="n">
+        <v>550</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1031250</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>03005001003000000</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Бинт</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Бинт тканный нестерильный GT 7m x 14cm</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6277500</v>
+      </c>
+      <c r="I58" t="n">
+        <v>2692</v>
+      </c>
+      <c r="J58" t="n">
+        <v>7210714.259999998</v>
+      </c>
+      <c r="K58" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>18600</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>04015001002000000</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Тиббиёт қўлқоплари</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Перчатки Медицинские, Нитриловые Чёрного Цвета, Нестерильные для Однократного Применения LDH Glove, Размер:L</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H59" t="n">
+        <v>625000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J59" t="n">
+        <v>714285.7200000002</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>02106999028180003</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза олма таъми билан</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №5 (яблоко)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H60" t="n">
+        <v>960000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>800</v>
+      </c>
+      <c r="J60" t="n">
+        <v>463392.8699999999</v>
+      </c>
+      <c r="K60" t="n">
+        <v>800</v>
+      </c>
+      <c r="L60" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>02106999028180011</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза апельсин таъми билан</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №5 (апельсин)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H61" t="n">
+        <v>960000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>800</v>
+      </c>
+      <c r="J61" t="n">
+        <v>463392.8699999999</v>
+      </c>
+      <c r="K61" t="n">
+        <v>800</v>
+      </c>
+      <c r="L61" t="n">
+        <v>480000</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>01806001007000000</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Шоколадли тўпламлар</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Chokovita N°60</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H62" t="n">
+        <v>48450000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>772</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34464285.75999999</v>
+      </c>
+      <c r="K62" t="n">
+        <v>528</v>
+      </c>
+      <c r="L62" t="n">
+        <v>19678153.84615384</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02106999028180012</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (апельсин)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>340</v>
+      </c>
+      <c r="J63" t="n">
+        <v>487500.04</v>
+      </c>
+      <c r="K63" t="n">
+        <v>960</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>02106999028180001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (яблоко)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>340</v>
+      </c>
+      <c r="J64" t="n">
+        <v>487500.04</v>
+      </c>
+      <c r="K64" t="n">
+        <v>960</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>02106999028180005</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (смородина)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>340</v>
+      </c>
+      <c r="J65" t="n">
+        <v>487500.04</v>
+      </c>
+      <c r="K65" t="n">
+        <v>960</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>02106999028180014</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза билан</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (малина)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1430000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>340</v>
+      </c>
+      <c r="J66" t="n">
+        <v>487500.04</v>
+      </c>
+      <c r="K66" t="n">
+        <v>960</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>02106999028180007</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза Қорағат таъми билан</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №5 (смородина)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>400</v>
+      </c>
+      <c r="J67" t="n">
+        <v>232142.8699999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>600</v>
+      </c>
+      <c r="L67" t="n">
+        <v>360000</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>02007002003000000</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Мармелад</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Vita Buum life</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>720</v>
+      </c>
+      <c r="H68" t="n">
+        <v>28944000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>638</v>
+      </c>
+      <c r="J68" t="n">
+        <v>28482142.90999999</v>
+      </c>
+      <c r="K68" t="n">
+        <v>82</v>
+      </c>
+      <c r="L68" t="n">
+        <v>3296400</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>02106999028180023</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Биологически активные добавки к пище NARPAY VITA ZONE Vanilla Таблетки аскорбиновой кислоты с глюкозой</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Аскорбинка 3,0 №10 (ваниль)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>500</v>
+      </c>
+      <c r="H69" t="n">
+        <v>550000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>500</v>
+      </c>
+      <c r="L69" t="n">
+        <v>550000</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>03005001002001002</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 2 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Марля медицинская отбеленная в кусках, 2 м</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>500</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>500</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>02106999028199012</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Биологик фаол қўшимчалар овқат учун NUROMON MED Мойчечак гуллари кукунда</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Ромашка чай №15</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>450</v>
+      </c>
+      <c r="H71" t="n">
+        <v>883930.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>269</v>
+      </c>
+      <c r="J71" t="n">
+        <v>960714.3300000002</v>
+      </c>
+      <c r="K71" t="n">
+        <v>181</v>
+      </c>
+      <c r="L71" t="n">
+        <v>355536.49</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>04016001027000000</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Металл қўллаб-қувватлаш оёқ учун резина қистирма</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Наконечник 19мм №1 Китай</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>400</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1428580</v>
+      </c>
+      <c r="I72" t="n">
+        <v>290</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1346428.56</v>
+      </c>
+      <c r="K72" t="n">
+        <v>110</v>
+      </c>
+      <c r="L72" t="n">
+        <v>392859.5</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>03005001002001003</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 3 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Марля медицинская отбеленная в кусках, 3 м</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>400</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>400</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2040000</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>01509001001000000</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Зайтун мойи (тозаланган ёки тозаланмаган)</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Масло оливковое очищенное EXTRA VIRGIN OLIVE OIL 12x250ML TM Marioliva</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>240</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6215357.140000001</v>
+      </c>
+      <c r="I74" t="n">
+        <v>197</v>
+      </c>
+      <c r="J74" t="n">
+        <v>7387500</v>
+      </c>
+      <c r="K74" t="n">
+        <v>43</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1113584.820916667</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>09605002003000000</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Саёҳат тўпламлари (шахсий гигиена, кийим ёки пойабзал учун)</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>№1 Гигиенический набор для малышей RBT-409</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>176</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2452107.43</v>
+      </c>
+      <c r="I75" t="n">
+        <v>176</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3614285.72</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>08213001002000000</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Қайчи (барча турдаги ва фойдаланиш мақсадлари учун)</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Маникюрний набор BABY CARE KIT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>144</v>
+      </c>
+      <c r="H76" t="n">
+        <v>2468571.42</v>
+      </c>
+      <c r="I76" t="n">
+        <v>120</v>
+      </c>
+      <c r="J76" t="n">
+        <v>2464285.73</v>
+      </c>
+      <c r="K76" t="n">
+        <v>24</v>
+      </c>
+      <c r="L76" t="n">
+        <v>411428.5699999999</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>03306001003000000</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Тиш ипи</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Зубная нить (616)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>108</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1253571.43</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>108</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1253571.43</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>03005001002001004</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Газлама медицина учун MM оқартирилган бўлакланган 5 м, полиэтилен пакет 1 дона</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Марля медицинская отбеленная в кусках, 5 м</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>100</v>
+      </c>
+      <c r="H78" t="n">
+        <v>850000</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>100</v>
+      </c>
+      <c r="L78" t="n">
+        <v>850000</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>04421001010000000</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Тиш кавлагич</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Зубная нить (616)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>60</v>
+      </c>
+      <c r="H79" t="n">
+        <v>696428.5699999999</v>
+      </c>
+      <c r="I79" t="n">
+        <v>137</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1957142.87</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-77</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-893749.9981666667</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Minus Qoldiq (Xavf!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>03402004012000000</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Юза-фаол органик моддалар (совундан ташқари), бошқалар</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>"Nihol" 250 гр.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>50</v>
+      </c>
+      <c r="H80" t="n">
+        <v>2410714.29</v>
+      </c>
+      <c r="I80" t="n">
+        <v>23</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1396428.63</v>
+      </c>
+      <c r="K80" t="n">
+        <v>27</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1301785.7166</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>03401001005009001</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Болалар совуни Bubchen мойчечак билан, 125 гр.</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Детское мыло,125 г</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>24</v>
+      </c>
+      <c r="H81" t="n">
+        <v>621428.5699999999</v>
+      </c>
+      <c r="I81" t="n">
+        <v>12</v>
+      </c>
+      <c r="J81" t="n">
+        <v>367500</v>
+      </c>
+      <c r="K81" t="n">
+        <v>12</v>
+      </c>
+      <c r="L81" t="n">
+        <v>310714.285</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>03304011011004016</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN майин парвариш 0+, таглик остидан, 150 мл</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Крем для младенцев,150 мл</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>20</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1267857.14</v>
+      </c>
+      <c r="I82" t="n">
+        <v>13</v>
+      </c>
+      <c r="J82" t="n">
+        <v>964553.58</v>
+      </c>
+      <c r="K82" t="n">
+        <v>7</v>
+      </c>
+      <c r="L82" t="n">
+        <v>443749.999</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>03304011014002001</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун молочко  Bubchen болалар учун каритэ ва кунгабоқар ёғи билан, ПЭТ флакон 200 мл.</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Молочко,200 мл</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>16</v>
+      </c>
+      <c r="H83" t="n">
+        <v>814285.71</v>
+      </c>
+      <c r="I83" t="n">
+        <v>11</v>
+      </c>
+      <c r="J83" t="n">
+        <v>660982.1499999999</v>
+      </c>
+      <c r="K83" t="n">
+        <v>5</v>
+      </c>
+      <c r="L83" t="n">
+        <v>254464.284375</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>• .Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт.: [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• Бутылка для детс.питание "MUMMY" обье 80 мл 1074-1 кор.-1шт: [Kirim: 240 | Chiqim: 2,017 | Qoldiq: -1,777]
-• Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128-  шт: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
-• Бутылка плас-вые для кормление 300мл/ "MUMMY" 1128- шт: [Kirim: 0 | Chiqim: 435 | Qoldiq: -435]
-• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт: [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
-• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1078-шт.: [Kirim: 984 | Chiqim: 1,166 | Qoldiq: -182]
-• Бутылка плас-вые с ручкой для кормление 150 мл/MUMMY 1127-шт.: [Kirim: 480 | Chiqim: 518 | Qoldiq: -38]
-• Бутылка плас-вые с ручкой для кормление 240мл/ MUMMY 1079- шт: [Kirim: 528 | Chiqim: 452 | Qoldiq: 76]
-• Бутылочки для детс. питание "MUMMY"1074: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Бутылочки для детс. питание "MUMMY"1078: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Бутылочки для детс. питание "MUMMY"1079: [Kirim: 72 | Chiqim: 5 | Qoldiq: 67]
-• Бутылочки для детс. питание "MUMMY"1127: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Бутылочки для детс. питание "MUMMY"1128: [Kirim: 312 | Chiqim: 0 | Qoldiq: 312]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 1 шт: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074 шт-: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074- шт: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт: [Kirim: 1,128 | Chiqim: 0 | Qoldiq: 1,128]
-• Бутылочки для детс. питание "MUMMY"объе 80 мл 1074-1 шт-: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Детская бутылка пластмассовый    (7.17.016) 330ml: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детская бутылка пластмассовый   (ALGO 7.17.013) 125ml: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
-• Детская бутылка пластмассовый  (7.17.017) 260 ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детская бутылка пластмассовый  (ALGO 7.17.012) 280 ml: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детская бутылка пластмассовый  (ALGO 8107) 280 ml: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
-• Детская бутылка пластмассовый  (ALGO 8228) 60 ml: [Kirim: 576 | Chiqim: 0 | Qoldiq: 576]
-• Детская бутылка пластмассовый  (RBT-706)  706ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детская бутылка пластмассовый (7,17,016) 330 ml: [Kirim: 0 | Chiqim: 126 | Qoldiq: -126]
-• Детская бутылка пластмассовый (7,17,017) 260 ml: [Kirim: 0 | Chiqim: 92 | Qoldiq: -92]
-• Детская бутылка пластмассовый (7.17.016) 330 ml: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детская бутылка пластмассовый (ALGO 8107) 280 ml: [Kirim: 0 | Chiqim: 508 | Qoldiq: -508]
-• Детская бутылка пластмассовый (ALGO 8228) 60 ml: [Kirim: 0 | Chiqim: 1,270 | Qoldiq: -1,270]
-• Детская бутылка пластмассовый (RBT-706) 706ml (7.17.027): [Kirim: 0 | Chiqim: 82 | Qoldiq: -82]
-• Детская бутылка пластмассовый 125ml Бренд: ALGO 8108 (7.17.013): [Kirim: 288 | Chiqim: 635 | Qoldiq: -347]
-• Детская бутылка пластмассовый Бренд: ALGO. Model: 8228 60ml (7.17.042): [Kirim: 1,152 | Chiqim: 0 | Qoldiq: 1,152]
-• Детские  бутылки  180 мл (DDE-1035): [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
-• Детские  бутылки  270 мл (DDE-1036): [Kirim: 210 | Chiqim: 0 | Qoldiq: 210]
-• Детские  бутылки (200): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские  бутылки (248): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детские  бутылки ONLY BABY NATURAL 125 мл (А-3): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детские  бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детские бутилки (248): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутилки (249): [Kirim: 288 | Chiqim: 54 | Qoldiq: 234]
-• Детские бутилки (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутилки (360): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки  (200): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки  (201): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки  (202): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки  (249): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки (200) 180ml: [Kirim: 0 | Chiqim: 136 | Qoldiq: -136]
-• Детские бутылки (201): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки (201) 240ml: [Kirim: 0 | Chiqim: 136 | Qoldiq: -136]
-• Детские бутылки (202): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Детские бутылки (202) 300ml: [Kirim: 0 | Chiqim: 72 | Qoldiq: -72]
-• Детские бутылки (248): [Kirim: 144 | Chiqim: 716 | Qoldiq: -572]
-• Детские бутылки (249): [Kirim: 432 | Chiqim: 954 | Qoldiq: -522]
-• Детские бутылки (358): [Kirim: 864 | Chiqim: 1,296 | Qoldiq: -432]
-• Детские бутылки (360): [Kirim: 1,584 | Chiqim: 1,946 | Qoldiq: -362]
-• Детские бутылки (A-2-T): [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детские бутылки (А-2 )  260 мл: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детские бутылки (А-2 ) 260 мл: [Kirim: 0 | Chiqim: 186 | Qoldiq: -186]
-• Детские бутылки (А-3-Т 125 мл): [Kirim: 192 | Chiqim: 186 | Qoldiq: 6]
-• Детские бутылки 180 мл (DDE-1035): [Kirim: 0 | Chiqim: 107 | Qoldiq: -107]
-• Детские бутылки 270 мл (DDE-1036): [Kirim: 0 | Chiqim: 24 | Qoldiq: -24]
-• Детские бутылки ONLY BABY NATURAL 125 мл (А-3): [Kirim: 0 | Chiqim: 41 | Qoldiq: -41]
-• Детские бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 0 | Chiqim: 26 | Qoldiq: -26]
-• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7,17,036: [Kirim: 0 | Chiqim: 1,015 | Qoldiq: -1,015]
-• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Model: 9622. Артикул:7.17.036: [Kirim: 1,056 | Chiqim: 0 | Qoldiq: 1,056]
-• Детские бутылки стеклянные из безцвет стекла 120ml (9131): [Kirim: 384 | Chiqim: 12 | Qoldiq: 372]
-• Детские бутылки стеклянные из безцвет стекла 120ml (9131) (7.17.032): [Kirim: 0 | Chiqim: 796 | Qoldiq: -796]
-• Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Детские бутылки стеклянные из безцвет стекла 240ml ( Z3519) (7.17.021): [Kirim: 0 | Chiqim: 39 | Qoldiq: -39]
-• Детские бутылки стеклянные из безцвет стекла 240ml (9130): [Kirim: 384 | Chiqim: 12 | Qoldiq: 372]
-• Детские бутылки стеклянные из безцвет стекла 240ml (9130) (7.17.031): [Kirim: 0 | Chiqim: 555 | Qoldiq: -555]
-• Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374): [Kirim: 192 | Chiqim: 10 | Qoldiq: 182]
-• Детские бутылки стеклянные из безцвет стекла 60ml ( Z1374) (7.17.023): [Kirim: 0 | Chiqim: 278 | Qoldiq: -278]
-• Детские бутылки стеклянные из безцвет стекла ALGO 120ml (7.17.043): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детские бутылки стеклянные из безцвет стекла ALGO 120ml (RBT-206) (7,17,043): [Kirim: 0 | Chiqim: 196 | Qoldiq: -196]
-• Детские бутьлки  (248): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутьлки  (249): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутьлки  (358: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутьлки  (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутьлки  (360 ): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Соска-Пустышки "PANDA" силиконовая 1122: [Kirim: 720 | Chiqim: 348 | Qoldiq: 372]</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>19266</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>217341945.0000003</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>16457</v>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>241963660.569998</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>2809</v>
-      </c>
-      <c r="K4" s="13" t="n">
-        <v>31688649.61616323</v>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>03305005002018007</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Болалар шампуни BUBCHEN таъсирчан тери учун, ПЭТ бутилка 200 мл.</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Детский шампунь, 200 мл</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>16</v>
+      </c>
+      <c r="H84" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="I84" t="n">
+        <v>12</v>
+      </c>
+      <c r="J84" t="n">
+        <v>695357.16</v>
+      </c>
+      <c r="K84" t="n">
+        <v>4</v>
+      </c>
+      <c r="L84" t="n">
+        <v>196428.5725</v>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>Omborda bor</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="10" t="n">
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>03304011011004006</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Чақалоқлар учун мой, 200мл</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Масло для младенцев, 200 мл</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>16</v>
+      </c>
+      <c r="H85" t="n">
+        <v>857142.86</v>
+      </c>
+      <c r="I85" t="n">
+        <v>16</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1011428.56</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>03304011011004005</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Косметик, 75мл</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Детский косметический крем,75 мл</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>12</v>
+      </c>
+      <c r="H86" t="n">
+        <v>546428.5699999999</v>
+      </c>
+      <c r="I86" t="n">
+        <v>11</v>
+      </c>
+      <c r="J86" t="n">
+        <v>591250</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>45535.71416666666</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Omborda bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>03305005002000000</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Болалар шампуни</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Шампунь и средство для купания младенцев, 400 мл/ Bad &amp; Shampoo, 400ml</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>8</v>
+      </c>
+      <c r="H87" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="I87" t="n">
+        <v>8</v>
+      </c>
+      <c r="J87" t="n">
+        <v>919285.72</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>03304001003000000</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Бадан учун балзам</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Солнцезащитный крем для лица младенцев и детей с чувствительной кожей ФЗ 50+ 50 мл/Sensitive Gesich</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>571428.5699999999</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>668571.4399999999</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>03401002001004009</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Юз ювиш учун геллар BÜBCHEN чўмилиш учун, 200 мл</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Средство для купания младенцев,200 мл</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" t="n">
+        <v>392857.14</v>
+      </c>
+      <c r="I89" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>04016001083000000</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Резинали сўрғич</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>• Teddy Ниппел накладкаси + сўрғич: [Kirim: 630 | Chiqim: 225 | Qoldiq: 405]
-• Дет Соски (LOT-10): [Kirim: 320 | Chiqim: 650 | Qoldiq: -330]
-• Детcкие Соски (LOT-12): [Kirim: 340 | Chiqim: 340 | Qoldiq: 0]
-• Детские  соски (260): [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
-• Детские  соски (383): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские  соски (387): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские  соски для питания (285): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские  соски для питания (291): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские Cоски  (383): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские соски  для питания (285): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детские соски  для питания (291): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
-• Детские соски (038): [Kirim: 11,520 | Chiqim: 10,790 | Qoldiq: 730]
-• Детские соски (260): [Kirim: 1,008 | Chiqim: 1,056 | Qoldiq: -48]
-• Детские соски (383): [Kirim: 216 | Chiqim: 345 | Qoldiq: -129]
-• Детские соски (387): [Kirim: 576 | Chiqim: 680 | Qoldiq: -104]
-• Детские соски (LOT-10): [Kirim: 640 | Chiqim: 2 | Qoldiq: 638]
-• Детские соски для питания (285): [Kirim: 0 | Chiqim: 382 | Qoldiq: -382]
-• Детские соски для питания (291): [Kirim: 72 | Chiqim: 569 | Qoldiq: -497]
-• Соска для питание ниблер MUMMY 1129-1 шт: [Kirim: 288 | Chiqim: 5 | Qoldiq: 283]
-• Соска для питание ниблер MUMMY 1129-1 шт -: [Kirim: 360 | Chiqim: 751 | Qoldiq: -391]
-• Соска для питание ниблер MUMMY 1129-1 шт -2025: [Kirim: 108 | Chiqim: 0 | Qoldiq: 108]
-• Соска пустышка Panda c крышкой 106 шт: [Kirim: 2,220 | Chiqim: 3,864 | Qoldiq: -1,644]
-• Соска-Пустышки "PANDA"  силиконовая 1123: [Kirim: 7,200 | Chiqim: 0 | Qoldiq: 7,200]
-• Соска-Пустышки "PANDA" силиконовая 1122: [Kirim: 5,760 | Chiqim: 5,689 | Qoldiq: 71]
-• Соска-Пустышки "PANDA" силиконовая 1123: [Kirim: 0 | Chiqim: 7,669 | Qoldiq: -7,669]
-• Соски пустышки Mummy 1112: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Соски пустышки Mummy 1113: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Соски пустышки Mummy 1114: [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Соски пустышки Mummy модель 1111 в одном комплекте 2 шт: [Kirim: 216 | Chiqim: 2 | Qoldiq: 214]
-• Соски пустышки Mummy модель 1112 в одном комплекте 2 шт: [Kirim: 72 | Chiqim: 2 | Qoldiq: 70]
-• Соски пустышки Mummy модель1113 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Соски пустышки Mummy модель1115 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Соски-Пустышки "PANDA" 100: [Kirim: 5,760 | Chiqim: 12 | Qoldiq: 5,748]
-• Соски-Пустышки "PANDA" 100 шт: [Kirim: 1,440 | Chiqim: 6,386 | Qoldiq: -4,946]</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>40738</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>100886785.7</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>39419</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>110605802.9999992</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>1319</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>3266475.289368649</v>
-      </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="J89" t="n">
+        <v>231785.72</v>
+      </c>
+      <c r="K89" t="n">
+        <v>4</v>
+      </c>
+      <c r="L89" t="n">
+        <v>196428.57</v>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>Omborda bor</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>09021001001000000</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Ортопедик асбоблар (таёқчалар, бинтлар, камарлар) ёки синишларни даволаш учун (шу жумладан шиналар)</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>• "(01959) Вальгусная шина большого пальца стопы (шарнирная), пара ": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• "(01960) Вальгусная шина большого пальца стопы (носочки), пара. Размер (S)": [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01905) Вальгусная шина большого пальца стопы (ночная), пара: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
-• (01905)Вальгусная шина большого пальца стопы (ночная): [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• (01922) Тутор коленного сустава, Размер 1: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01922) Тутор коленного сустава, Размер 2: [Kirim: 24 | Chiqim: 0 | Qoldiq: 24]
-• (01922) Тутор коленного сустава, Размер 3: [Kirim: 15 | Chiqim: 0 | Qoldiq: 15]
-• (01922-2)Тутор коленного сустава, Размер 2: [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01922-3)Тутор коленного сустава, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01922d) Тутор коленного сустава, детский универсальный: [Kirim: 7 | Chiqim: 0 | Qoldiq: 7]
-• (01923) Вальгусная шина большого пальца стопы (дневной), пара: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• (01960)Вальгусная шина большого пальцастопы (носочки), пара. Размер (S): [Kirim: 0 | Chiqim: 1 | Qoldiq: -1]
-• (01963) Шина для фиксации пальцев руки, Размер 1: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01963) Шина для фиксации пальцев руки, Размер 2: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• (01963) Шина для фиксации пальцев руки, Размер 3: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• Вальгусная шина большого пальца стопы (дневной), пара: [Kirim: 20 | Chiqim: 50 | Qoldiq: -30]
-• Вальгусная шина большого пальца стопы (носочки), пара. Размер (S): [Kirim: 20 | Chiqim: 6 | Qoldiq: 14]
-• Вальгусная шина большого пальца стопы (ночная): [Kirim: 0 | Chiqim: 79 | Qoldiq: -79]
-• Вальгусная шина большого пальца стопы (ночная), пара: [Kirim: 20 | Chiqim: 2 | Qoldiq: 18]
-• Вальгусная шина большого пальца стопы (шарнирная), пара: [Kirim: 20 | Chiqim: 0 | Qoldiq: 20]
-• Вальгусная шина большого пальцастопы (носочки), пара. Размер (S): [Kirim: 0 | Chiqim: 22 | Qoldiq: -22]
-• Вальгусная шина большого пальцастопы (шарнирная), пара: [Kirim: 0 | Chiqim: 34 | Qoldiq: -34]
-• Костыли Нержавейка №2 Китай: [Kirim: 190 | Chiqim: 190 | Qoldiq: 0]
-• Тутор коленного сустава, Размер 1: [Kirim: 5 | Chiqim: 6 | Qoldiq: -1]
-• Тутор коленного сустава, Размер 2: [Kirim: 6 | Chiqim: 23 | Qoldiq: -17]
-• Тутор коленного сустава, Размер 3: [Kirim: 6 | Chiqim: 16 | Qoldiq: -10]
-• Тутор коленного сустава, детский универсальный: [Kirim: 7 | Chiqim: 7 | Qoldiq: 0]
-• Шина для фиксации пальцев руки, Размер 1: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]
-• Шина для фиксации пальцев руки, Размер 2: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]
-• Шина для фиксации пальцев руки, Размер 3: [Kirim: 0 | Chiqim: 11 | Qoldiq: -11]</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>570</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>38694000</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>472</v>
-      </c>
-      <c r="I6" s="13" t="n">
-        <v>42580503.55</v>
-      </c>
-      <c r="J6" s="14" t="n">
-        <v>98</v>
-      </c>
-      <c r="K6" s="13" t="n">
-        <v>6652652.631578947</v>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>03305005002018008</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Болалар шампуни BUBCHEN майин парвариш, ПЭТ бутилка 400 мл.</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Детский шампунь, 400 мл</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>8</v>
+      </c>
+      <c r="H90" t="n">
+        <v>657142.86</v>
+      </c>
+      <c r="I90" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" t="n">
+        <v>769285.72</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Tugagan (0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>03401002001004004</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Юз ювиш учун геллар BÜBCHEN 400 мл</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Гель для купания, 400 мл</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="n">
+        <v>785714.29</v>
+      </c>
+      <c r="I91" t="n">
+        <v>4</v>
+      </c>
+      <c r="J91" t="n">
+        <v>459642.86</v>
+      </c>
+      <c r="K91" t="n">
+        <v>4</v>
+      </c>
+      <c r="L91" t="n">
+        <v>392857.145</v>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>Omborda bor</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>00000000000000000</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Tasnif kodi</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>• Amelya oq: [Kirim: 0 | Chiqim: 2,000 | Qoldiq: -2,000]
-• Ayollar gigiyenik prokladkasi: [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
-• Best soft 120-talik: [Kirim: 0 | Chiqim: 1,200 | Qoldiq: -1,200]
-• Best soft 15-talik: [Kirim: 0 | Chiqim: 4,320 | Qoldiq: -4,320]
-• Best soft 72-talik: [Kirim: 0 | Chiqim: 1,200 | Qoldiq: -1,200]
-• Diva mamasha: [Kirim: 0 | Chiqim: 1,500 | Qoldiq: -1,500]
-• Gigiyenik mahsulotlar: [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
-• Tayyor biologik oziq-ovqat qo'shimchalari: [Kirim: 0 | Chiqim: 5,310,003 | Qoldiq: -5,310,003]
-• kattalar-bolalar tagliklari, (gigeniya va xo’jalik mahsulotlari): [Kirim: 0 | Chiqim: 500,000,000 | Qoldiq: -500,000,000]
-• Аскорбинка Витаминка C: [Kirim: 0 | Chiqim: 6,150,000 | Qoldiq: -6,150,000]
-• Бумагу и изделия бумажные санитарно-гигиенического назначения: [Kirim: 0 | Chiqim: 36,000,000 | Qoldiq: -36,000,000]
-• Гигиена ёки душ воситалари: [Kirim: 0 | Chiqim: 5,000,000 | Qoldiq: -5,000,000]
-• Гигиеник воситалар: [Kirim: 8,950,800 | Chiqim: 0 | Qoldiq: 8,950,800]
-• Гигиеник воситаларлар: [Kirim: 16,250,800 | Chiqim: 0 | Qoldiq: 16,250,800]
-• Детские гигиенические товары (бутылки для детского питания, зубогрызки , соски в ассортименте): [Kirim: 0 | Chiqim: 100,000,000 | Qoldiq: -100,000,000]
-• Детские гигиенические товары в  ассортименте: [Kirim: 209,247,300 | Chiqim: 0 | Qoldiq: 209,247,300]
-• Детские гигиенические товары в ассортименте: [Kirim: 97,698,400 | Chiqim: 0 | Qoldiq: 97,698,400]
-• Детские товары в ассортименте: [Kirim: 0 | Chiqim: 600,000,000 | Qoldiq: -600,000,000]
-• Зубные щетки в ассортименте: [Kirim: 0 | Chiqim: 13,642,800 | Qoldiq: -13,642,800]
-• Масло оливковое очищенное: [Kirim: 0 | Chiqim: 3,469,200 | Qoldiq: -3,469,200]
-• Парфюмерно-косметическая продукция и влажные гигиенические салфетки в ассортименте: [Kirim: 0 | Chiqim: 83,382,000 | Qoldiq: -83,382,000]
-• Пахтали таёкчалар: [Kirim: 0 | Chiqim: 15,001,000 | Qoldiq: -15,001,000]
-• Пластмассадан  тайорланган  бутилкалар  флаконлар  ва шунга  ухшаш  идишлар: [Kirim: 4,759,300 | Chiqim: 0 | Qoldiq: 4,759,300]
-• Подгузники детские упакованные в пакеты из полимерной пленки: [Kirim: 0 | Chiqim: 200,000,000 | Qoldiq: -200,000,000]
-• Тиш пастаси: [Kirim: 5,362,300 | Chiqim: 0 | Qoldiq: 5,362,300]
-• Товары народного потребления: [Kirim: 0 | Chiqim: 35,002,200 | Qoldiq: -35,002,200]
-• дори дармон ва бад махсулотлари учун: [Kirim: 500,000,000 | Chiqim: 0 | Qoldiq: 500,000,000]
-• кир ювиш парашоги: [Kirim: 0 | Chiqim: 2,700,000 | Qoldiq: -2,700,000]
-• медицинские изделия: [Kirim: 0 | Chiqim: 132,889,248 | Qoldiq: -132,889,248]
-• тиббий буюмлар: [Kirim: 0 | Chiqim: 5,081,440 | Qoldiq: -5,081,440]</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>842268899.99</v>
-      </c>
-      <c r="G7" s="13" t="n">
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>03306001002000000</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ополаскиватель для рта</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>ЛЕСНОЙ БАЛЬЗАМ ОПОЛАСКИВАТЕЛЬ ДЛЯ ДЕСЕН КОРА ДУБА ПИХТА ОТВАРЕ ТРАВ, 400 мл</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>dona</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>53928.57</v>
+      </c>
+      <c r="I92" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="12" t="n">
-        <v>1943638110.88</v>
-      </c>
-      <c r="I7" s="13" t="n">
+      <c r="J92" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>-1101369210.89</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>03306001001000000</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Тиш пастаси</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>• Зубная паста Лесной бальзам с органическими маслами, углём и кальцием, 75 МЛ: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
-• Зубная паста детская Ежик Сема  60мл: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• Зубная паста детская Ежик Сема  Крем брюле 60мл: [Kirim: 180 | Chiqim: 0 | Qoldiq: 180]
-• Зубная паста детская Ежик Сема 60мл: [Kirim: 0 | Chiqim: 101 | Qoldiq: -101]
-• Зубная паста детская Крокодильчик Свомпи  с мятой 60мл: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
-• Зубная паста детская Крокодильчик Свомпи с мятой 60мл: [Kirim: 0 | Chiqim: 139 | Qoldiq: -139]
-• Зубная паста профилактическая детская Фруктовая  75г: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
-• Зубная паста профилактическая детская Фруктовая 75г: [Kirim: 0 | Chiqim: 105 | Qoldiq: -105]
-• ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ Р2, 75 МЛ: [Kirim: 12 | Chiqim: 104 | Qoldiq: -92]
-• ЛЕСНОЙ БАЛЬЗАМ ЗУБНАЯ ПАСТА ТОТАЛ КОМПЛЕКС ДВОЙНАЯ МЯТА НА ОТВАРЕ ТРАВ ЧЗ, 75 МЛ: [Kirim: 36 | Chiqim: 5 | Qoldiq: 31]
-• ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ КОРЫ ДУБА И ПИХТЫ НА ОТВАРЕ ТРАВ, 75 МЛ: [Kirim: 96 | Chiqim: 6 | Qoldiq: 90]
-• ЛЕСНОЙ БАЛЬЗАМ ПРОФИЛАКТИЧЕСКАЯ ЗУБНАЯ ПАСТА С ЭКСТРАКТОМ ПРОПОЛИСА И ЗВЕРОБОЯ НА ОТВАРЕ ТРАВ, 75 МЛ: [Kirim: 36 | Chiqim: 0 | Qoldiq: 36]
-• ЛЕСНОЙ БАЛЬЗАМ Профилактическая зубная паста "Лесной бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ: [Kirim: 36 | Chiqim: 0 | Qoldiq: 36]
-• Профилактическая зубная паста "Лесной Бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ: [Kirim: 12 | Chiqim: 28 | Qoldiq: -16]
-• Профилактическая зубная паста "Лесной Бальзам" с экстрактом шалфея и алоэ-вера на отваре трав, 75 МЛ: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
-• Профилактическая зубная паста "Лесной бальзам" с экстрактами алоэ-вера и белого чая на отваре трав, 75 МЛ: [Kirim: 36 | Chiqim: 61 | Qoldiq: -25]
-• Профилактическая зубная паста "Лесной бальзам" с экстрактами коры дуба и пихты на отваре трав, 75 МЛ: [Kirim: 96 | Chiqim: 134 | Qoldiq: -38]
-• Профилактическая зубная паста "Лесной бальзам" с экстрактами прополиса и зверобоя на отваре трав, 75 МЛ: [Kirim: 48 | Chiqim: 19 | Qoldiq: 29]
-• Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 МЛ: [Kirim: 48 | Chiqim: 125 | Qoldiq: -77]
-• Профилактическая зубная паста "Лесной бальзам" с экстрактом ромашки и маслом облепихи на отваре трав, 75 мл: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
-• детская Ежик Сема с мятой  60мл: [Kirim: 90 | Chiqim: 0 | Qoldiq: 90]
-• детская Ежик Сема с мятой 60мл: [Kirim: 0 | Chiqim: 5 | Qoldiq: -5]</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>1322</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>8164047.879999999</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>842</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>8254017.82</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>480</v>
-      </c>
-      <c r="K8" s="13" t="n">
-        <v>2964253.390620272</v>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" t="n">
+        <v>53928.57</v>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>09619002001000000</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Тагликлар</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>• SMART ADULT DIAPERS L: [Kirim: 1,200 | Chiqim: 1,200 | Qoldiq: 0]
-• SMART ADULT DIAPERS M: [Kirim: 600 | Chiqim: 540 | Qoldiq: 60]
-• SMART ADULT DIAPERS XL: [Kirim: 2,400 | Chiqim: 2,342 | Qoldiq: 58]
-• Подгузники для взрослых  Evony  Х-Large 30х4: [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
-• Подгузники для взрослых  Evony Large 30х4: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
-• Подгузники для взрослых  Evony М размер 30х4: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• Подгузники для взрослых Evony Large 30х4: [Kirim: 0 | Chiqim: 80 | Qoldiq: -80]
-• Подгузники для взрослых Evony М размер 30х4: [Kirim: 0 | Chiqim: 40 | Qoldiq: -40]
-• Подгузники для взрослых Evony Х-Large 30х4: [Kirim: 0 | Chiqim: 160 | Qoldiq: -160]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/12: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  JUNIOR PLUS 6/38: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MAXI 4/16: [Kirim: 840 | Chiqim: 0 | Qoldiq: 840]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium  MIDI 3/18: [Kirim: 600 | Chiqim: 0 | Qoldiq: 600]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR 5/14: [Kirim: 840 | Chiqim: 596 | Qoldiq: 244]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/12: [Kirim: 0 | Chiqim: 203 | Qoldiq: -203]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium JUNIOR PLUS 6/38: [Kirim: 0 | Chiqim: 27 | Qoldiq: -27]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MAXI 4/16: [Kirim: 0 | Chiqim: 621 | Qoldiq: -621]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MIDI 3/18: [Kirim: 0 | Chiqim: 452 | Qoldiq: -452]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium MINI 2/20: [Kirim: 720 | Chiqim: 421 | Qoldiq: 299]
-• УПАКОВАННЫЕ ДЕТСКИЕ ПОДГУЗНИКИ BABY STILL Premium YENIDOG'AN 1/22: [Kirim: 1,745 | Chiqim: 972 | Qoldiq: 773]</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>9515</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>137804285.72</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>7654</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>136209821.5499999</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>1861</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>26952577.58538307</v>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>03304999015000000</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Присыпка (в т.ч. детская)</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>• Kodomo Детская присыпка (Extra Mild) 50гр: [Kirim: 576 | Chiqim: 489 | Qoldiq: 87]
-• Kodomo Детская присыпка (Extra Mild) English &amp; Arabic Label 180гр: [Kirim: 336 | Chiqim: 178 | Qoldiq: 158]
-• Kodomo Детская присыпка (Gentle Soft) 50гр: [Kirim: 576 | Chiqim: 624 | Qoldiq: -48]
-• Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр: [Kirim: 240 | Chiqim: 207 | Qoldiq: 33]
-• Kodomo Детская присыпка (Natural Soft Protection) 50гр: [Kirim: 576 | Chiqim: 620 | Qoldiq: -44]
-• Kodomo Детская присыпка (Natural Soft Protection)English &amp; Arabic Language 180гр: [Kirim: 288 | Chiqim: 207 | Qoldiq: 81]
-• Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 160гр: [Kirim: 240 | Chiqim: 174 | Qoldiq: 66]
-• Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр: [Kirim: 576 | Chiqim: 608 | Qoldiq: -32]
-• Teddy Болалар упаси (Лаванда) 50 гр: [Kirim: 432 | Chiqim: 367 | Qoldiq: 65]
-• Teddy Болалар упаси (Оддий) 50 гр: [Kirim: 432 | Chiqim: 219 | Qoldiq: 213]
-• Teddy Присыпка  простой  50 гр: [Kirim: 216 | Chiqim: 0 | Qoldiq: 216]
-• Детская присыпка  " Попкинсы"  120г: [Kirim: 320 | Chiqim: 0 | Qoldiq: 320]
-• Детская присыпка " Попкинсы" 120г: [Kirim: 0 | Chiqim: 120 | Qoldiq: -120]
-• Детская присыпка 80 г/Puder 80g: [Kirim: 24 | Chiqim: 10 | Qoldiq: 14]
-• Пересипка детский Baby "UPPY" 100 мл: [Kirim: 960 | Chiqim: 960 | Qoldiq: 0]
-• №1 Kodomo Детская присыпка (Gentle Soft) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• №1 Kodomo Детская присыпка (Gentle Soft) English &amp; Arabic Language 180гр: [Kirim: 48 | Chiqim: 0 | Qoldiq: 48]
-• №1 Kodomo Детская присыпка (Natural Soft Protection) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• №1 Kodomo Детская присыпка (Oganiku Organic Aloe Vera Extract) 50гр: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>6704</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>61153395.69000001</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>4783</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>56578035.75999999</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>1921</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>17523220.93086068</v>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>04014001012000000</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>Тишлар учун резина</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>• Грудная накладка  MUMMY - 1132 -шт: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Грудная накладка MUMMY - 1132 -шт: [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
-• Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детский силиконовый прорезыватель для зубов RABITO (RBT-106) (GIRAFEE EDICATION) (7.29.003): [Kirim: 0 | Chiqim: 225 | Qoldiq: -225]
-• Детский силиконовый прорезыватель для зубов RBT-401  (CORN EDITION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION): [Kirim: 0 | Chiqim: 256 | Qoldiq: -256]
-• Детский силиконовый прорезыватель для зубов RBT-402  (BANANA EDITION): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION): [Kirim: 0 | Chiqim: 255 | Qoldiq: -255]
-• Зубагризки: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Зубагризки (FZ-188): [Kirim: 432 | Chiqim: 456 | Qoldiq: -24]
-• Зубагризки (FZ-189): [Kirim: 432 | Chiqim: 401 | Qoldiq: 31]
-• Зубогрызки из силикова Артикуль №3 MUMMY модел 1102-  шт: [Kirim: 720 | Chiqim: 0 | Qoldiq: 720]
-• Зубогрызки из силикова Артикуль №3 MUMMY модел 1102- шт: [Kirim: 96 | Chiqim: 697 | Qoldiq: -601]
-• Зубогрызки из силикона Артикуль №1 MUMMY модель 1100-шт: [Kirim: 2,640 | Chiqim: 2,556 | Qoldiq: 84]
-• Зубогрызки из силикона Артикуль №2 MUMMY модел 1101- шт: [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Зубогрызки из силикона Артикуль №2 MUMMY модел 1101-шт: [Kirim: 1,296 | Chiqim: 1,468 | Qoldiq: -172]
-• Соска-Пустышки "PANDA"  силиконовая 1123: [Kirim: 1,440 | Chiqim: 0 | Qoldiq: 1,440]
-• Соска-Пустышки "PANDA" силиконовая 1123: [Kirim: 0 | Chiqim: 336 | Qoldiq: -336]</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>8352</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>28759388.57</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>6670</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>32928392.3900001</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>1682</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>5791821.309236111</v>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>06214001013000000</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Корсет маҳсулотлари</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>• (01944) Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01944) Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01944) Корсет эластичный для коррекции фигуры, Размер 5: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• (01944-3)Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01944-4)Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 0 | Chiqim: 3 | Qoldiq: -3]
-• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 28 | Chiqim: 0 | Qoldiq: 28]
-• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 49 | Chiqim: 0 | Qoldiq: 49]
-• (01946) Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 28 | Chiqim: 0 | Qoldiq: 28]
-• (01946-2)Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 0 | Chiqim: 9 | Qoldiq: -9]
-• (01946-3)Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 0 | Chiqim: 13 | Qoldiq: -13]
-• (01946-4)Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 0 | Chiqim: 7 | Qoldiq: -7]
-• Корсет поясничный ортопедический, с жёстками вставками, Размер 2: [Kirim: 21 | Chiqim: 35 | Qoldiq: -14]
-• Корсет поясничный ортопедический, с жёстками вставками, Размер 3: [Kirim: 21 | Chiqim: 43 | Qoldiq: -22]
-• Корсет поясничный ортопедический, с жёстками вставками, Размер 4: [Kirim: 21 | Chiqim: 32 | Qoldiq: -11]
-• Корсет эластичный для коррекции фигуры, Размер 3: [Kirim: 10 | Chiqim: 8 | Qoldiq: 2]
-• Корсет эластичный для коррекции фигуры, Размер 4: [Kirim: 10 | Chiqim: 6 | Qoldiq: 4]
-• Корсет эластичный для коррекции фигуры, Размер 5: [Kirim: 10 | Chiqim: 9 | Qoldiq: 1]</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>228</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>14646000</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>12213482.32999999</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>61</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>3918447.368421053</v>
-      </c>
-      <c r="L12" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>03003001018000000</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Бошқа қадоқланмаган дори воситалари (фармацевтик субстанциялар)</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>• Achchiq bodom 100 ml: [Kirim: 200 | Chiqim: 200 | Qoldiq: 0]
-• G'oz moyi 100 ml: [Kirim: 100 | Chiqim: 387 | Qoldiq: -287]
-• Gʻoz 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• G’oz yogʻi 100ml: [Kirim: 200 | Chiqim: 10 | Qoldiq: 190]
-• Kanakunjut 100 ml: [Kirim: 200 | Chiqim: 500 | Qoldiq: -300]
-• Kanakunjut 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• Kanakunjut yogʻi 100ml: [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
-• Qovoq danak moyi 100 ml: [Kirim: 100 | Chiqim: 113 | Qoldiq: -13]
-• Qovoq donagi moyi 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• Sedana 100 ml: [Kirim: 200 | Chiqim: 281 | Qoldiq: -81]
-• Sedana 100ml: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]
-• Shaftoli danak moyi 100 ml: [Kirim: 500 | Chiqim: 500 | Qoldiq: 0]
-• Shirin bodom 100 ml: [Kirim: 200 | Chiqim: 181 | Qoldiq: 19]
-• Zaytun 100 ml: [Kirim: 500 | Chiqim: 1,380 | Qoldiq: -880]
-• Zaytun 100ml: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
-• Zaytun yogʻi 100ml: [Kirim: 600 | Chiqim: 20 | Qoldiq: 580]</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>3700</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>16387919</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>3572</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>18383124.71000005</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>128</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>566933.4140540541</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>02106999028000000</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>• Achchiq bodom yog'i 100 ml: [Kirim: 100 | Chiqim: 100 | Qoldiq: 0]
-• Achchiq bodom yog'i 100ml: [Kirim: 200 | Chiqim: 54 | Qoldiq: 146]
-• G'oz yog'i 100 ml: [Kirim: 100 | Chiqim: 48 | Qoldiq: 52]
-• Kanakunjut yog'i 100 ml: [Kirim: 300 | Chiqim: 294 | Qoldiq: 6]
-• Kanakunjut yog'i 100ml: [Kirim: 100 | Chiqim: 100 | Qoldiq: 0]
-• Qora sedana yog'i 100 ml: [Kirim: 200 | Chiqim: 107 | Qoldiq: 93]
-• Sedana yog'i 100ml: [Kirim: 100 | Chiqim: 50 | Qoldiq: 50]
-• Shaftoli danagi yog'i 100 ml: [Kirim: 500 | Chiqim: 366 | Qoldiq: 134]
-• Shaftoli yog'i 100ml: [Kirim: 300 | Chiqim: 268 | Qoldiq: 32]
-• Shirin bodom yog'i 100ml: [Kirim: 200 | Chiqim: 92 | Qoldiq: 108]
-• Zaytun yog'i 100 ml: [Kirim: 1,200 | Chiqim: 1,185 | Qoldiq: 15]
-• Zaytun yog'i 100ml: [Kirim: 300 | Chiqim: 300 | Qoldiq: 0]
-• Пол Пола чай №15: [Kirim: 450 | Chiqim: 67 | Qoldiq: 383]
-• Расторопша чай №15: [Kirim: 450 | Chiqim: 247 | Qoldiq: 203]
-• Шиповник чай №15: [Kirim: 450 | Chiqim: 119 | Qoldiq: 331]</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>4950</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>23142857.81</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>3397</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>20027321.29000001</v>
-      </c>
-      <c r="J14" s="14" t="n">
-        <v>1553</v>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>7260779.430086868</v>
-      </c>
-      <c r="L14" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>03401001001000000</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>Атир совун</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>• БОРО ПЛЮС Антибактериальное Мыло 100гр в коробке №1(1х1): [Kirim: 288 | Chiqim: 62 | Qoldiq: 226]
-• И01-072-00 Мыло туалетное твердое " ABSOLUT FitoGuard" Белый чай и масло оливы, 90 гр.: [Kirim: 12 | Chiqim: 5 | Qoldiq: 7]
-• И01-072-00 Мыло туалетное твердое "ABSOLUT 2в1" дикая орхидея, 90 гр.: [Kirim: 12 | Chiqim: 29 | Qoldiq: -17]
-• И01-072-00 Мыло туалетное твердое "ABSOLUT For men" Лемонграсс и мята, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
-• И01-072-00 Мыло туалетное твердое "ABSOLUT" FitoGuard облепиха, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS освежающее, 90 гр.: [Kirim: 18 | Chiqim: 19 | Qoldiq: -1]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT ABS ультразащита, 90 гр.: [Kirim: 12 | Chiqim: 60 | Qoldiq: -48]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard алоэ, 90 гр.: [Kirim: 18 | Chiqim: 9 | Qoldiq: 9]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT FitoGuard ромашка, 90 гр.: [Kirim: 12 | Chiqim: 29 | Qoldiq: -17]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' календула, 90 гр.: [Kirim: 12 | Chiqim: 9 | Qoldiq: 3]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT Kids' череда, 90 гр.: [Kirim: 12 | Chiqim: 6 | Qoldiq: 6]
-• И01-072-00 Мыло туалетное твердое 'ABSOLUT' 2в1 нежное, 90 гр.: [Kirim: 24 | Chiqim: 2 | Qoldiq: 22]
-• И01-072-00 Мыло туалетное твердое ABSOLUT грейпфрут и бергамот, 90 гр.: [Kirim: 12 | Chiqim: 0 | Qoldiq: 12]
-• И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Главаптека' (дегтярное), 90 гр.: [Kirim: 440 | Chiqim: 299 | Qoldiq: 141]
-• И01-072-00 Мыло туалетное твердое клас 'ВЕСНА Малышам', 90 гр.: [Kirim: 432 | Chiqim: 355 | Qoldiq: 77]</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1328</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>7707857.159999997</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>884</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>5451071.52</v>
-      </c>
-      <c r="J15" s="14" t="n">
-        <v>444</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>2577024.532409638</v>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>03005002002000000</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>Эластик бинтлар</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>• Бинт эластичный медицинский GT 100мм х 2 метр: [Kirim: 120 | Chiqim: 145 | Qoldiq: -25]
-• Бинт эластичный медицинский GT 100мм х 3 метр: [Kirim: 200 | Chiqim: 186 | Qoldiq: 14]
-• Бинт эластичный медицинский GT 100мм х 4 метр: [Kirim: 60 | Chiqim: 60 | Qoldiq: 0]
-• Бинт эластичный медицинский GT 100мм х 5 метр: [Kirim: 186 | Chiqim: 221 | Qoldiq: -35]
-• Бинт эластичный медицинский GT 100мм х 6 метр: [Kirim: 90 | Chiqim: 105 | Qoldiq: -15]
-• Бинт эластичный медицинский GT 120мм х 2 метр: [Kirim: 120 | Chiqim: 83 | Qoldiq: 37]
-• Бинт эластичный медицинский GT 120мм х 3 метр: [Kirim: 110 | Chiqim: 123 | Qoldiq: -13]
-• Бинт эластичный медицинский GT 120мм х 4 метр: [Kirim: 90 | Chiqim: 73 | Qoldiq: 17]
-• Бинт эластичный медицинский GT 120мм х 5 метр: [Kirim: 90 | Chiqim: 101 | Qoldiq: -11]
-• Бинт эластичный медицинский GT 140мм х 2 метр: [Kirim: 225 | Chiqim: 90 | Qoldiq: 135]
-• Бинт эластичный медицинский GT 140мм х 3 метр: [Kirim: 120 | Chiqim: 24 | Qoldiq: 96]
-• Бинт эластичный медицинский GT 140мм х 4 метр: [Kirim: 100 | Chiqim: 11 | Qoldiq: 89]
-• Бинт эластичный медицинский GT 140мм х 5 метр: [Kirim: 54 | Chiqim: 14 | Qoldiq: 40]
-• Бинт эластичный медицинский GT 80мм х 2 метр: [Kirim: 90 | Chiqim: 71 | Qoldiq: 19]
-• Бинт эластичный медицинский GT 80мм х 3 метр: [Kirim: 135 | Chiqim: 87 | Qoldiq: 48]</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>21765800</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>1394</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>19309464.10000002</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>396</v>
-      </c>
-      <c r="K16" s="13" t="n">
-        <v>4815227.262569833</v>
-      </c>
-      <c r="L16" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>03926001020008003</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар CANPOL Babies Клипса-ушлагич сўрғич учун, 0 ой+</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001): [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• Соски из силикона (RBT-309): [Kirim: 336 | Chiqim: 10 | Qoldiq: 326]
-• Соски из силикона (RBT-309) (7.23.034): [Kirim: 0 | Chiqim: 220 | Qoldiq: -220]
-• Соски из силикона (RBT-310): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Соски из силикона (RBT-310) (7.23.035): [Kirim: 0 | Chiqim: 62 | Qoldiq: -62]
-• Соски из силикона MAGEMIOR: [Kirim: 340 | Chiqim: 161 | Qoldiq: 179]
-• Соски из силикона RABITO (RBT-101): [Kirim: 288 | Chiqim: 76 | Qoldiq: 212]
-• Соски из силикона RABITO (RBT-410): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
-• Соски из силикона RABITO (RBT-410) (7.35.001): [Kirim: 0 | Chiqim: 251 | Qoldiq: -251]
-• Соски из силикона Артикул: 7,23,003: [Kirim: 0 | Chiqim: 300 | Qoldiq: -300]
-• Соски из силикона Артикул: 7,23,042: [Kirim: 0 | Chiqim: 182 | Qoldiq: -182]
-• Соски из силикона Артикул: 7.23.003: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
-• Соски из силикона Артикул: 7.23.042: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Соски из силикона Модель:S-23-A. Артикул: 7.23.026 barcode 6928568951760 размер:S (0-6 месяц): [Kirim: 600 | Chiqim: 360 | Qoldiq: 240]</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>2872</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>19155016.68</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>1632</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>15894642.88999999</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>1240</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>8270271.825626741</v>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>03304011005000000</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>Қўл учун крем</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК И НОГТЕЙ КОМПЛЕКСНЫЙ, 80 МЛ: [Kirim: 10 | Chiqim: 55 | Qoldiq: -45]
-• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК НОЧНОЙ ВОССТАНАВЛИВАЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 159 | Qoldiq: -149]
-• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК РЕГЕНЕРИРУЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 27 | Qoldiq: -17]
-• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК СМЯГЧАЮЩИЙ Р2, 80 МЛ: [Kirim: 10 | Chiqim: 10 | Qoldiq: 0]
-• БАРХАТНЫЕ РУЧКИ КРЕМ ДЛЯ РУК УВЛАЖНЯЮЩИЙ, 80 МЛ: [Kirim: 20 | Chiqim: 51 | Qoldiq: -31]
-• Крем БАРХАТНЫЕ РУЧКИ защитный для рук, 80 МЛ: [Kirim: 80 | Chiqim: 37 | Qoldiq: 43]
-• Крем БАРХАТНЫЕ РУЧКИ комплексный для рук и ногтей, 80 МЛ: [Kirim: 60 | Chiqim: 11 | Qoldiq: 49]
-• Крем БАРХАТНЫЕ РУЧКИ ночной восстанавливающий для рук, 80 МЛ: [Kirim: 50 | Chiqim: 7 | Qoldiq: 43]
-• Крем БАРХАТНЫЕ РУЧКИ питательный для рук, 80 МЛ: [Kirim: 120 | Chiqim: 65 | Qoldiq: 55]
-• Крем БАРХАТНЫЕ РУЧКИ регенерирующий для рук, 80 МЛ: [Kirim: 70 | Chiqim: 0 | Qoldiq: 70]
-• Крем БАРХАТНЫЕ РУЧКИ смягчающий для рук, 80 МЛ: [Kirim: 80 | Chiqim: 0 | Qoldiq: 80]
-• Крем БАРХАТНЫЕ РУЧКИ увлажняющий для рук, 80 МЛ: [Kirim: 80 | Chiqim: 23 | Qoldiq: 57]
-• Крем косметический Нежные ручки Козье молоко 125мл: [Kirim: 250 | Chiqim: 161 | Qoldiq: 89]
-• Крем косметический Нежные ручки Питательный 125мл: [Kirim: 250 | Chiqim: 170 | Qoldiq: 80]</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>7599327.12</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>776</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>6842857.200000002</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <v>324</v>
-      </c>
-      <c r="K18" s="13" t="n">
-        <v>2238347.2608</v>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>03401001002000000</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Суюқ совун</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>• ELFIN  JIDKOYE  MILO 300 GR  DOZ: [Kirim: 810 | Chiqim: 0 | Qoldiq: 810]
-• ELFIN  JIDKOYE  MILO 300 GR SOS: [Kirim: 954 | Chiqim: 0 | Qoldiq: 954]
-• ELFIN  JIDKOYE  MILO 500 GR SOS: [Kirim: 300 | Chiqim: 0 | Qoldiq: 300]
-• ELFIN JIDKOYE MILO 300 GR DOZ: [Kirim: 0 | Chiqim: 2,354 | Qoldiq: -2,354]
-• ELFIN JIDKOYE MILO 300 GR SOS: [Kirim: 0 | Chiqim: 2,318 | Qoldiq: -2,318]
-• ELFIN JIDKOYE MILO 300 GR SOSELFIN JIDKOYE MILO 300 GR SOS: [Kirim: 0 | Chiqim: 4 | Qoldiq: -4]
-• ELFIN JIDKOYE MILO 500 GR SOS: [Kirim: 0 | Chiqim: 298 | Qoldiq: -298]
-• Elfin  jitki Mila 300 gr soskalik: [Kirim: 360 | Chiqim: 0 | Qoldiq: 360]
-• Elfin jidki mila 300 dozorlik: [Kirim: 1,800 | Chiqim: 441 | Qoldiq: 1,359]
-• Elfin jidki mila 300 gr soskalik: [Kirim: 1,440 | Chiqim: 734 | Qoldiq: 706]
-• HAVEN JIDKOYE MILO  500 GR  kapalak: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Елфин житки мило 300гр SOS: [Kirim: 432 | Chiqim: 131 | Qoldiq: 301]
-• Елфин житки мило 300гр Дазатр: [Kirim: 498 | Chiqim: 308 | Qoldiq: 190]</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>6714</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>18558714.3</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>6588</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>20880178.37000005</v>
-      </c>
-      <c r="J19" s="14" t="n">
-        <v>126</v>
-      </c>
-      <c r="K19" s="13" t="n">
-        <v>348286.8635388739</v>
-      </c>
-      <c r="L19" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>04014001006000000</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Болалар соскаси бутилка учун</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>• Детские cоски для  бутылочек  (40332MIX): [Kirim: 1,296 | Chiqim: 0 | Qoldiq: 1,296]
-• Детские Соски для бутылочек (40332MIX): [Kirim: 432 | Chiqim: 0 | Qoldiq: 432]
-• Детские соски для бутылок: [Kirim: 4,600 | Chiqim: 0 | Qoldiq: 4,600]
-• Детские соски для бутылочек: [Kirim: 5,000 | Chiqim: 8,194 | Qoldiq: -3,194]
-• Детские соски для бутылочек (40332): [Kirim: 864 | Chiqim: 2,274 | Qoldiq: -1,410]
-• Соска пустышка Panda c крышкой 106 шт: [Kirim: 1,440 | Chiqim: 0 | Qoldiq: 1,440]
-• Соски пустышки Mummy модель 1111 в одном комплекте 2 шт: [Kirim: 216 | Chiqim: 411 | Qoldiq: -195]
-• Соски пустышки Mummy модель 1112 в одном комплекте 2 шт: [Kirim: 288 | Chiqim: 404 | Qoldiq: -116]
-• Соски пустышки Mummy модель 1114 в одном комплекте 2 шт: [Kirim: 144 | Chiqim: 164 | Qoldiq: -20]
-• Соски пустышки Mummy модель1113 одном комплекте 2 штук: [Kirim: 144 | Chiqim: 337 | Qoldiq: -193]
-• Соски пустышки Mummy модель1115 одном комплекте 2 штук: [Kirim: 216 | Chiqim: 342 | Qoldiq: -126]</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>14640</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>19504999.97</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>12126</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>25891785.63000003</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>2514</v>
-      </c>
-      <c r="K20" s="13" t="n">
-        <v>3349424.175176229</v>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>03924001010000000</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Уй-рўзғор ва маиший эҳтиёжлар учун пластмасса буюмлар (пластмассадан тайёрланган ошхона идиш-товоқлари, приборлар ва ошхона анжомларидан ташқари)</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>• Детские  бутылки ONLY BABY NATURAL 260 мл (А-2): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детские бутылки   (358): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Детские бутылки (358): [Kirim: 0 | Chiqim: 138 | Qoldiq: -138]
-• Детские бутылки (360): [Kirim: 288 | Chiqim: 121 | Qoldiq: 167]
-• Пластмассовый цепочка держатель для  соски( RBT-305): [Kirim: 1,728 | Chiqim: 0 | Qoldiq: 1,728]
-• Пластмассовый цепочка держатель для соски (RBT-129) 7,30,011: [Kirim: 0 | Chiqim: 1,306 | Qoldiq: -1,306]
-• Пластмассовый цепочка держатель для соски (RBT-129) 7.30.011: [Kirim: 1,728 | Chiqim: 0 | Qoldiq: 1,728]
-• Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003: [Kirim: 0 | Chiqim: 329 | Qoldiq: -329]
-• Пластмассовый цепочка держатель для соски (RBT-130) 7.30.003: [Kirim: 1,152 | Chiqim: 0 | Qoldiq: 1,152]
-• Пластмассовый цепочка держатель для соски( RBT-305): [Kirim: 0 | Chiqim: 48 | Qoldiq: -48]
-• Пластмассовый цепочка держатель для соски( RBT-305) (7.30.002): [Kirim: 0 | Chiqim: 1,291 | Qoldiq: -1,291]</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>5328</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>32060828.56</v>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>3233</v>
-      </c>
-      <c r="I21" s="13" t="n">
-        <v>25938660.62000002</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>2095</v>
-      </c>
-      <c r="K21" s="13" t="n">
-        <v>12606500.71944444</v>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>10306002005000000</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>Услуги по электронному документообороту.</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>• Услуги по организации юридически значимого документооборота между организациями (Didox) за август 2026г.: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за апрель 2026г.: [Kirim: 160 | Chiqim: 0 | Qoldiq: 160]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за декабрь 2025г.: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за июль 2026г.: [Kirim: 171 | Chiqim: 0 | Qoldiq: 171]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за июнь 2026г.: [Kirim: 149 | Chiqim: 0 | Qoldiq: 149]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за май 2026г.: [Kirim: 148 | Chiqim: 0 | Qoldiq: 148]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за март 2026г.: [Kirim: 157 | Chiqim: 0 | Qoldiq: 157]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за ноябрь 2025г.: [Kirim: 42 | Chiqim: 0 | Qoldiq: 42]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за февраль 2026г.: [Kirim: 119 | Chiqim: 0 | Qoldiq: 119]
-• Услуги по организации юридически значимого документооборота между организациями (Didox) за январь 2026г.: [Kirim: 68 | Chiqim: 0 | Qoldiq: 68]</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>1174</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>632000</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="14" t="n">
-        <v>1174</v>
-      </c>
-      <c r="K22" s="13" t="n">
-        <v>632000</v>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>03924001002000000</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Пластик ошхона идишлари, приборлар ва ошхона анжомлари</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>• Детская бутылка пластмассовый  (ALGO 7.17.018) 125ml: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детская бутылка пластмассовый  (RBT-705)  160ml: [Kirim: 347 | Chiqim: 0 | Qoldiq: 347]
-• Детская бутылка пластмассовый (ALGO 7,17,018) 125ml: [Kirim: 0 | Chiqim: 105 | Qoldiq: -105]
-• Детская бутылка пластмассовый (RBT-705) 160ml: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
-• Детская бутылка пластмассовый (RBT-705) 160ml (7.17.028): [Kirim: 0 | Chiqim: 242 | Qoldiq: -242]
-• Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621): [Kirim: 480 | Chiqim: 10 | Qoldiq: 470]
-• Детские бутылки стеклянные из безцвет стекла 240ml (Algo 9621) (7.17.035): [Kirim: 0 | Chiqim: 566 | Qoldiq: -566]
-• Детский силиконовый прорезыватель для зубов RBT-401 (CORN EDITION): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Детский силиконовый прорезыватель для зубов RBT-402 (BANANA EDITION): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>1019</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>16434080.56</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>939</v>
-      </c>
-      <c r="I23" s="13" t="n">
-        <v>20854553.61999999</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="K23" s="13" t="n">
-        <v>1290212.40902846</v>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>03307001002000000</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Гигиеник салфеткалар (нам ва қурутувчи )</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>• Влажные салфетки (120 штук): [Kirim: 2,640 | Chiqim: 2,640 | Qoldiq: 0]
-• Влажные салфетки (15 штук): [Kirim: 6,480 | Chiqim: 5,256 | Qoldiq: 1,224]
-• Влажные салфетки (72 штук): [Kirim: 3,120 | Chiqim: 2,996 | Qoldiq: 124]
-• Влажные салфетки «Aqua Touch»: [Kirim: 12 | Chiqim: 2 | Qoldiq: 10]
-• Салфетка влажный   120 шт: [Kirim: 1,076 | Chiqim: 0 | Qoldiq: 1,076]
-• Салфетка влажный   72 шт: [Kirim: 1,104 | Chiqim: 0 | Qoldiq: 1,104]
-• Салфетка влажный 120 шт: [Kirim: 0 | Chiqim: 1,039 | Qoldiq: -1,039]
-• Салфетка влажный 72 шт: [Kirim: 0 | Chiqim: 1,104 | Qoldiq: -1,104]</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>14432</v>
-      </c>
-      <c r="G24" s="13" t="n">
-        <v>38049571.44</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>13037</v>
-      </c>
-      <c r="I24" s="13" t="n">
-        <v>44391696.68999996</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <v>1395</v>
-      </c>
-      <c r="K24" s="13" t="n">
-        <v>3677879.168431263</v>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>03304011006000000</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>Бадан учун крем</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>• БОРО ПЛЮС БЕЗ ЗАПАХА Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
-• БОРО ПЛЮС Крем для ног интенсивного действия 50мл туба №1(1х1): [Kirim: 144 | Chiqim: 144 | Qoldiq: 0]
-• БОРО ПЛЮС РЕГУЛЯРНЫЙ Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
-• БОРО ПЛЮС ТРАВЯНОЙ Крем 25мл туба №1(1х1): [Kirim: 480 | Chiqim: 480 | Qoldiq: 0]
-• Крем детский  под подгузник" PAPPY PAMPER" 45мл: [Kirim: 150 | Chiqim: 0 | Qoldiq: 150]
-• Крем детский  под подгузник" PAPPY PAMPER" 80мл: [Kirim: 250 | Chiqim: 0 | Qoldiq: 250]
-• Крем детский под подгузник" PAPPY PAMPER" 45мл: [Kirim: 0 | Chiqim: 62 | Qoldiq: -62]
-• Крем детский под подгузник" PAPPY PAMPER" 80мл: [Kirim: 0 | Chiqim: 111 | Qoldiq: -111]</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>1984</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>17009462.64</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>1757</v>
-      </c>
-      <c r="I25" s="13" t="n">
-        <v>19559642.86</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <v>227</v>
-      </c>
-      <c r="K25" s="13" t="n">
-        <v>1946143.154879032</v>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>03305005001431004</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Шампунь (барча турлари) Антипедикулёзный Шампунь, картон қутида, ПЭТ бутилка 110 г.</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>• Шампунь "PEPILINO"  265мл  Бегемотик Гоша: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• Шампунь "PEPILINO"  265мл  Дельфинчик Вилли: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• Шампунь "PEPILINO"  265мл  Зайка степашка: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• Шампунь "PEPILINO"  265мл  Медвежонок Пух: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]
-• Шампунь "PEPILINO" 265мл Бегемотик Гоша: [Kirim: 0 | Chiqim: 28 | Qoldiq: -28]
-• Шампунь "PEPILINO" 265мл Дельфинчик Вилли: [Kirim: 0 | Chiqim: 100 | Qoldiq: -100]
-• Шампунь "PEPILINO" 265мл Зайка степашка: [Kirim: 0 | Chiqim: 14 | Qoldiq: -14]
-• Шампунь "PEPILINO" 265мл Медвежонок Пух: [Kirim: 0 | Chiqim: 38 | Qoldiq: -38]</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>1339285.7</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>180</v>
-      </c>
-      <c r="I26" s="13" t="n">
-        <v>1526785.71</v>
-      </c>
-      <c r="J26" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>133928.57</v>
-      </c>
-      <c r="L26" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>03304021006000000</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>Масло косметическое</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>• Teddy Болалар ёғи (Алоэ) 100 мл: [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]
-• Teddy Болалар ёғи (Гипоаллерген) 100 мл: [Kirim: 72 | Chiqim: 68 | Qoldiq: 4]
-• Teddy Болалар ёғи (Лаванда) 100 мл: [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]
-• Teddy Болалар ёғи (Ромашка) 100 мл: [Kirim: 72 | Chiqim: 66 | Qoldiq: 6]
-• Детская масло SHOFF 100gr: [Kirim: 1,584 | Chiqim: 1,270 | Qoldiq: 314]
-• Детская масло SHOFF 50gr: [Kirim: 1,536 | Chiqim: 1,195 | Qoldiq: 341]
-• Косметические изделия в ассортименте: [Kirim: 0 | Chiqim: 7,673,540 | Qoldiq: -7,673,540]
-• Парфюмерно-косметические: [Kirim: 0 | Chiqim: 10,483,200 | Qoldiq: -10,483,200]</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>3408</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>24395574.86</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>18159483</v>
-      </c>
-      <c r="I27" s="13" t="n">
-        <v>25332589.18000002</v>
-      </c>
-      <c r="J27" s="15" t="n">
-        <v>-18156075</v>
-      </c>
-      <c r="K27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>07010001004000000</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>Шиша (бутилка)</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>• Детские бутылки стеклянные 120 ml. Бренд: ALGO. Артикул:7.17.032: [Kirim: 480 | Chiqim: 0 | Qoldiq: 480]
-• Детские бутылки стеклянные 240 ml. Бренд: ALGO. Артикул:7.17.031: [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Детские бутылки стеклянные 60 ml. Бренд: Rabito. Model:  Артикул:7.17.023: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детские бутылки стеклянные из безцвет стекла 150ml (7.17.043): [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Детские бутылки стеклянные из безцвет стекла 240ml (7.17.044): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детские бутылки стеклянные из безцвет стекла 240ml (RBT-207) (7,17,044): [Kirim: 0 | Chiqim: 169 | Qoldiq: -169]
-• №1 Детские бутылки стеклянные 240 ml. Бренд: Rabito. Артикул:7.17.035: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>1248</v>
-      </c>
-      <c r="G28" s="13" t="n">
-        <v>21490337.15</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="I28" s="13" t="n">
-        <v>4828571.439999999</v>
-      </c>
-      <c r="J28" s="14" t="n">
-        <v>1079</v>
-      </c>
-      <c r="K28" s="13" t="n">
-        <v>18580187.32760417</v>
-      </c>
-      <c r="L28" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
-        <is>
-          <t>03926001020000000</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Бошқа жойда киритилмаган пластмассадан тайёрланган бошқа буюмлар</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>• Держатель для сосок (JK BABY модел с колокльчика ): [Kirim: 120 | Chiqim: 504 | Qoldiq: -384]
-• Держатель для сосок (JM BABY простой): [Kirim: 384 | Chiqim: 0 | Qoldiq: 384]
-• Детские бутылки (А-2 ) 260 мл: [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• Детские бутылки (А-3-Т 125 мл): [Kirim: 0 | Chiqim: 6 | Qoldiq: -6]
-• Пластмассовый цепочка держатель для соски (RBT-130) 7,30,003: [Kirim: 0 | Chiqim: 132 | Qoldiq: -132]
-• Соски из силикона (RBT-310): [Kirim: 0 | Chiqim: 10 | Qoldiq: -10]
-• Соски из силикона (RBT-310) (7.23.035): [Kirim: 0 | Chiqim: 98 | Qoldiq: -98]</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>504</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>3240000</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>756</v>
-      </c>
-      <c r="I29" s="13" t="n">
-        <v>6613749.949999998</v>
-      </c>
-      <c r="J29" s="15" t="n">
-        <v>-252</v>
-      </c>
-      <c r="K29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>09603002002000000</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Тиш чўткаси</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>• зубная щетка № 11B: [Kirim: 360 | Chiqim: 360 | Qoldiq: 0]
-• зубная щетка № 14А: [Kirim: 1,728 | Chiqim: 1,152 | Qoldiq: 576]
-• зубная щетка № 2F: [Kirim: 720 | Chiqim: 480 | Qoldiq: 240]
-• зубная щетка № 4F: [Kirim: 720 | Chiqim: 624 | Qoldiq: 96]
-• зубная щетка № 5Д: [Kirim: 576 | Chiqim: 576 | Qoldiq: 0]
-• зубная щетка № 8Д: [Kirim: 1,344 | Chiqim: 636 | Qoldiq: 708]</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>5448</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>12528214.27</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>3828</v>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>11546785.27000004</v>
-      </c>
-      <c r="J30" s="14" t="n">
-        <v>1620</v>
-      </c>
-      <c r="K30" s="13" t="n">
-        <v>3725350.058259912</v>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>03926999004000000</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Молокоотсос (ПВХ)</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>• Молокоотос Mummy модель 1134: [Kirim: 840 | Chiqim: 786 | Qoldiq: 54]
-• Молокоотсос  (А1357): [Kirim: 288 | Chiqim: 0 | Qoldiq: 288]
-• Молокоотсос (A1357): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]
-• Молокоотсос (А-240): [Kirim: 192 | Chiqim: 192 | Qoldiq: 0]
-• Молокоотсос (А1357): [Kirim: 432 | Chiqim: 720 | Qoldiq: -288]
-• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]</t>
-        </is>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>2136</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>25432285.73</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>1698</v>
-      </c>
-      <c r="I31" s="13" t="n">
-        <v>19609821.48999999</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <v>438</v>
-      </c>
-      <c r="K31" s="13" t="n">
-        <v>5215047.35474719</v>
-      </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>06602001001000001</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Ҳассалар, ўриндиқ ҳассалар ва бошқа шунга ўхшаш буюмлар хасса</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>• Хасса (трость) 4х опорная №1 Серия - 1, Срок годности 01/2030: [Kirim: 50 | Chiqim: 50 | Qoldiq: 0]
-• Хасса (трость) деревянная №1 Серия - 1, Срок годности 01/2030: [Kirim: 162 | Chiqim: 162 | Qoldiq: 0]
-• Хасса (трость) подлокотная №1 Серия - 1, Срок годности 01/2030: [Kirim: 90 | Chiqim: 90 | Qoldiq: 0]
-• Хасса (трость) регулируемая №1  Серия - 1, Срок годности 01/2030: [Kirim: 10 | Chiqim: 0 | Qoldiq: 10]
-• Хасса (трость) регулируемая №1 Цвет Серый Китай: [Kirim: 175 | Chiqim: 204 | Qoldiq: -29]
-• Хасса (трость) регулируемая №1 Цвет Черный Китай: [Kirim: 155 | Chiqim: 131 | Qoldiq: 24]</t>
-        </is>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>642</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>24056000</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>637</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>29271000</v>
-      </c>
-      <c r="J32" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>187352.0249221183</v>
-      </c>
-      <c r="L32" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>09619001002000000</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Аёллар учун санитария тампонлари</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>• deasy: [Kirim: 4,000 | Chiqim: 1,396 | Qoldiq: 2,604]
-• mira: [Kirim: 4,000 | Chiqim: 1,700 | Qoldiq: 2,300]
-• Женские прокладки (онажон): [Kirim: 15,000 | Chiqim: 13,380 | Qoldiq: 1,620]
-• Женские прокладки (роза): [Kirim: 7,500 | Chiqim: 8,540 | Qoldiq: -1,040]
-• Тампоны женские гиг. «LINDA» картонный упаковка №10: [Kirim: 4,500 | Chiqim: 3,320 | Qoldiq: 1,180]</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>51525000</v>
-      </c>
-      <c r="H33" s="12" t="n">
-        <v>28336</v>
-      </c>
-      <c r="I33" s="13" t="n">
-        <v>40508928.26000006</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <v>6664</v>
-      </c>
-      <c r="K33" s="13" t="n">
-        <v>9810360</v>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>09619001001000000</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Аёллар учун санитария ёстиқчалари (шу жумладан эркаклар учун)</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>• Вкладыши для груди RABITO (Артикул 7.31.005): [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
-• Гигиенические женские прокладки LIBRESSE Maxi Night wing sw 6x20pcs: [Kirim: 4 | Chiqim: 4 | Qoldiq: 0]
-• Гигиенические прокладки "Amelie": [Kirim: 2,000 | Chiqim: 0 | Qoldiq: 2,000]
-• Гигиенические прокладки "Дива": [Kirim: 1,500 | Chiqim: 0 | Qoldiq: 1,500]
-• Женские гигиенические прокладки дива мама: [Kirim: 4,500 | Chiqim: 3,486 | Qoldiq: 1,014]</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>8244</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>47020571.44</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>3490</v>
-      </c>
-      <c r="I34" s="13" t="n">
-        <v>31253571.29000003</v>
-      </c>
-      <c r="J34" s="14" t="n">
-        <v>4754</v>
-      </c>
-      <c r="K34" s="13" t="n">
-        <v>27114968.05261523</v>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>04014001003000000</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>Презервативлар</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>• Презервативы из натурального латекса торговой марки "Lovit" (ANATOMIC): [Kirim: 1,184 | Chiqim: 0 | Qoldiq: 1,184]
-• Презервативы из натурального латекса торговой марки "Lovit" (Classic): [Kirim: 1,000 | Chiqim: 401 | Qoldiq: 599]
-• Презервативы из натурального латекса торговой марки "Lovit" (DOTTED): [Kirim: 1,000 | Chiqim: 679 | Qoldiq: 321]
-• Презервативы из натурального латекса торговой марки "Lovit" (RIBBED): [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
-• Презервативы из натурального латекса торговой марки "Lovit" (ULTRA THIN): [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>5184</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>9534857.129999999</v>
-      </c>
-      <c r="H35" s="12" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I35" s="13" t="n">
-        <v>3434598.25</v>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>4104</v>
-      </c>
-      <c r="K35" s="13" t="n">
-        <v>7548428.561249999</v>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180009</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Classic Таблетка аскорбинка кислота глюкоза билан</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (апельсин): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
-• Аскорбинка 3,0 №10 (классик): [Kirim: 1,300 | Chiqim: 380 | Qoldiq: 920]
-• Аскорбинка 3,0 №10 (малина): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
-• Аскорбинка 3,0 №10 (смородина): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]
-• Аскорбинка 3,0 №10 (яблоко): [Kirim: 0 | Chiqim: 20 | Qoldiq: -20]</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="I36" s="13" t="n">
-        <v>626785.7799999999</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>840</v>
-      </c>
-      <c r="K36" s="13" t="n">
-        <v>924000</v>
-      </c>
-      <c r="L36" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>02712001002000000</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>Косметика вазелини</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>• Вазелин косметический 100гр: [Kirim: 3,600 | Chiqim: 6,426 | Qoldiq: -2,826]
-• Вазелин косметический 100гр в баночках: [Kirim: 2,880 | Chiqim: 6 | Qoldiq: 2,874]
-• Вазелин косметический 20гр: [Kirim: 2,000 | Chiqim: 3,000 | Qoldiq: -1,000]
-• Вазелин косметический 20гр в тубах: [Kirim: 1,000 | Chiqim: 0 | Qoldiq: 1,000]
-• Вазелин косметический 40гр: [Kirim: 1,000 | Chiqim: 689 | Qoldiq: 311]</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>10480</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>37833928.57</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>10121</v>
-      </c>
-      <c r="I37" s="13" t="n">
-        <v>44842410.70000003</v>
-      </c>
-      <c r="J37" s="14" t="n">
-        <v>359</v>
-      </c>
-      <c r="K37" s="13" t="n">
-        <v>1296028.659983779</v>
-      </c>
-      <c r="L37" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>04014001005000000</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Резинадан бурун тозалагич</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>• Аспиратор (носочиска) MUMMY 1130-1 шт: [Kirim: 1,020 | Chiqim: 9 | Qoldiq: 1,011]
-• Аспиратор (носочиска) MUMMY 1130-1 шт -: [Kirim: 300 | Chiqim: 1,247 | Qoldiq: -947]
-• Аспиратор (носочиска) MUMMY 1130-1 шт -2025: [Kirim: 120 | Chiqim: 2 | Qoldiq: 118]
-• Аспиратор (носочиска) MUMMY 1133 шт: [Kirim: 120 | Chiqim: 2,359 | Qoldiq: -2,239]
-• Носочистка  "MUMMY" модель 1133: [Kirim: 2,160 | Chiqim: 0 | Qoldiq: 2,160]</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>3720</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>21428571.45</v>
-      </c>
-      <c r="H38" s="12" t="n">
-        <v>3617</v>
-      </c>
-      <c r="I38" s="13" t="n">
-        <v>29355357.24999998</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>103</v>
-      </c>
-      <c r="K38" s="13" t="n">
-        <v>593317.9729435483</v>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>03307001038000000</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>Ванна қабул қилиш учун восита</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>• Teddy Болалар упаси (Лаванда) 50 гр: [Kirim: 0 | Chiqim: 12 | Qoldiq: -12]
-• Teddy Чўмилиш тузи (Лаванда) 500 гр: [Kirim: 32 | Chiqim: 15 | Qoldiq: 17]
-• Teddy Чўмилиш тузи (Ромашка) 500 гр: [Kirim: 32 | Chiqim: 21 | Qoldiq: 11]
-• Teddy Чўмилиш тузи (Хвоя) 500 гр: [Kirim: 32 | Chiqim: 15 | Qoldiq: 17]
-• Teddy Чўмилиш тузи (Череда) 500 гр: [Kirim: 32 | Chiqim: 18 | Qoldiq: 14]</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>793600</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="I39" s="13" t="n">
-        <v>550714.28</v>
-      </c>
-      <c r="J39" s="14" t="n">
-        <v>47</v>
-      </c>
-      <c r="K39" s="13" t="n">
-        <v>291400</v>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>06214001014000000</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>Тиббий эластик тасма</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>• (01942-2)Пояс медицинский эластичный, согревающий, Размер 2: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• (01942-3)Пояс медицинский эластичный, согревающий, Размер 3: [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Пояс медицинский эластичный, согревающий, Размер 2: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]
-• Пояс медицинский эластичный, согревающий, Размер 3: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]
-• Пояс медицинский эластичный, согревающий, Размер 4: [Kirim: 20 | Chiqim: 12 | Qoldiq: 8]</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <v>1980000</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="I40" s="13" t="n">
-        <v>1552500.050000001</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K40" s="13" t="n">
-        <v>594000</v>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>03004900002002000</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>D-Пантенол, гидролизат, магния хлорид, ниацинамид, пиридоксин, рибофлавин, сульфат цинка, хлорид марганца - A11A</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>• Жидкий пластырь 100 мл С экстрактом подорожника в коробочке: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• Жидкий пластырь 50мл в коробочке: [Kirim: 120 | Chiqim: 0 | Qoldiq: 120]
-• Пантенол взрослый 130мл в коробочке: [Kirim: 60 | Chiqim: 0 | Qoldiq: 60]
-• Пантенол детский 130мл в коробочке: [Kirim: 24 | Chiqim: 0 | Qoldiq: 24]</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>264</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>9360000.010000002</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="14" t="n">
-        <v>264</v>
-      </c>
-      <c r="K41" s="13" t="n">
-        <v>9360000.010000002</v>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>07020999004000000</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>Болалар шишали бутилка</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>• Детские бутылки стеклянные (В1376): [Kirim: 144 | Chiqim: 144 | Qoldiq: 0]
-• Детские бутылки стеклянные (В1377): [Kirim: 96 | Chiqim: 94 | Qoldiq: 2]
-• Детские бутылки стеклянные (В1377)): [Kirim: 0 | Chiqim: 2 | Qoldiq: -2]
-• Детские бутылки стеклянные (В1378): [Kirim: 72 | Chiqim: 72 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>312</v>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>5297142.859999999</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>312</v>
-      </c>
-      <c r="I42" s="13" t="n">
-        <v>6428571.450000001</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>03304999024000000</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Маникюр ва педикюр учун косметика маҳсулотлари</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>• Маникюрный  набор (С-11): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Маникюрный набор  (FZ-47): [Kirim: 72 | Chiqim: 0 | Qoldiq: 72]
-• Маникюрный набор (FZ-47): [Kirim: 0 | Chiqim: 53 | Qoldiq: -53]
-• Маникюрный набор (С-11): [Kirim: 0 | Chiqim: 115 | Qoldiq: -115]</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="G43" s="13" t="n">
-        <v>2455714.28</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>168</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>3450000.020000001</v>
-      </c>
-      <c r="J43" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="K43" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="10" t="inlineStr">
-        <is>
-          <t>04014001004000000</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>Резинали кўкрак помпаси</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>• Грудная накладка  MUMMY - 1132 -шт: [Kirim: 624 | Chiqim: 0 | Qoldiq: 624]
-• Грудная накладка  MUMMY - 1132 -шт  04.2025: [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Грудная накладка MUMMY - 1132: [Kirim: 96 | Chiqim: 0 | Qoldiq: 96]
-• Грудная накладка MUMMY - 1132 -шт: [Kirim: 0 | Chiqim: 1,065 | Qoldiq: -1,065]</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>912</v>
-      </c>
-      <c r="G44" s="13" t="n">
-        <v>3257142.830000001</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>1065</v>
-      </c>
-      <c r="I44" s="13" t="n">
-        <v>4834821.41</v>
-      </c>
-      <c r="J44" s="15" t="n">
-        <v>-153</v>
-      </c>
-      <c r="K44" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="inlineStr">
-        <is>
-          <t>05601001002000000</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="inlineStr">
-        <is>
-          <t>Пахтали таёқча</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="10" t="inlineStr">
-        <is>
-          <t>• ПТ MG Cotton п.п. квадрат 100д: [Kirim: 1,875 | Chiqim: 1,545 | Qoldiq: 330]
-• ПТ MG Cotton п.п. квадрат 200д: [Kirim: 1,154 | Chiqim: 763 | Qoldiq: 391]
-• №1 Ватные палочки для ушей (ухочистка) BRICK 55: [Kirim: 40 | Chiqim: 0 | Qoldiq: 40]</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>3069</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>14379464.29</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>2308</v>
-      </c>
-      <c r="I45" s="13" t="n">
-        <v>11636428.72999998</v>
-      </c>
-      <c r="J45" s="14" t="n">
-        <v>761</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>3565582.380153144</v>
-      </c>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>03305005001000000</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>Шампунь (барча турлари)</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>• Шампунь "Антипедикулезный"110мл (комплект): [Kirim: 150 | Chiqim: 120 | Qoldiq: 30]
-• Шампунь "Антипедикулезный"130мл комплект: [Kirim: 150 | Chiqim: 94 | Qoldiq: 56]
-• Шампунь "Антипедикулезный"60мл (комплект): [Kirim: 300 | Chiqim: 179 | Qoldiq: 121]</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>600</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>3375000</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>393</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>2579553.519999999</v>
-      </c>
-      <c r="J46" s="14" t="n">
-        <v>207</v>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>1164375</v>
-      </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>10701001001000000</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>Bino va inshootlar ijaraga berish xizmati</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>• Ijara to'lovi DEKABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]
-• Ijara to'lovi NOYABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]
-• Ijara to'lovi OKTABR  oyi 2025 yil: [Kirim: 1 | Chiqim: 0 | Qoldiq: 1]</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>1071428.58</v>
-      </c>
-      <c r="H47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K47" s="13" t="n">
-        <v>1071428.58</v>
-      </c>
-      <c r="L47" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>03005001002001001</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Газлама медицина учун MM оқартирилган бўлакланган 1м, полиэтилен пакет 1 дона</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>• Марля медицинская отбеленная в кусках, 1 м: [Kirim: 500 | Chiqim: 10 | Qoldiq: 490]
-• Марля медицинская отбеленная в кусках, 1 м х 84 см: [Kirim: 0 | Chiqim: 450 | Qoldiq: -450]
-• Марля медицинская отбеленная в кусках, 2 м: [Kirim: 0 | Chiqim: 50 | Qoldiq: -50]</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="G48" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="H48" s="12" t="n">
-        <v>510</v>
-      </c>
-      <c r="I48" s="13" t="n">
-        <v>1095535.74</v>
-      </c>
-      <c r="J48" s="15" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K48" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180016</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза малина таъми билан</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E49" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №5 (апельсин): [Kirim: 0 | Chiqim: 400 | Qoldiq: -400]
-• Аскорбинка 3,0 №5 (малина): [Kirim: 1,600 | Chiqim: 1,000 | Qoldiq: 600]
-• Аскорбинка 3,0 №5 (яблоко): [Kirim: 0 | Chiqim: 400 | Qoldiq: -400]</t>
-        </is>
-      </c>
-      <c r="F49" s="12" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>960000</v>
-      </c>
-      <c r="H49" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I49" s="13" t="n">
-        <v>1046428.59</v>
-      </c>
-      <c r="J49" s="15" t="n">
-        <v>-200</v>
-      </c>
-      <c r="K49" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>08414002002000000</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>Ҳаво ёки вакуум насослари, компрессорлар, қурилиш соҳасида ишлатилмайдиган</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>• Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803: [Kirim: 240 | Chiqim: 304 | Qoldiq: -64]
-• №1 Молокоотсос электрический с принадлежностями. МОДЕЛЬ:BH803: [Kirim: 800 | Chiqim: 0 | Qoldiq: 800]</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>1040</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>94800000</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>304</v>
-      </c>
-      <c r="I50" s="13" t="n">
-        <v>38000000</v>
-      </c>
-      <c r="J50" s="14" t="n">
-        <v>736</v>
-      </c>
-      <c r="K50" s="13" t="n">
-        <v>67089230.76923077</v>
-      </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>03926999438000000</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>Бурун бўшлиғини ювиш учун мослама</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>• Аспиратор (носочиска) MUMMY1133: [Kirim: 180 | Chiqim: 0 | Qoldiq: 180]
-• Носочистка HELLO: [Kirim: 192 | Chiqim: 23 | Qoldiq: 169]</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>372</v>
-      </c>
-      <c r="G51" s="13" t="n">
-        <v>5400000</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I51" s="13" t="n">
-        <v>821428.5800000001</v>
-      </c>
-      <c r="J51" s="14" t="n">
-        <v>349</v>
-      </c>
-      <c r="K51" s="13" t="n">
-        <v>5066129.032258064</v>
-      </c>
-      <c r="L51" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>07013004008000000</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Шиша бутилкача</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>• Детские бутылки Стеклянные (В1377): [Kirim: 192 | Chiqim: 0 | Qoldiq: 192]
-• Детские бутылки Стеклянные (В1378): [Kirim: 144 | Chiqim: 0 | Qoldiq: 144]</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>336</v>
-      </c>
-      <c r="G52" s="13" t="n">
-        <v>6274285.72</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>336</v>
-      </c>
-      <c r="K52" s="13" t="n">
-        <v>6274285.72</v>
-      </c>
-      <c r="L52" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>03926001155000000</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>Спринцовка (ПВХ)</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412: [Kirim: 240 | Chiqim: 0 | Qoldiq: 240]
-• Ручной молокоотсос с принадлежностями. МОДЕЛЬ: RBT-412 (7.31.001): [Kirim: 0 | Chiqim: 222 | Qoldiq: -222]</t>
-        </is>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>9521781.43</v>
-      </c>
-      <c r="H53" s="12" t="n">
-        <v>222</v>
-      </c>
-      <c r="I53" s="13" t="n">
-        <v>11892857.18</v>
-      </c>
-      <c r="J53" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="K53" s="13" t="n">
-        <v>714133.6072499999</v>
-      </c>
-      <c r="L53" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>08414002001000000</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>Ҳаво ёки вакуум насослари, компрессорлар (барча турлари)</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E54" s="10" t="inlineStr">
-        <is>
-          <t>• Молокоотсос вакуумный электический  (RH-803): [Kirim: 200 | Chiqim: 0 | Qoldiq: 200]
-• Молокоотсос вакуумный электический (RH-803): [Kirim: 0 | Chiqim: 200 | Qoldiq: -200]</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>25714285.71</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="I54" s="13" t="n">
-        <v>29464285.72</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>03304011011004003</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Юз ва танани юмшатувчи, 75 мл</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>• Крем увлажняющий для лица и тела "Нежный",: [Kirim: 8 | Chiqim: 0 | Qoldiq: 8]
-• Крем увлажняющий для лица и тела "Нежный", 75 ml: [Kirim: 0 | Chiqim: 8 | Qoldiq: -8]</t>
-        </is>
-      </c>
-      <c r="F55" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>392857.14</v>
-      </c>
-      <c r="H55" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I55" s="13" t="n">
-        <v>463571.43</v>
-      </c>
-      <c r="J55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>03304011011000000</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун болалар креми</t>
-        </is>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="10" t="inlineStr">
-        <is>
-          <t>• Крем детский 50мл: [Kirim: 4,000 | Chiqim: 2,510 | Qoldiq: 1,490]</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G56" s="13" t="n">
-        <v>4107142.86</v>
-      </c>
-      <c r="H56" s="12" t="n">
-        <v>2510</v>
-      </c>
-      <c r="I56" s="13" t="n">
-        <v>3361607.11</v>
-      </c>
-      <c r="J56" s="14" t="n">
-        <v>1490</v>
-      </c>
-      <c r="K56" s="13" t="n">
-        <v>1529910.71535</v>
-      </c>
-      <c r="L56" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>04803001001000000</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Қоғоз салфетка</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>• полотенца рулонные: [Kirim: 8,400 | Chiqim: 7,236 | Qoldiq: 1,164]</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n">
-        <v>8400</v>
-      </c>
-      <c r="G57" s="13" t="n">
-        <v>37500000</v>
-      </c>
-      <c r="H57" s="12" t="n">
-        <v>7236</v>
-      </c>
-      <c r="I57" s="13" t="n">
-        <v>41981250.05999999</v>
-      </c>
-      <c r="J57" s="14" t="n">
-        <v>1164</v>
-      </c>
-      <c r="K57" s="13" t="n">
-        <v>5196428.571428572</v>
-      </c>
-      <c r="L57" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180012</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза билан</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (апельсин): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H58" s="12" t="n">
-        <v>360</v>
-      </c>
-      <c r="I58" s="13" t="n">
-        <v>510714.33</v>
-      </c>
-      <c r="J58" s="14" t="n">
-        <v>940</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L58" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180001</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза билан</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (яблоко): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G59" s="13" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H59" s="12" t="n">
-        <v>360</v>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>510714.33</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>940</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L59" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180005</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза билан</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (смородина): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H60" s="12" t="n">
-        <v>360</v>
-      </c>
-      <c r="I60" s="13" t="n">
-        <v>510714.33</v>
-      </c>
-      <c r="J60" s="14" t="n">
-        <v>940</v>
-      </c>
-      <c r="K60" s="13" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L60" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180014</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Raspberry Таблетка аскорбинка кислота глюкоза билан</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (малина): [Kirim: 1,300 | Chiqim: 360 | Qoldiq: 940]</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G61" s="13" t="n">
-        <v>1430000</v>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>360</v>
-      </c>
-      <c r="I61" s="13" t="n">
-        <v>510714.33</v>
-      </c>
-      <c r="J61" s="14" t="n">
-        <v>940</v>
-      </c>
-      <c r="K61" s="13" t="n">
-        <v>1034000</v>
-      </c>
-      <c r="L61" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180003</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Apple Таблетка аскорбинка кислота глюкоза олма таъми билан</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №5 (яблоко): [Kirim: 1,600 | Chiqim: 800 | Qoldiq: 800]</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G62" s="13" t="n">
-        <v>960000</v>
-      </c>
-      <c r="H62" s="12" t="n">
-        <v>800</v>
-      </c>
-      <c r="I62" s="13" t="n">
-        <v>463392.8699999999</v>
-      </c>
-      <c r="J62" s="14" t="n">
-        <v>800</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>480000</v>
-      </c>
-      <c r="L62" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180011</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Orange Таблетка аскорбинка кислота глюкоза апельсин таъми билан</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №5 (апельсин): [Kirim: 1,600 | Chiqim: 800 | Qoldiq: 800]</t>
-        </is>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>1600</v>
-      </c>
-      <c r="G63" s="13" t="n">
-        <v>960000</v>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>800</v>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>463392.8699999999</v>
-      </c>
-      <c r="J63" s="14" t="n">
-        <v>800</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>480000</v>
-      </c>
-      <c r="L63" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180007</t>
-        </is>
-      </c>
-      <c r="C64" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NARPAY VITA ZONE Blackcurrant Таблетка аскорбинка кислота глюкоза Қорағат таъми билан</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №5 (смородина): [Kirim: 1,000 | Chiqim: 400 | Qoldiq: 600]</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G64" s="13" t="n">
-        <v>600000</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="I64" s="13" t="n">
-        <v>232142.8699999999</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v>600</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>360000</v>
-      </c>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="10" t="inlineStr">
-        <is>
-          <t>04015001004000000</t>
-        </is>
-      </c>
-      <c r="C65" s="10" t="inlineStr">
-        <is>
-          <t>Жаррохлик қўлқопи</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>• Перчатки Хирургические, Латексные, Стерильные для Однократного Применения, Размер: 7,5: [Kirim: 4,000 | Chiqim: 3,450 | Qoldiq: 550]</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G65" s="13" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="H65" s="12" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I65" s="13" t="n">
-        <v>7700892.890000002</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v>550</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>1031250</v>
-      </c>
-      <c r="L65" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="10" t="inlineStr">
-        <is>
-          <t>01806001007000000</t>
-        </is>
-      </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>Шоколадли тўпламлар</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>• Chokovita N°60: [Kirim: 1,300 | Chiqim: 776 | Qoldiq: 524]</t>
-        </is>
-      </c>
-      <c r="F66" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G66" s="13" t="n">
-        <v>48450000</v>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>776</v>
-      </c>
-      <c r="I66" s="13" t="n">
-        <v>34642857.18999999</v>
-      </c>
-      <c r="J66" s="14" t="n">
-        <v>524</v>
-      </c>
-      <c r="K66" s="13" t="n">
-        <v>19529076.92307692</v>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>02106999028180023</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>Биологически активные добавки к пище NARPAY VITA ZONE Vanilla Таблетки аскорбиновой кислоты с глюкозой</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>• Аскорбинка 3,0 №10 (ваниль): [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]</t>
-        </is>
-      </c>
-      <c r="F67" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="G67" s="13" t="n">
-        <v>550000</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="K67" s="13" t="n">
-        <v>550000</v>
-      </c>
-      <c r="L67" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>03005001002001002</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Газлама медицина учун MM оқартирилган бўлакланган 2 м, полиэтилен пакет 1 дона</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>• Марля медицинская отбеленная в кусках, 2 м: [Kirim: 500 | Chiqim: 0 | Qoldiq: 500]</t>
-        </is>
-      </c>
-      <c r="F68" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="G68" s="13" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="14" t="n">
-        <v>500</v>
-      </c>
-      <c r="K68" s="13" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="L68" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="10" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>03005001002001003</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Газлама медицина учун MM оқартирилган бўлакланган 3 м, полиэтилен пакет 1 дона</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="10" t="inlineStr">
-        <is>
-          <t>• Марля медицинская отбеленная в кусках, 3 м: [Kirim: 400 | Chiqim: 0 | Qoldiq: 400]</t>
-        </is>
-      </c>
-      <c r="F69" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="G69" s="13" t="n">
-        <v>2040000</v>
-      </c>
-      <c r="H69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="14" t="n">
-        <v>400</v>
-      </c>
-      <c r="K69" s="13" t="n">
-        <v>2040000</v>
-      </c>
-      <c r="L69" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="10" t="inlineStr">
-        <is>
-          <t>02106999028199012</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Биологик фаол қўшимчалар овқат учун NUROMON MED Мойчечак гуллари кукунда</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="10" t="inlineStr">
-        <is>
-          <t>• Ромашка чай №15: [Kirim: 450 | Chiqim: 269 | Qoldiq: 181]</t>
-        </is>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="G70" s="13" t="n">
-        <v>883930.5</v>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>269</v>
-      </c>
-      <c r="I70" s="13" t="n">
-        <v>960714.3300000002</v>
-      </c>
-      <c r="J70" s="14" t="n">
-        <v>181</v>
-      </c>
-      <c r="K70" s="13" t="n">
-        <v>355536.49</v>
-      </c>
-      <c r="L70" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="10" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>04016001027000000</t>
-        </is>
-      </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Металл қўллаб-қувватлаш оёқ учун резина қистирма</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="10" t="inlineStr">
-        <is>
-          <t>• Наконечник 19мм №1 Китай: [Kirim: 400 | Chiqim: 290 | Qoldiq: 110]</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>400</v>
-      </c>
-      <c r="G71" s="13" t="n">
-        <v>1428580</v>
-      </c>
-      <c r="H71" s="12" t="n">
-        <v>290</v>
-      </c>
-      <c r="I71" s="13" t="n">
-        <v>1346428.56</v>
-      </c>
-      <c r="J71" s="14" t="n">
-        <v>110</v>
-      </c>
-      <c r="K71" s="13" t="n">
-        <v>392859.5</v>
-      </c>
-      <c r="L71" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>03306001003000000</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>Тиш ипи</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>• Зубная нить (616): [Kirim: 108 | Chiqim: 0 | Qoldiq: 108]</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="G72" s="13" t="n">
-        <v>1253571.43</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="14" t="n">
-        <v>108</v>
-      </c>
-      <c r="K72" s="13" t="n">
-        <v>1253571.43</v>
-      </c>
-      <c r="L72" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="10" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>03005001002001004</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Газлама медицина учун MM оқартирилган бўлакланган 5 м, полиэтилен пакет 1 дона</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="10" t="inlineStr">
-        <is>
-          <t>• Марля медицинская отбеленная в кусках, 5 м: [Kirim: 100 | Chiqim: 0 | Qoldiq: 100]</t>
-        </is>
-      </c>
-      <c r="F73" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="G73" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="14" t="n">
-        <v>100</v>
-      </c>
-      <c r="K73" s="13" t="n">
-        <v>850000</v>
-      </c>
-      <c r="L73" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>02007002003000000</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Мармелад</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>• Vita Buum life: [Kirim: 720 | Chiqim: 638 | Qoldiq: 82]</t>
-        </is>
-      </c>
-      <c r="F74" s="12" t="n">
-        <v>720</v>
-      </c>
-      <c r="G74" s="13" t="n">
-        <v>28944000</v>
-      </c>
-      <c r="H74" s="12" t="n">
-        <v>638</v>
-      </c>
-      <c r="I74" s="13" t="n">
-        <v>28482142.90999999</v>
-      </c>
-      <c r="J74" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="K74" s="13" t="n">
-        <v>3296400</v>
-      </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="10" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="10" t="inlineStr">
-        <is>
-          <t>01509001001000000</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>Зайтун мойи (тозаланган ёки тозаланмаган)</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="10" t="inlineStr">
-        <is>
-          <t>• Масло оливковое очищенное EXTRA VIRGIN OLIVE OIL 12x250ML TM Marioliva: [Kirim: 240 | Chiqim: 197 | Qoldiq: 43]</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="G75" s="13" t="n">
-        <v>6215357.140000001</v>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>197</v>
-      </c>
-      <c r="I75" s="13" t="n">
-        <v>7387500</v>
-      </c>
-      <c r="J75" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="K75" s="13" t="n">
-        <v>1113584.820916667</v>
-      </c>
-      <c r="L75" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>03402004012000000</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Юза-фаол органик моддалар (совундан ташқари), бошқалар</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="10" t="inlineStr">
-        <is>
-          <t>• "Nihol" 250 гр.: [Kirim: 50 | Chiqim: 23 | Qoldiq: 27]</t>
-        </is>
-      </c>
-      <c r="F76" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G76" s="13" t="n">
-        <v>2410714.29</v>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I76" s="13" t="n">
-        <v>1396428.63</v>
-      </c>
-      <c r="J76" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="K76" s="13" t="n">
-        <v>1301785.7166</v>
-      </c>
-      <c r="L76" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="10" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>08213001002000000</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>Қайчи (барча турдаги ва фойдаланиш мақсадлари учун)</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>• Маникюрний набор BABY CARE KIT: [Kirim: 144 | Chiqim: 120 | Qoldiq: 24]</t>
-        </is>
-      </c>
-      <c r="F77" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="G77" s="13" t="n">
-        <v>2468571.42</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="I77" s="13" t="n">
-        <v>2464285.73</v>
-      </c>
-      <c r="J77" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="K77" s="13" t="n">
-        <v>411428.5699999999</v>
-      </c>
-      <c r="L77" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>03401001005009001</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>Болалар совуни Bubchen мойчечак билан, 125 гр.</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>• Детское мыло,125 г: [Kirim: 24 | Chiqim: 12 | Qoldiq: 12]</t>
-        </is>
-      </c>
-      <c r="F78" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="G78" s="13" t="n">
-        <v>621428.5699999999</v>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I78" s="13" t="n">
-        <v>367500</v>
-      </c>
-      <c r="J78" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K78" s="13" t="n">
-        <v>310714.285</v>
-      </c>
-      <c r="L78" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>03005001003000000</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Бинт</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>• Бинт тканный нестерильный GT 7m x 14cm: [Kirim: 2,700 | Chiqim: 2,692 | Qoldiq: 8]</t>
-        </is>
-      </c>
-      <c r="F79" s="12" t="n">
-        <v>2700</v>
-      </c>
-      <c r="G79" s="13" t="n">
-        <v>6277500</v>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>2692</v>
-      </c>
-      <c r="I79" s="13" t="n">
-        <v>7210714.259999998</v>
-      </c>
-      <c r="J79" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="K79" s="13" t="n">
-        <v>18600</v>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="10" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
-        <is>
-          <t>03304011011004016</t>
-        </is>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун болалар креми BUBCHEN майин парвариш 0+, таглик остидан, 150 мл</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="10" t="inlineStr">
-        <is>
-          <t>• Крем для младенцев,150 мл: [Kirim: 20 | Chiqim: 13 | Qoldiq: 7]</t>
-        </is>
-      </c>
-      <c r="F80" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="G80" s="13" t="n">
-        <v>1267857.14</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I80" s="13" t="n">
-        <v>964553.58</v>
-      </c>
-      <c r="J80" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="K80" s="13" t="n">
-        <v>443749.999</v>
-      </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>03304011014002001</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун молочко  Bubchen болалар учун каритэ ва кунгабоқар ёғи билан, ПЭТ флакон 200 мл.</t>
-        </is>
-      </c>
-      <c r="D81" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="10" t="inlineStr">
-        <is>
-          <t>• Молочко,200 мл: [Kirim: 16 | Chiqim: 11 | Qoldiq: 5]</t>
-        </is>
-      </c>
-      <c r="F81" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="G81" s="13" t="n">
-        <v>814285.71</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I81" s="13" t="n">
-        <v>660982.1499999999</v>
-      </c>
-      <c r="J81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="K81" s="13" t="n">
-        <v>254464.284375</v>
-      </c>
-      <c r="L81" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>03401002001004009</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>Юз ювиш учун геллар BÜBCHEN чўмилиш учун, 200 мл</t>
-        </is>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="10" t="inlineStr">
-        <is>
-          <t>• Средство для купания младенцев,200 мл: [Kirim: 8 | Chiqim: 4 | Qoldiq: 4]</t>
-        </is>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G82" s="13" t="n">
-        <v>392857.14</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I82" s="13" t="n">
-        <v>231785.72</v>
-      </c>
-      <c r="J82" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K82" s="13" t="n">
-        <v>196428.57</v>
-      </c>
-      <c r="L82" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>03305005002018007</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>Болалар шампуни BUBCHEN таъсирчан тери учун, ПЭТ бутилка 200 мл.</t>
-        </is>
-      </c>
-      <c r="D83" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="10" t="inlineStr">
-        <is>
-          <t>• Детский шампунь, 200 мл: [Kirim: 16 | Chiqim: 12 | Qoldiq: 4]</t>
-        </is>
-      </c>
-      <c r="F83" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="G83" s="13" t="n">
-        <v>785714.29</v>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I83" s="13" t="n">
-        <v>695357.16</v>
-      </c>
-      <c r="J83" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K83" s="13" t="n">
-        <v>196428.5725</v>
-      </c>
-      <c r="L83" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="10" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="10" t="inlineStr">
-        <is>
-          <t>03401002001004004</t>
-        </is>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Юз ювиш учун геллар BÜBCHEN 400 мл</t>
-        </is>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="10" t="inlineStr">
-        <is>
-          <t>• Гель для купания, 400 мл: [Kirim: 8 | Chiqim: 4 | Qoldiq: 4]</t>
-        </is>
-      </c>
-      <c r="F84" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G84" s="13" t="n">
-        <v>785714.29</v>
-      </c>
-      <c r="H84" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I84" s="13" t="n">
-        <v>459642.86</v>
-      </c>
-      <c r="J84" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K84" s="13" t="n">
-        <v>392857.145</v>
-      </c>
-      <c r="L84" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>03306001002000000</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Ополаскиватель для рта</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>• ЛЕСНОЙ БАЛЬЗАМ ОПОЛАСКИВАТЕЛЬ ДЛЯ ДЕСЕН КОРА ДУБА ПИХТА ОТВАРЕ ТРАВ, 400 мл: [Kirim: 2 | Chiqim: 0 | Qoldiq: 2]</t>
-        </is>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" s="13" t="n">
-        <v>53928.57</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K85" s="13" t="n">
-        <v>53928.57</v>
-      </c>
-      <c r="L85" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="10" t="inlineStr">
-        <is>
-          <t>03304011011004005</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Косметик, 75мл</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="10" t="inlineStr">
-        <is>
-          <t>• Детский косметический крем,75 мл: [Kirim: 12 | Chiqim: 11 | Qoldiq: 1]</t>
-        </is>
-      </c>
-      <c r="F86" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G86" s="13" t="n">
-        <v>546428.5699999999</v>
-      </c>
-      <c r="H86" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I86" s="13" t="n">
-        <v>591250</v>
-      </c>
-      <c r="J86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="13" t="n">
-        <v>45535.71416666666</v>
-      </c>
-      <c r="L86" s="10" t="inlineStr">
-        <is>
-          <t>Omborda bor</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="10" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="10" t="inlineStr">
-        <is>
-          <t>09605002003000000</t>
-        </is>
-      </c>
-      <c r="C87" s="10" t="inlineStr">
-        <is>
-          <t>Саёҳат тўпламлари (шахсий гигиена, кийим ёки пойабзал учун)</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>• №1 Гигиенический набор для малышей RBT-409: [Kirim: 176 | Chiqim: 176 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F87" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="G87" s="13" t="n">
-        <v>2452107.43</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>176</v>
-      </c>
-      <c r="I87" s="13" t="n">
-        <v>3614285.72</v>
-      </c>
-      <c r="J87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="10" t="inlineStr">
-        <is>
-          <t>03305005002000000</t>
-        </is>
-      </c>
-      <c r="C88" s="10" t="inlineStr">
-        <is>
-          <t>Болалар шампуни</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="10" t="inlineStr">
-        <is>
-          <t>• Шампунь и средство для купания младенцев, 400 мл/ Bad &amp; Shampoo, 400ml: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F88" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G88" s="13" t="n">
-        <v>785714.29</v>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I88" s="13" t="n">
-        <v>919285.72</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>03304001003000000</t>
-        </is>
-      </c>
-      <c r="C89" s="10" t="inlineStr">
-        <is>
-          <t>Бадан учун балзам</t>
-        </is>
-      </c>
-      <c r="D89" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>• Солнцезащитный крем для лица младенцев и детей с чувствительной кожей ФЗ 50+ 50 мл/Sensitive Gesich: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F89" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G89" s="13" t="n">
-        <v>571428.5699999999</v>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I89" s="13" t="n">
-        <v>668571.4399999999</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="10" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="10" t="inlineStr">
-        <is>
-          <t>03305005002018008</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>Болалар шампуни BUBCHEN майин парвариш, ПЭТ бутилка 400 мл.</t>
-        </is>
-      </c>
-      <c r="D90" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>• Детский шампунь, 400 мл: [Kirim: 8 | Chiqim: 8 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F90" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G90" s="13" t="n">
-        <v>657142.86</v>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I90" s="13" t="n">
-        <v>769285.72</v>
-      </c>
-      <c r="J90" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="10" t="inlineStr">
-        <is>
-          <t>03304011011004006</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>Терини парвариш қилиш учун болалар креми BUBCHEN Чақалоқлар учун мой, 200мл</t>
-        </is>
-      </c>
-      <c r="D91" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>• Масло для младенцев, 200 мл: [Kirim: 16 | Chiqim: 16 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" s="13" t="n">
-        <v>857142.86</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I91" s="13" t="n">
-        <v>1011428.56</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
-        <is>
-          <t>04015001002000000</t>
-        </is>
-      </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>Тиббиёт қўлқоплари</t>
-        </is>
-      </c>
-      <c r="D92" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="10" t="inlineStr">
-        <is>
-          <t>• Перчатки Медицинские, Нитриловые Чёрного Цвета, Нестерильные для Однократного Применения LDH Glove, Размер:L: [Kirim: 2,000 | Chiqim: 2,000 | Qoldiq: 0]</t>
-        </is>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G92" s="13" t="n">
-        <v>625000</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I92" s="13" t="n">
-        <v>714285.7200000002</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="10" t="inlineStr">
-        <is>
-          <t>0 (Tugagan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="10" t="inlineStr">
-        <is>
-          <t>04421001010000000</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>Тиш кавлагич</t>
-        </is>
-      </c>
-      <c r="D93" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="10" t="inlineStr">
-        <is>
-          <t>• Зубная нить (616): [Kirim: 60 | Chiqim: 137 | Qoldiq: -77]</t>
-        </is>
-      </c>
-      <c r="F93" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G93" s="13" t="n">
-        <v>696428.5699999999</v>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>137</v>
-      </c>
-      <c r="I93" s="13" t="n">
-        <v>1957142.87</v>
-      </c>
-      <c r="J93" s="15" t="n">
-        <v>-77</v>
-      </c>
-      <c r="K93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="10" t="inlineStr">
-        <is>
-          <t>⚠️ MINUS (Xavfli!)</t>
         </is>
       </c>
     </row>
